--- a/research/traditional_assets/database/data/turkey/turkey_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_telecom_services.xlsx
@@ -644,10 +644,10 @@
         <v>0.4886824324324325</v>
       </c>
       <c r="X2">
-        <v>0.1210109805862918</v>
+        <v>0.1210119433843921</v>
       </c>
       <c r="Y2">
-        <v>0.3676714518461407</v>
+        <v>0.3676704890480404</v>
       </c>
       <c r="Z2">
         <v>1.050689755222621</v>
@@ -656,10 +656,10 @@
         <v>0.08951651192234648</v>
       </c>
       <c r="AB2">
-        <v>0.1080739339834453</v>
+        <v>0.1080745814366519</v>
       </c>
       <c r="AC2">
-        <v>-0.01855742206109887</v>
+        <v>-0.01855806951430546</v>
       </c>
       <c r="AD2">
         <v>2095.6</v>
@@ -775,10 +775,10 @@
         <v>0.4886824324324325</v>
       </c>
       <c r="X3">
-        <v>0.1210109805862918</v>
+        <v>0.1210119433843921</v>
       </c>
       <c r="Y3">
-        <v>0.3676714518461407</v>
+        <v>0.3676704890480404</v>
       </c>
       <c r="Z3">
         <v>1.050689755222621</v>
@@ -787,10 +787,10 @@
         <v>0.08951651192234648</v>
       </c>
       <c r="AB3">
-        <v>0.1080739339834453</v>
+        <v>0.1080745814366519</v>
       </c>
       <c r="AC3">
-        <v>-0.01855742206109887</v>
+        <v>-0.01855806951430546</v>
       </c>
       <c r="AD3">
         <v>2095.6</v>
@@ -1145,13 +1145,13 @@
         <v>4302.6</v>
       </c>
       <c r="L2">
-        <v>7201.9491035469</v>
+        <v>7201.93235623997</v>
       </c>
       <c r="M2">
         <v>6161.5</v>
       </c>
       <c r="N2">
-        <v>6965.2491035469</v>
+        <v>6965.23235623997</v>
       </c>
       <c r="O2">
         <v>2095.6</v>
@@ -1160,16 +1160,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.108073933983445</v>
+        <v>0.108074581436652</v>
       </c>
       <c r="R2">
-        <v>0.10088788537708</v>
+        <v>0.100888590573462</v>
       </c>
       <c r="S2">
         <v>0.0815121203198611</v>
       </c>
       <c r="T2">
-        <v>0.0722121203198612</v>
+        <v>0.07116212031986111</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.121010980586292</v>
+        <v>0.121011943384392</v>
       </c>
       <c r="X2">
-        <v>0.10088788537708</v>
+        <v>0.100888590573462</v>
       </c>
       <c r="Y2">
         <v>0.727356975691306</v>
@@ -1224,7 +1224,7 @@
         <v>4302.6</v>
       </c>
       <c r="AK2">
-        <v>0.1034031199258227</v>
+        <v>0.1034044436198718</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1008878853770797</v>
+        <v>0.1008885905734616</v>
       </c>
       <c r="C2">
-        <v>7201.949103546903</v>
+        <v>7201.932356239973</v>
       </c>
       <c r="D2">
-        <v>6965.249103546903</v>
+        <v>6965.232356239973</v>
       </c>
       <c r="E2">
         <v>-2095.6</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1008878853770797</v>
+        <v>0.1008885905734616</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1010142868668356</v>
+        <v>0.1010044903002265</v>
       </c>
       <c r="C3">
-        <v>7122.021631583588</v>
+        <v>7123.327115946431</v>
       </c>
       <c r="D3">
-        <v>6949.303631583588</v>
+        <v>6950.609115946431</v>
       </c>
       <c r="E3">
         <v>-2031.618</v>
@@ -1527,37 +1527,37 @@
         <v>1034.9</v>
       </c>
       <c r="M3">
-        <v>6.160367843073809</v>
+        <v>6.070793043073808</v>
       </c>
       <c r="N3">
-        <v>1028.739632156926</v>
+        <v>1028.829206956926</v>
       </c>
       <c r="O3">
-        <v>257.1849080392316</v>
+        <v>257.2073017392316</v>
       </c>
       <c r="P3">
-        <v>771.5547241176947</v>
+        <v>771.6219052176948</v>
       </c>
       <c r="Q3">
-        <v>1645.154724117695</v>
+        <v>1645.221905217695</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1013052178420575</v>
+        <v>0.1013059283808363</v>
       </c>
       <c r="T3">
         <v>0.5367847496465754</v>
       </c>
       <c r="U3">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>167.993215074576</v>
+        <v>170.4719618437202</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1011406883565915</v>
+        <v>0.1011203900269915</v>
       </c>
       <c r="C4">
-        <v>7042.16700047105</v>
+        <v>7044.783148885189</v>
       </c>
       <c r="D4">
-        <v>6933.43100047105</v>
+        <v>6936.047148885189</v>
       </c>
       <c r="E4">
         <v>-1967.636</v>
@@ -1609,37 +1609,37 @@
         <v>1034.9</v>
       </c>
       <c r="M4">
-        <v>12.32073568614762</v>
+        <v>12.14158608614762</v>
       </c>
       <c r="N4">
-        <v>1022.579264313852</v>
+        <v>1022.758413913852</v>
       </c>
       <c r="O4">
-        <v>255.6448160784631</v>
+        <v>255.6896034784631</v>
       </c>
       <c r="P4">
-        <v>766.9344482353894</v>
+        <v>767.0688104353893</v>
       </c>
       <c r="Q4">
-        <v>1640.534448235389</v>
+        <v>1640.668810435389</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1017310672961166</v>
+        <v>0.1017317832863207</v>
       </c>
       <c r="T4">
         <v>0.5409030920560167</v>
       </c>
       <c r="U4">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>83.99660753728799</v>
+        <v>85.23598092186009</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1012670898463474</v>
+        <v>0.1012362897537564</v>
       </c>
       <c r="C5">
-        <v>6962.384712227929</v>
+        <v>6966.300070747468</v>
       </c>
       <c r="D5">
-        <v>6917.630712227929</v>
+        <v>6921.546070747468</v>
       </c>
       <c r="E5">
         <v>-1903.654</v>
@@ -1691,37 +1691,37 @@
         <v>1034.9</v>
       </c>
       <c r="M5">
-        <v>18.48110352922142</v>
+        <v>18.21237912922142</v>
       </c>
       <c r="N5">
-        <v>1016.418896470779</v>
+        <v>1016.687620870779</v>
       </c>
       <c r="O5">
-        <v>254.1047241176947</v>
+        <v>254.1719052176947</v>
       </c>
       <c r="P5">
-        <v>762.314172353084</v>
+        <v>762.515715653084</v>
       </c>
       <c r="Q5">
-        <v>1635.914172353084</v>
+        <v>1636.115715653084</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1021656971512903</v>
+        <v>0.1021664187053202</v>
       </c>
       <c r="T5">
         <v>0.5451063487419412</v>
       </c>
       <c r="U5">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.997738358192</v>
+        <v>56.82398728124006</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1013934913361033</v>
+        <v>0.1013521894805214</v>
       </c>
       <c r="C6">
-        <v>6882.674273401874</v>
+        <v>6887.877500431655</v>
       </c>
       <c r="D6">
-        <v>6901.902273401874</v>
+        <v>6907.105500431655</v>
       </c>
       <c r="E6">
         <v>-1839.672</v>
@@ -1773,37 +1773,37 @@
         <v>1034.9</v>
       </c>
       <c r="M6">
-        <v>24.64147137229524</v>
+        <v>24.28317217229523</v>
       </c>
       <c r="N6">
-        <v>1010.258528627705</v>
+        <v>1010.616827827705</v>
       </c>
       <c r="O6">
-        <v>252.5646321569262</v>
+        <v>252.6542069569262</v>
       </c>
       <c r="P6">
-        <v>757.6938964707787</v>
+        <v>757.9626208707787</v>
       </c>
       <c r="Q6">
-        <v>1631.293896470779</v>
+        <v>1631.562620870779</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1026093817951134</v>
+        <v>0.1026101090288823</v>
       </c>
       <c r="T6">
         <v>0.5493971732754893</v>
       </c>
       <c r="U6">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.99830376864399</v>
+        <v>42.61799046093005</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1015198928258592</v>
+        <v>0.1014680892072864</v>
       </c>
       <c r="C7">
-        <v>6803.035195018139</v>
+        <v>6809.51506000993</v>
       </c>
       <c r="D7">
-        <v>6886.245195018139</v>
+        <v>6892.725060009931</v>
       </c>
       <c r="E7">
         <v>-1775.69</v>
@@ -1855,37 +1855,37 @@
         <v>1034.9</v>
       </c>
       <c r="M7">
-        <v>30.80183921536905</v>
+        <v>30.35396521536904</v>
       </c>
       <c r="N7">
-        <v>1004.098160784631</v>
+        <v>1004.546034784631</v>
       </c>
       <c r="O7">
-        <v>251.0245401961578</v>
+        <v>251.1365086961578</v>
       </c>
       <c r="P7">
-        <v>753.0736205884733</v>
+        <v>753.4095260884733</v>
       </c>
       <c r="Q7">
-        <v>1626.673620588473</v>
+        <v>1627.009526088473</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1030624071682802</v>
+        <v>0.1030631402013614</v>
       </c>
       <c r="T7">
         <v>0.553778330957112</v>
       </c>
       <c r="U7">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.59864301491519</v>
+        <v>34.09439236874403</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1016462943156151</v>
+        <v>0.1015839889340513</v>
       </c>
       <c r="C8">
-        <v>6723.466992528935</v>
+        <v>6731.212374695269</v>
       </c>
       <c r="D8">
-        <v>6870.658992528935</v>
+        <v>6878.404374695269</v>
       </c>
       <c r="E8">
         <v>-1711.708</v>
@@ -1937,37 +1937,37 @@
         <v>1034.9</v>
       </c>
       <c r="M8">
-        <v>36.96220705844285</v>
+        <v>36.42475825844285</v>
       </c>
       <c r="N8">
-        <v>997.9377929415573</v>
+        <v>998.4752417415573</v>
       </c>
       <c r="O8">
-        <v>249.4844482353893</v>
+        <v>249.6188104353893</v>
       </c>
       <c r="P8">
-        <v>748.453344706168</v>
+        <v>748.8564313061679</v>
       </c>
       <c r="Q8">
-        <v>1622.053344706168</v>
+        <v>1622.456431306168</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1035250713791739</v>
+        <v>0.1035258103349571</v>
       </c>
       <c r="T8">
         <v>0.5582527047596203</v>
       </c>
       <c r="U8">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.998869179096</v>
+        <v>28.41199364062003</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.101772695805371</v>
+        <v>0.1016998886608163</v>
       </c>
       <c r="C9">
-        <v>6643.969185763431</v>
+        <v>6652.969072808904</v>
       </c>
       <c r="D9">
-        <v>6855.143185763431</v>
+        <v>6864.143072808904</v>
       </c>
       <c r="E9">
         <v>-1647.726</v>
@@ -2019,37 +2019,37 @@
         <v>1034.9</v>
       </c>
       <c r="M9">
-        <v>43.12257490151666</v>
+        <v>42.49555130151666</v>
       </c>
       <c r="N9">
-        <v>991.7774250984834</v>
+        <v>992.4044486984834</v>
       </c>
       <c r="O9">
-        <v>247.9443562746208</v>
+        <v>248.1011121746209</v>
       </c>
       <c r="P9">
-        <v>743.8330688238625</v>
+        <v>744.3033365238625</v>
       </c>
       <c r="Q9">
-        <v>1617.433068823862</v>
+        <v>1617.903336523862</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1039976853580438</v>
+        <v>0.1039984303638989</v>
       </c>
       <c r="T9">
         <v>0.5628233016546557</v>
       </c>
       <c r="U9">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.99903072493942</v>
+        <v>24.35313740624574</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.101899097295127</v>
+        <v>0.1018157883875812</v>
       </c>
       <c r="C10">
-        <v>6564.541298878439</v>
+        <v>6574.78478574816</v>
       </c>
       <c r="D10">
-        <v>6839.697298878439</v>
+        <v>6849.94078574816</v>
       </c>
       <c r="E10">
         <v>-1583.744</v>
@@ -2101,37 +2101,37 @@
         <v>1034.9</v>
       </c>
       <c r="M10">
-        <v>49.28294274459047</v>
+        <v>48.56634434459046</v>
       </c>
       <c r="N10">
-        <v>985.6170572554096</v>
+        <v>986.3336556554096</v>
       </c>
       <c r="O10">
-        <v>246.4042643138524</v>
+        <v>246.5834139138524</v>
       </c>
       <c r="P10">
-        <v>739.2127929415572</v>
+        <v>739.7502417415573</v>
       </c>
       <c r="Q10">
-        <v>1612.812792941557</v>
+        <v>1613.350241741557</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1044805735538457</v>
+        <v>0.104481324741296</v>
       </c>
       <c r="T10">
         <v>0.5674932593517571</v>
       </c>
       <c r="U10">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.999151884322</v>
+        <v>21.30899523046502</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1020254987848829</v>
+        <v>0.1019316881143462</v>
       </c>
       <c r="C11">
-        <v>6485.182860309783</v>
+        <v>6496.65914795471</v>
       </c>
       <c r="D11">
-        <v>6824.320860309783</v>
+        <v>6835.79714795471</v>
       </c>
       <c r="E11">
         <v>-1519.762</v>
@@ -2183,37 +2183,37 @@
         <v>1034.9</v>
       </c>
       <c r="M11">
-        <v>55.44331058766428</v>
+        <v>54.63713738766427</v>
       </c>
       <c r="N11">
-        <v>979.4566894123358</v>
+        <v>980.2628626123358</v>
       </c>
       <c r="O11">
-        <v>244.8641723530839</v>
+        <v>245.0657156530839</v>
       </c>
       <c r="P11">
-        <v>734.5925170592518</v>
+        <v>735.1971469592518</v>
       </c>
       <c r="Q11">
-        <v>1608.192517059252</v>
+        <v>1608.797146959252</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1049740746770279</v>
+        <v>0.1049748321819326</v>
       </c>
       <c r="T11">
         <v>0.5722658534817617</v>
       </c>
       <c r="U11">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.665912786064</v>
+        <v>18.94132909374668</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1021519002746388</v>
+        <v>0.1020475878411111</v>
       </c>
       <c r="C12">
-        <v>6405.893402724301</v>
+        <v>6418.591796883182</v>
       </c>
       <c r="D12">
-        <v>6809.013402724302</v>
+        <v>6821.711796883183</v>
       </c>
       <c r="E12">
         <v>-1455.78</v>
@@ -2265,37 +2265,37 @@
         <v>1034.9</v>
       </c>
       <c r="M12">
-        <v>61.6036784307381</v>
+        <v>60.70793043073809</v>
       </c>
       <c r="N12">
-        <v>973.296321569262</v>
+        <v>974.192069569262</v>
       </c>
       <c r="O12">
-        <v>243.3240803923155</v>
+        <v>243.5480173923155</v>
       </c>
       <c r="P12">
-        <v>729.9722411769465</v>
+        <v>730.6440521769465</v>
       </c>
       <c r="Q12">
-        <v>1603.572241176946</v>
+        <v>1604.244052176946</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1054785424918363</v>
+        <v>0.1054793064545834</v>
       </c>
       <c r="T12">
         <v>0.5771445052590998</v>
       </c>
       <c r="U12">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.7993215074576</v>
+        <v>17.04719618437202</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1022783017643947</v>
+        <v>0.1021634875678761</v>
       </c>
       <c r="C13">
-        <v>6326.672462972487</v>
+        <v>6340.58237297021</v>
       </c>
       <c r="D13">
-        <v>6793.774462972488</v>
+        <v>6807.68437297021</v>
       </c>
       <c r="E13">
         <v>-1391.798</v>
@@ -2347,37 +2347,37 @@
         <v>1034.9</v>
       </c>
       <c r="M13">
-        <v>67.7640462738119</v>
+        <v>66.77872347381189</v>
       </c>
       <c r="N13">
-        <v>967.1359537261882</v>
+        <v>968.1212765261882</v>
       </c>
       <c r="O13">
-        <v>241.783988431547</v>
+        <v>242.0303191315471</v>
       </c>
       <c r="P13">
-        <v>725.3519652946411</v>
+        <v>726.0909573946412</v>
       </c>
       <c r="Q13">
-        <v>1598.951965294641</v>
+        <v>1599.690957394641</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1059943466620337</v>
+        <v>0.1059951172277431</v>
       </c>
       <c r="T13">
         <v>0.5821327896606479</v>
       </c>
       <c r="U13">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.27211046132509</v>
+        <v>15.49745107670183</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1024047032541506</v>
+        <v>0.1022793872946411</v>
       </c>
       <c r="C14">
-        <v>6247.519582041803</v>
+        <v>6262.630519603827</v>
       </c>
       <c r="D14">
-        <v>6778.603582041804</v>
+        <v>6793.714519603827</v>
       </c>
       <c r="E14">
         <v>-1327.816</v>
@@ -2429,37 +2429,37 @@
         <v>1034.9</v>
       </c>
       <c r="M14">
-        <v>73.9244141168857</v>
+        <v>72.8495165168857</v>
       </c>
       <c r="N14">
-        <v>960.9755858831144</v>
+        <v>962.0504834831144</v>
       </c>
       <c r="O14">
-        <v>240.2438964707786</v>
+        <v>240.5126208707786</v>
       </c>
       <c r="P14">
-        <v>720.7316894123358</v>
+        <v>721.5378626123357</v>
       </c>
       <c r="Q14">
-        <v>1594.331689412336</v>
+        <v>1595.137862612336</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.106521873654281</v>
+        <v>0.1065226509730202</v>
       </c>
       <c r="T14">
         <v>0.587234444162231</v>
       </c>
       <c r="U14">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.999434589548</v>
+        <v>14.20599682031001</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1025311047439065</v>
+        <v>0.102395287021406</v>
       </c>
       <c r="C15">
-        <v>6168.434305010574</v>
+        <v>6184.735883093241</v>
       </c>
       <c r="D15">
-        <v>6763.500305010575</v>
+        <v>6779.801883093241</v>
       </c>
       <c r="E15">
         <v>-1263.834</v>
@@ -2511,37 +2511,37 @@
         <v>1034.9</v>
       </c>
       <c r="M15">
-        <v>80.08478195995951</v>
+        <v>78.92030955995951</v>
       </c>
       <c r="N15">
-        <v>954.8152180400406</v>
+        <v>955.9796904400406</v>
       </c>
       <c r="O15">
-        <v>238.7038045100101</v>
+        <v>238.9949226100101</v>
       </c>
       <c r="P15">
-        <v>716.1114135300304</v>
+        <v>716.9847678300305</v>
       </c>
       <c r="Q15">
-        <v>1589.71141353003</v>
+        <v>1590.58476783003</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1070615277038213</v>
+        <v>0.1070623119308323</v>
       </c>
       <c r="T15">
         <v>0.5924533780776436</v>
       </c>
       <c r="U15">
-        <v>0.0962828270931482</v>
+        <v>0.09488282709314819</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.07221212031986116</v>
+        <v>0.07116212031986113</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.92255500573661</v>
+        <v>13.11322783413232</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1027730062336624</v>
+        <v>0.102668686748171</v>
       </c>
       <c r="C16">
-        <v>6075.735182501075</v>
+        <v>6088.159566460495</v>
       </c>
       <c r="D16">
-        <v>6734.783182501075</v>
+        <v>6747.207566460495</v>
       </c>
       <c r="E16">
         <v>-1199.852</v>
@@ -2593,37 +2593,37 @@
         <v>1034.9</v>
       </c>
       <c r="M16">
-        <v>87.23047260303332</v>
+        <v>86.33472460303332</v>
       </c>
       <c r="N16">
-        <v>947.6695273969667</v>
+        <v>948.5652753969667</v>
       </c>
       <c r="O16">
-        <v>236.9173818492417</v>
+        <v>237.1413188492417</v>
       </c>
       <c r="P16">
-        <v>710.752145547725</v>
+        <v>711.4239565477251</v>
       </c>
       <c r="Q16">
-        <v>1584.352145547725</v>
+        <v>1585.023956547725</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1076137318475371</v>
+        <v>0.1076145231434772</v>
       </c>
       <c r="T16">
         <v>0.5977936825492287</v>
       </c>
       <c r="U16">
-        <v>0.09738282709314819</v>
+        <v>0.09638282709314819</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.07303712031986115</v>
+        <v>0.07228712031986115</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.86397332397363</v>
+        <v>11.98706551458252</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1029076577234183</v>
+        <v>0.1027958364749359</v>
       </c>
       <c r="C17">
-        <v>5995.873550506731</v>
+        <v>6009.125491579918</v>
       </c>
       <c r="D17">
-        <v>6718.90355050673</v>
+        <v>6732.155491579918</v>
       </c>
       <c r="E17">
         <v>-1135.87</v>
@@ -2675,37 +2675,37 @@
         <v>1034.9</v>
       </c>
       <c r="M17">
-        <v>93.46122064610711</v>
+        <v>92.50149064610711</v>
       </c>
       <c r="N17">
-        <v>941.438779353893</v>
+        <v>942.398509353893</v>
       </c>
       <c r="O17">
-        <v>235.3596948384732</v>
+        <v>235.5996273384733</v>
       </c>
       <c r="P17">
-        <v>706.0790845154197</v>
+        <v>706.7988820154197</v>
       </c>
       <c r="Q17">
-        <v>1579.67908451542</v>
+        <v>1580.39888201542</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1081789290299284</v>
+        <v>0.1081797275611256</v>
       </c>
       <c r="T17">
         <v>0.6032596412436745</v>
       </c>
       <c r="U17">
-        <v>0.09738282709314819</v>
+        <v>0.09638282709314819</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.07303712031986115</v>
+        <v>0.07228712031986115</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.07304176904206</v>
+        <v>11.18792781361036</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1030423092131742</v>
+        <v>0.1029229862017009</v>
       </c>
       <c r="C18">
-        <v>5916.086626054212</v>
+        <v>5930.158425353319</v>
       </c>
       <c r="D18">
-        <v>6703.098626054212</v>
+        <v>6717.17042535332</v>
       </c>
       <c r="E18">
         <v>-1071.888</v>
@@ -2757,37 +2757,37 @@
         <v>1034.9</v>
       </c>
       <c r="M18">
-        <v>99.69196868918092</v>
+        <v>98.66825668918092</v>
       </c>
       <c r="N18">
-        <v>935.2080313108191</v>
+        <v>936.2317433108192</v>
       </c>
       <c r="O18">
-        <v>233.8020078277048</v>
+        <v>234.0579358277048</v>
       </c>
       <c r="P18">
-        <v>701.4060234831144</v>
+        <v>702.1738074831144</v>
       </c>
       <c r="Q18">
-        <v>1575.006023483114</v>
+        <v>1575.773807483114</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.108757583288091</v>
+        <v>0.1087583892268132</v>
       </c>
       <c r="T18">
         <v>0.6088557418117976</v>
       </c>
       <c r="U18">
-        <v>0.09738282709314819</v>
+        <v>0.09638282709314819</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.07303712031986115</v>
+        <v>0.07228712031986115</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.38097665847693</v>
+        <v>10.48868232525971</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1031769607029302</v>
+        <v>0.1030501359284658</v>
       </c>
       <c r="C19">
-        <v>5836.37388317551</v>
+        <v>5851.257921311958</v>
       </c>
       <c r="D19">
-        <v>6687.367883175511</v>
+        <v>6702.251921311959</v>
       </c>
       <c r="E19">
         <v>-1007.906</v>
@@ -2839,37 +2839,37 @@
         <v>1034.9</v>
       </c>
       <c r="M19">
-        <v>105.9227167322547</v>
+        <v>104.8350227322547</v>
       </c>
       <c r="N19">
-        <v>928.9772832677454</v>
+        <v>930.0649772677453</v>
       </c>
       <c r="O19">
-        <v>232.2443208169364</v>
+        <v>232.5162443169363</v>
       </c>
       <c r="P19">
-        <v>696.7329624508091</v>
+        <v>697.548732950809</v>
       </c>
       <c r="Q19">
-        <v>1570.332962450809</v>
+        <v>1571.148732950809</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1093501810223539</v>
+        <v>0.1093509945470957</v>
       </c>
       <c r="T19">
         <v>0.6145866881767431</v>
       </c>
       <c r="U19">
-        <v>0.09738282709314819</v>
+        <v>0.09638282709314819</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.07303712031986115</v>
+        <v>0.07228712031986115</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.770330972684169</v>
+        <v>9.871701012009138</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1036086121926861</v>
+        <v>0.1034067856552308</v>
       </c>
       <c r="C20">
-        <v>5722.457933893058</v>
+        <v>5745.781568012125</v>
       </c>
       <c r="D20">
-        <v>6637.433933893059</v>
+        <v>6660.757568012125</v>
       </c>
       <c r="E20">
         <v>-943.9239999999998</v>
@@ -2921,37 +2921,37 @@
         <v>1034.9</v>
       </c>
       <c r="M20">
-        <v>114.6871519753286</v>
+        <v>112.9596379753286</v>
       </c>
       <c r="N20">
-        <v>920.2128480246715</v>
+        <v>921.9403620246716</v>
       </c>
       <c r="O20">
-        <v>230.0532120061679</v>
+        <v>230.4850905061679</v>
       </c>
       <c r="P20">
-        <v>690.1596360185036</v>
+        <v>691.4552715185037</v>
       </c>
       <c r="Q20">
-        <v>1563.759636018503</v>
+        <v>1565.055271518504</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1099572323598915</v>
+        <v>0.1099580536556778</v>
       </c>
       <c r="T20">
         <v>0.6204574137213212</v>
       </c>
       <c r="U20">
-        <v>0.0995828270931482</v>
+        <v>0.09808282709314819</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.07468712031986115</v>
+        <v>0.07356212031986115</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.023678608939798</v>
+        <v>9.161679503842176</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.103759763682442</v>
+        <v>0.1035466853819958</v>
       </c>
       <c r="C21">
-        <v>5641.166373544242</v>
+        <v>5665.66291605282</v>
       </c>
       <c r="D21">
-        <v>6620.124373544242</v>
+        <v>6644.620916052821</v>
       </c>
       <c r="E21">
         <v>-879.9419999999998</v>
@@ -3003,37 +3003,37 @@
         <v>1034.9</v>
       </c>
       <c r="M21">
-        <v>121.0586604184024</v>
+        <v>119.2351734184024</v>
       </c>
       <c r="N21">
-        <v>913.8413395815977</v>
+        <v>915.6648265815977</v>
       </c>
       <c r="O21">
-        <v>228.4603348953994</v>
+        <v>228.9162066453994</v>
       </c>
       <c r="P21">
-        <v>685.3810046861983</v>
+        <v>686.7486199361983</v>
       </c>
       <c r="Q21">
-        <v>1558.981004686198</v>
+        <v>1560.348619936198</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1105792726193437</v>
+        <v>0.1105801018780521</v>
       </c>
       <c r="T21">
         <v>0.6264730954521854</v>
       </c>
       <c r="U21">
-        <v>0.0995828270931482</v>
+        <v>0.09808282709314819</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.07468712031986115</v>
+        <v>0.07356212031986115</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.548748155837703</v>
+        <v>8.679485845745221</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1039109151721979</v>
+        <v>0.1036865851087607</v>
       </c>
       <c r="C22">
-        <v>5559.964860506707</v>
+        <v>5585.622261895458</v>
       </c>
       <c r="D22">
-        <v>6602.904860506707</v>
+        <v>6628.562261895459</v>
       </c>
       <c r="E22">
         <v>-815.9599999999996</v>
@@ -3085,37 +3085,37 @@
         <v>1034.9</v>
       </c>
       <c r="M22">
-        <v>127.4301688614762</v>
+        <v>125.5107088614762</v>
       </c>
       <c r="N22">
-        <v>907.4698311385239</v>
+        <v>909.389291138524</v>
       </c>
       <c r="O22">
-        <v>226.867457784631</v>
+        <v>227.347322784631</v>
       </c>
       <c r="P22">
-        <v>680.602373353893</v>
+        <v>682.041968353893</v>
       </c>
       <c r="Q22">
-        <v>1554.202373353893</v>
+        <v>1555.641968353893</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1112168638852821</v>
+        <v>0.1112177013059856</v>
       </c>
       <c r="T22">
         <v>0.632639169226321</v>
       </c>
       <c r="U22">
-        <v>0.0995828270931482</v>
+        <v>0.09808282709314819</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.07468712031986115</v>
+        <v>0.07356212031986115</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.121310748045818</v>
+        <v>8.245511553457959</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1040620666619538</v>
+        <v>0.1038264848355257</v>
       </c>
       <c r="C23">
-        <v>5478.852693940993</v>
+        <v>5505.65904139051</v>
       </c>
       <c r="D23">
-        <v>6585.774693940994</v>
+        <v>6612.58104139051</v>
       </c>
       <c r="E23">
         <v>-751.9779999999998</v>
@@ -3167,37 +3167,37 @@
         <v>1034.9</v>
       </c>
       <c r="M23">
-        <v>133.80167730455</v>
+        <v>131.78624430455</v>
       </c>
       <c r="N23">
-        <v>901.0983226954502</v>
+        <v>903.1137556954501</v>
       </c>
       <c r="O23">
-        <v>225.2745806738625</v>
+        <v>225.7784389238625</v>
       </c>
       <c r="P23">
-        <v>675.8237420215876</v>
+        <v>677.3353167715876</v>
       </c>
       <c r="Q23">
-        <v>1549.423742021587</v>
+        <v>1550.935316771588</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1118705967022569</v>
+        <v>0.1118714424915884</v>
       </c>
       <c r="T23">
         <v>0.638961346133979</v>
       </c>
       <c r="U23">
-        <v>0.0995828270931482</v>
+        <v>0.09808282709314819</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.07468712031986115</v>
+        <v>0.07356212031986115</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.734581664805543</v>
+        <v>7.852868146150438</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1044607181517097</v>
+        <v>0.1040983845622906</v>
       </c>
       <c r="C24">
-        <v>5370.114527026255</v>
+        <v>5410.836410181522</v>
       </c>
       <c r="D24">
-        <v>6541.018527026255</v>
+        <v>6581.740410181523</v>
       </c>
       <c r="E24">
         <v>-687.9959999999996</v>
@@ -3249,37 +3249,37 @@
         <v>1034.9</v>
       </c>
       <c r="M24">
-        <v>142.2845917476238</v>
+        <v>139.1878629476238</v>
       </c>
       <c r="N24">
-        <v>892.6154082523763</v>
+        <v>895.7121370523763</v>
       </c>
       <c r="O24">
-        <v>223.1538520630941</v>
+        <v>223.9280342630941</v>
       </c>
       <c r="P24">
-        <v>669.4615561892822</v>
+        <v>671.7841027892822</v>
       </c>
       <c r="Q24">
-        <v>1543.061556189282</v>
+        <v>1545.384102789282</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1125410918991542</v>
+        <v>0.1125419462716938</v>
       </c>
       <c r="T24">
         <v>0.6454456301418335</v>
       </c>
       <c r="U24">
-        <v>0.1010828270931482</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.07581212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.273450956907871</v>
+        <v>7.435274729301876</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1046231196414656</v>
+        <v>0.1042442842890556</v>
       </c>
       <c r="C25">
-        <v>5288.073791621114</v>
+        <v>5330.423819249244</v>
       </c>
       <c r="D25">
-        <v>6522.959791621114</v>
+        <v>6565.309819249244</v>
       </c>
       <c r="E25">
         <v>-624.0139999999997</v>
@@ -3331,37 +3331,37 @@
         <v>1034.9</v>
       </c>
       <c r="M25">
-        <v>148.7520731906976</v>
+        <v>145.5145839906976</v>
       </c>
       <c r="N25">
-        <v>886.1479268093025</v>
+        <v>889.3854160093025</v>
       </c>
       <c r="O25">
-        <v>221.5369817023256</v>
+        <v>222.3463540023256</v>
       </c>
       <c r="P25">
-        <v>664.6109451069768</v>
+        <v>667.0390620069769</v>
       </c>
       <c r="Q25">
-        <v>1538.210945106977</v>
+        <v>1540.639062006977</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1132290025557111</v>
+        <v>0.1132298657343994</v>
       </c>
       <c r="T25">
         <v>0.652098337110931</v>
       </c>
       <c r="U25">
-        <v>0.1010828270931482</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.07581212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.957213958781441</v>
+        <v>7.112001914984404</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1047855211312216</v>
+        <v>0.1043901840158206</v>
       </c>
       <c r="C26">
-        <v>5206.132496399825</v>
+        <v>5250.093058362996</v>
       </c>
       <c r="D26">
-        <v>6505.000496399825</v>
+        <v>6548.961058362996</v>
       </c>
       <c r="E26">
         <v>-560.0319999999997</v>
@@ -3413,37 +3413,37 @@
         <v>1034.9</v>
       </c>
       <c r="M26">
-        <v>155.2195546337714</v>
+        <v>151.8413050337714</v>
       </c>
       <c r="N26">
-        <v>879.6804453662287</v>
+        <v>883.0586949662287</v>
       </c>
       <c r="O26">
-        <v>219.9201113415572</v>
+        <v>220.7646737415572</v>
       </c>
       <c r="P26">
-        <v>659.7603340246715</v>
+        <v>662.2940212246715</v>
       </c>
       <c r="Q26">
-        <v>1533.360334024671</v>
+        <v>1535.894021224671</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1139350161242827</v>
+        <v>0.1139358883408604</v>
       </c>
       <c r="T26">
         <v>0.6589261153160574</v>
       </c>
       <c r="U26">
-        <v>0.1010828270931482</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.07581212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.667330043832215</v>
+        <v>6.815668501860054</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1049479226209775</v>
+        <v>0.1045360837425855</v>
       </c>
       <c r="C27">
-        <v>5124.289822268498</v>
+        <v>5169.843517728234</v>
       </c>
       <c r="D27">
-        <v>6487.139822268498</v>
+        <v>6532.693517728234</v>
       </c>
       <c r="E27">
         <v>-496.0499999999997</v>
@@ -3495,37 +3495,37 @@
         <v>1034.9</v>
       </c>
       <c r="M27">
-        <v>161.6870360768452</v>
+        <v>158.1680260768452</v>
       </c>
       <c r="N27">
-        <v>873.2129639231548</v>
+        <v>876.7319739231549</v>
       </c>
       <c r="O27">
-        <v>218.3032409807887</v>
+        <v>219.1829934807887</v>
       </c>
       <c r="P27">
-        <v>654.9097229423661</v>
+        <v>657.5489804423662</v>
       </c>
       <c r="Q27">
-        <v>1528.509722942366</v>
+        <v>1531.148980442366</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1146598567213496</v>
+        <v>0.114660738216827</v>
       </c>
       <c r="T27">
         <v>0.6659359676066536</v>
       </c>
       <c r="U27">
-        <v>0.1010828270931482</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.07581212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.400636842078926</v>
+        <v>6.543041761785652</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1051103241107334</v>
+        <v>0.1046819834693505</v>
       </c>
       <c r="C28">
-        <v>5042.5449591045</v>
+        <v>5089.674593594265</v>
       </c>
       <c r="D28">
-        <v>6469.3769591045</v>
+        <v>6516.506593594266</v>
       </c>
       <c r="E28">
         <v>-432.0679999999998</v>
@@ -3577,37 +3577,37 @@
         <v>1034.9</v>
       </c>
       <c r="M28">
-        <v>168.154517519919</v>
+        <v>164.494747119919</v>
       </c>
       <c r="N28">
-        <v>866.7454824800811</v>
+        <v>870.4052528800811</v>
       </c>
       <c r="O28">
-        <v>216.6863706200203</v>
+        <v>217.6013132200203</v>
       </c>
       <c r="P28">
-        <v>650.0591118600609</v>
+        <v>652.8039396600608</v>
       </c>
       <c r="Q28">
-        <v>1523.659111860061</v>
+        <v>1526.403939660061</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1154042876048236</v>
+        <v>0.1154051786299819</v>
       </c>
       <c r="T28">
         <v>0.6731352753645635</v>
       </c>
       <c r="U28">
-        <v>0.1010828270931482</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.07581212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.154458501998969</v>
+        <v>6.291386309409281</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1055562256004893</v>
+        <v>0.1050303831961154</v>
       </c>
       <c r="C29">
-        <v>4930.288410388128</v>
+        <v>4987.361774272145</v>
       </c>
       <c r="D29">
-        <v>6421.102410388128</v>
+        <v>6478.175774272146</v>
       </c>
       <c r="E29">
         <v>-368.0859999999996</v>
@@ -3659,37 +3659,37 @@
         <v>1034.9</v>
       </c>
       <c r="M29">
-        <v>177.0405185629928</v>
+        <v>172.5489821629928</v>
       </c>
       <c r="N29">
-        <v>857.8594814370073</v>
+        <v>862.3510178370072</v>
       </c>
       <c r="O29">
-        <v>214.4648703592518</v>
+        <v>215.5877544592518</v>
       </c>
       <c r="P29">
-        <v>643.3946110777555</v>
+        <v>646.7632633777555</v>
       </c>
       <c r="Q29">
-        <v>1516.994611077756</v>
+        <v>1520.363263377755</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1161691138549682</v>
+        <v>0.1161700146708944</v>
       </c>
       <c r="T29">
         <v>0.6805318244309092</v>
       </c>
       <c r="U29">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.845554500179415</v>
+        <v>5.997717210655089</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1057291270902452</v>
+        <v>0.1051837829228804</v>
       </c>
       <c r="C30">
-        <v>4847.780891553864</v>
+        <v>4906.645400933228</v>
       </c>
       <c r="D30">
-        <v>6402.576891553864</v>
+        <v>6461.441400933229</v>
       </c>
       <c r="E30">
         <v>-304.1039999999996</v>
@@ -3741,37 +3741,37 @@
         <v>1034.9</v>
       </c>
       <c r="M30">
-        <v>183.5975748060667</v>
+        <v>178.9396852060667</v>
       </c>
       <c r="N30">
-        <v>851.3024251939335</v>
+        <v>855.9603147939334</v>
       </c>
       <c r="O30">
-        <v>212.8256062984834</v>
+        <v>213.9900786984834</v>
       </c>
       <c r="P30">
-        <v>638.4768188954502</v>
+        <v>641.9702360954501</v>
       </c>
       <c r="Q30">
-        <v>1512.07681889545</v>
+        <v>1515.57023609545</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1169551852787279</v>
+        <v>0.1169560961573879</v>
       </c>
       <c r="T30">
         <v>0.6881338331935422</v>
       </c>
       <c r="U30">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.636784696601579</v>
+        <v>5.783513024560264</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1059020285800011</v>
+        <v>0.1053371826496453</v>
       </c>
       <c r="C31">
-        <v>4765.3799611287</v>
+        <v>4826.015261043177</v>
       </c>
       <c r="D31">
-        <v>6384.157961128701</v>
+        <v>6444.793261043177</v>
       </c>
       <c r="E31">
         <v>-240.1219999999998</v>
@@ -3823,37 +3823,37 @@
         <v>1034.9</v>
       </c>
       <c r="M31">
-        <v>190.1546310491404</v>
+        <v>185.3303882491404</v>
       </c>
       <c r="N31">
-        <v>844.7453689508596</v>
+        <v>849.5696117508596</v>
       </c>
       <c r="O31">
-        <v>211.1863422377149</v>
+        <v>212.3924029377149</v>
       </c>
       <c r="P31">
-        <v>633.5590267131447</v>
+        <v>637.1772088131447</v>
       </c>
       <c r="Q31">
-        <v>1507.159026713145</v>
+        <v>1510.777208813145</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1177633995594949</v>
+        <v>0.1177643207843459</v>
       </c>
       <c r="T31">
         <v>0.6959499830480803</v>
       </c>
       <c r="U31">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.442412810511869</v>
+        <v>5.584081540954739</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.106074930069757</v>
+        <v>0.1054905823764103</v>
       </c>
       <c r="C32">
-        <v>4683.084701850939</v>
+        <v>4745.470689764068</v>
       </c>
       <c r="D32">
-        <v>6365.84470185094</v>
+        <v>6428.230689764068</v>
       </c>
       <c r="E32">
         <v>-176.1399999999999</v>
@@ -3905,37 +3905,37 @@
         <v>1034.9</v>
       </c>
       <c r="M32">
-        <v>196.7116872922142</v>
+        <v>191.7210912922142</v>
       </c>
       <c r="N32">
-        <v>838.1883127077858</v>
+        <v>843.1789087077859</v>
       </c>
       <c r="O32">
-        <v>209.5470781769465</v>
+        <v>210.7947271769465</v>
       </c>
       <c r="P32">
-        <v>628.6412345308394</v>
+        <v>632.3841815308394</v>
       </c>
       <c r="Q32">
-        <v>1502.241234530839</v>
+        <v>1505.984181530839</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1185947056768553</v>
+        <v>0.1185956375435028</v>
       </c>
       <c r="T32">
         <v>0.703989451469891</v>
       </c>
       <c r="U32">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.260999050161474</v>
+        <v>5.397945489589581</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1062478315595129</v>
+        <v>0.1056439821031752</v>
       </c>
       <c r="C33">
-        <v>4600.894206953632</v>
+        <v>4665.011029074783</v>
       </c>
       <c r="D33">
-        <v>6347.636206953632</v>
+        <v>6411.753029074784</v>
       </c>
       <c r="E33">
         <v>-112.1579999999997</v>
@@ -3987,37 +3987,37 @@
         <v>1034.9</v>
       </c>
       <c r="M33">
-        <v>203.2687435352881</v>
+        <v>198.1117943352881</v>
       </c>
       <c r="N33">
-        <v>831.631256464712</v>
+        <v>836.788205664712</v>
       </c>
       <c r="O33">
-        <v>207.907814116178</v>
+        <v>209.197051416178</v>
       </c>
       <c r="P33">
-        <v>623.723442348534</v>
+        <v>627.5911542485339</v>
       </c>
       <c r="Q33">
-        <v>1497.323442348534</v>
+        <v>1501.191154248534</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1194501076237043</v>
+        <v>0.1194510504406062</v>
       </c>
       <c r="T33">
         <v>0.7122619479618991</v>
       </c>
       <c r="U33">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.091289403382071</v>
+        <v>5.223818215731852</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1064207330492688</v>
+        <v>0.1057973818299402</v>
       </c>
       <c r="C34">
-        <v>4518.807580014874</v>
+        <v>4584.63562768383</v>
       </c>
       <c r="D34">
-        <v>6329.531580014875</v>
+        <v>6395.35962768383</v>
       </c>
       <c r="E34">
         <v>-48.1759999999997</v>
@@ -4069,37 +4069,37 @@
         <v>1034.9</v>
       </c>
       <c r="M34">
-        <v>209.8257997783619</v>
+        <v>204.5024973783619</v>
       </c>
       <c r="N34">
-        <v>825.0742002216382</v>
+        <v>830.3975026216383</v>
       </c>
       <c r="O34">
-        <v>206.2685500554095</v>
+        <v>207.5993756554096</v>
       </c>
       <c r="P34">
-        <v>618.8056501662286</v>
+        <v>622.7981269662287</v>
       </c>
       <c r="Q34">
-        <v>1492.405650166228</v>
+        <v>1496.398126966229</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1203306684513431</v>
+        <v>0.1203316225405657</v>
       </c>
       <c r="T34">
         <v>0.7207777531742605</v>
       </c>
       <c r="U34">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.932186609526382</v>
+        <v>5.060573896490232</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1065936345390247</v>
+        <v>0.1059507815567052</v>
       </c>
       <c r="C35">
-        <v>4436.823934810734</v>
+        <v>4504.343840943558</v>
       </c>
       <c r="D35">
-        <v>6311.529934810736</v>
+        <v>6379.04984094356</v>
       </c>
       <c r="E35">
         <v>15.80600000000049</v>
@@ -4151,37 +4151,37 @@
         <v>1034.9</v>
       </c>
       <c r="M35">
-        <v>216.3828560214357</v>
+        <v>210.8932004214357</v>
       </c>
       <c r="N35">
-        <v>818.5171439785644</v>
+        <v>824.0067995785644</v>
       </c>
       <c r="O35">
-        <v>204.6292859946411</v>
+        <v>206.0016998946411</v>
       </c>
       <c r="P35">
-        <v>613.8878579839233</v>
+        <v>618.0050996839233</v>
       </c>
       <c r="Q35">
-        <v>1487.487857983923</v>
+        <v>1491.605099683923</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1212375146768218</v>
+        <v>0.1212384803748522</v>
       </c>
       <c r="T35">
         <v>0.7295477615272893</v>
       </c>
       <c r="U35">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.782726409237704</v>
+        <v>4.907223172354163</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1067665360287807</v>
+        <v>0.1061041812834701</v>
       </c>
       <c r="C36">
-        <v>4354.942395170618</v>
+        <v>4424.135030765656</v>
       </c>
       <c r="D36">
-        <v>6293.630395170618</v>
+        <v>6362.823030765657</v>
       </c>
       <c r="E36">
         <v>79.78800000000047</v>
@@ -4233,37 +4233,37 @@
         <v>1034.9</v>
       </c>
       <c r="M36">
-        <v>222.9399122645095</v>
+        <v>217.2839034645095</v>
       </c>
       <c r="N36">
-        <v>811.9600877354906</v>
+        <v>817.6160965354906</v>
       </c>
       <c r="O36">
-        <v>202.9900219338726</v>
+        <v>204.4040241338726</v>
       </c>
       <c r="P36">
-        <v>608.9700658016179</v>
+        <v>613.2120724016179</v>
       </c>
       <c r="Q36">
-        <v>1482.570065801618</v>
+        <v>1486.812072401618</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1221718410909513</v>
+        <v>0.1221728187495717</v>
       </c>
       <c r="T36">
         <v>0.7385835277091978</v>
       </c>
       <c r="U36">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.642057985436594</v>
+        <v>4.762893079049629</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1069394375185366</v>
+        <v>0.1062575810102351</v>
       </c>
       <c r="C37">
-        <v>4273.162094835125</v>
+        <v>4344.008565537915</v>
       </c>
       <c r="D37">
-        <v>6275.832094835125</v>
+        <v>6346.678565537915</v>
       </c>
       <c r="E37">
         <v>143.7700000000004</v>
@@ -4315,37 +4315,37 @@
         <v>1034.9</v>
       </c>
       <c r="M37">
-        <v>229.4969685075833</v>
+        <v>223.6746065075833</v>
       </c>
       <c r="N37">
-        <v>805.4030314924167</v>
+        <v>811.2253934924167</v>
       </c>
       <c r="O37">
-        <v>201.3507578731042</v>
+        <v>202.8063483731042</v>
       </c>
       <c r="P37">
-        <v>604.0522736193126</v>
+        <v>608.4190451193126</v>
       </c>
       <c r="Q37">
-        <v>1477.652273619312</v>
+        <v>1482.019045119313</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.123134916010131</v>
+        <v>0.1231359059973595</v>
       </c>
       <c r="T37">
         <v>0.7478973174659342</v>
       </c>
       <c r="U37">
-        <v>0.1024828270931482</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.07686212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.509427757281263</v>
+        <v>4.626810419648212</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1078143390082925</v>
+        <v>0.1070859807370001</v>
       </c>
       <c r="C38">
-        <v>4120.640332305444</v>
+        <v>4194.238809083156</v>
       </c>
       <c r="D38">
-        <v>6187.292332305444</v>
+        <v>6260.890809083156</v>
       </c>
       <c r="E38">
         <v>207.7520000000004</v>
@@ -4397,37 +4397,37 @@
         <v>1034.9</v>
       </c>
       <c r="M38">
-        <v>242.0427399506571</v>
+        <v>235.8236895506571</v>
       </c>
       <c r="N38">
-        <v>792.8572600493429</v>
+        <v>799.0763104493429</v>
       </c>
       <c r="O38">
-        <v>198.2143150123357</v>
+        <v>199.7690776123357</v>
       </c>
       <c r="P38">
-        <v>594.6429450370072</v>
+        <v>599.3072328370072</v>
       </c>
       <c r="Q38">
-        <v>1468.242945037007</v>
+        <v>1472.907232837007</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1241280870205351</v>
+        <v>0.1241290897216407</v>
       </c>
       <c r="T38">
         <v>0.7575021631525686</v>
       </c>
       <c r="U38">
-        <v>0.1050828270931482</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.07881212031986115</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.275691145336459</v>
+        <v>4.388448005253068</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1080067404980484</v>
+        <v>0.107258130463765</v>
       </c>
       <c r="C39">
-        <v>4037.52143085779</v>
+        <v>4112.719493288554</v>
       </c>
       <c r="D39">
-        <v>6168.155430857791</v>
+        <v>6243.353493288555</v>
       </c>
       <c r="E39">
         <v>271.7340000000004</v>
@@ -4479,37 +4479,37 @@
         <v>1034.9</v>
       </c>
       <c r="M39">
-        <v>248.7661493937309</v>
+        <v>242.3743475937309</v>
       </c>
       <c r="N39">
-        <v>786.1338506062691</v>
+        <v>792.5256524062692</v>
       </c>
       <c r="O39">
-        <v>196.5334626515673</v>
+        <v>198.1314131015673</v>
       </c>
       <c r="P39">
-        <v>589.6003879547018</v>
+        <v>594.3942393047018</v>
       </c>
       <c r="Q39">
-        <v>1463.200387954702</v>
+        <v>1467.994239304702</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1251527872693647</v>
+        <v>0.1251538030879625</v>
       </c>
       <c r="T39">
         <v>0.7674119245752866</v>
       </c>
       <c r="U39">
-        <v>0.1050828270931482</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.07881212031986115</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.160131925192231</v>
+        <v>4.269841302408391</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1081991419878043</v>
+        <v>0.10743028019053</v>
       </c>
       <c r="C40">
-        <v>3954.520542838864</v>
+        <v>4031.298150247374</v>
       </c>
       <c r="D40">
-        <v>6149.136542838864</v>
+        <v>6225.914150247374</v>
       </c>
       <c r="E40">
         <v>335.7160000000003</v>
@@ -4561,37 +4561,37 @@
         <v>1034.9</v>
       </c>
       <c r="M40">
-        <v>255.4895588368047</v>
+        <v>248.9250056368047</v>
       </c>
       <c r="N40">
-        <v>779.4104411631954</v>
+        <v>785.9749943631954</v>
       </c>
       <c r="O40">
-        <v>194.8526102907989</v>
+        <v>196.4937485907988</v>
       </c>
       <c r="P40">
-        <v>584.5578308723966</v>
+        <v>589.4812457723965</v>
       </c>
       <c r="Q40">
-        <v>1458.157830872397</v>
+        <v>1463.081245772396</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1262105423649308</v>
+        <v>0.1262115717241657</v>
       </c>
       <c r="T40">
         <v>0.7776413557213182</v>
       </c>
       <c r="U40">
-        <v>0.1050828270931482</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.07881212031986115</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.05065476926612</v>
+        <v>4.157477057608171</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1091812934775602</v>
+        <v>0.1076024299172949</v>
       </c>
       <c r="C41">
-        <v>3795.252011357777</v>
+        <v>3949.973961254782</v>
       </c>
       <c r="D41">
-        <v>6053.850011357777</v>
+        <v>6208.571961254783</v>
       </c>
       <c r="E41">
         <v>399.6980000000003</v>
@@ -4643,45 +4643,45 @@
         <v>1034.9</v>
       </c>
       <c r="M41">
-        <v>268.9502728798785</v>
+        <v>255.4756636798785</v>
       </c>
       <c r="N41">
-        <v>765.9497271201216</v>
+        <v>779.4243363201216</v>
       </c>
       <c r="O41">
-        <v>191.4874317800304</v>
+        <v>194.8560840800304</v>
       </c>
       <c r="P41">
-        <v>574.4622953400911</v>
+        <v>584.5682522400912</v>
       </c>
       <c r="Q41">
-        <v>1448.062295340091</v>
+        <v>1458.168252240091</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1273029779554334</v>
+        <v>0.1273040212992608</v>
       </c>
       <c r="T41">
         <v>0.7882061780524655</v>
       </c>
       <c r="U41">
-        <v>0.1077828270931482</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.08083712031986115</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.84792321985194</v>
+        <v>4.050875081772063</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1093939449673162</v>
+        <v>0.1088245796440599</v>
       </c>
       <c r="C42">
-        <v>3711.026571131891</v>
+        <v>3765.597591805573</v>
       </c>
       <c r="D42">
-        <v>6033.606571131892</v>
+        <v>6088.177591805574</v>
       </c>
       <c r="E42">
         <v>463.6800000000007</v>
@@ -4725,37 +4725,37 @@
         <v>1034.9</v>
       </c>
       <c r="M42">
-        <v>275.8464337229524</v>
+        <v>270.9838017229524</v>
       </c>
       <c r="N42">
-        <v>759.0535662770477</v>
+        <v>763.9161982770477</v>
       </c>
       <c r="O42">
-        <v>189.7633915692619</v>
+        <v>190.9790495692619</v>
       </c>
       <c r="P42">
-        <v>569.2901747077858</v>
+        <v>572.9371487077858</v>
       </c>
       <c r="Q42">
-        <v>1442.890174707786</v>
+        <v>1446.537148707786</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1284318280656195</v>
+        <v>0.1284328858601924</v>
       </c>
       <c r="T42">
         <v>0.7991231611279844</v>
       </c>
       <c r="U42">
-        <v>0.1077828270931482</v>
+        <v>0.1058828270931482</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.08083712031986115</v>
+        <v>0.07941212031986114</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.751725139355641</v>
+        <v>3.819047461213413</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1096065964570721</v>
+        <v>0.1090229793708248</v>
       </c>
       <c r="C43">
-        <v>3626.936063591992</v>
+        <v>3682.510311055893</v>
       </c>
       <c r="D43">
-        <v>6013.498063591993</v>
+        <v>6069.072311055894</v>
       </c>
       <c r="E43">
         <v>527.6620000000007</v>
@@ -4807,37 +4807,37 @@
         <v>1034.9</v>
       </c>
       <c r="M43">
-        <v>282.7425945660262</v>
+        <v>277.7583967660262</v>
       </c>
       <c r="N43">
-        <v>752.157405433974</v>
+        <v>757.1416032339739</v>
       </c>
       <c r="O43">
-        <v>188.0393513584935</v>
+        <v>189.2854008084935</v>
       </c>
       <c r="P43">
-        <v>564.1180540754805</v>
+        <v>567.8562024254804</v>
       </c>
       <c r="Q43">
-        <v>1437.71805407548</v>
+        <v>1441.45620242548</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1295989442812356</v>
+        <v>0.1296000170164098</v>
       </c>
       <c r="T43">
         <v>0.8104102114264023</v>
       </c>
       <c r="U43">
-        <v>0.1077828270931482</v>
+        <v>0.1058828270931482</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.08083712031986115</v>
+        <v>0.07941212031986114</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.660219648151845</v>
+        <v>3.725899962159427</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.109819247946828</v>
+        <v>0.1092213790975898</v>
       </c>
       <c r="C44">
-        <v>3542.979144128254</v>
+        <v>3599.542563578256</v>
       </c>
       <c r="D44">
-        <v>5993.523144128254</v>
+        <v>6050.086563578257</v>
       </c>
       <c r="E44">
         <v>591.6440000000002</v>
@@ -4889,37 +4889,37 @@
         <v>1034.9</v>
       </c>
       <c r="M44">
-        <v>289.6387554090999</v>
+        <v>284.5329918090999</v>
       </c>
       <c r="N44">
-        <v>745.2612445909001</v>
+        <v>750.3670081909002</v>
       </c>
       <c r="O44">
-        <v>186.315311147725</v>
+        <v>187.591752047725</v>
       </c>
       <c r="P44">
-        <v>558.9459334431751</v>
+        <v>562.7752561431751</v>
       </c>
       <c r="Q44">
-        <v>1432.545933443175</v>
+        <v>1436.375256143175</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.130806305883597</v>
+        <v>0.1308073940745657</v>
       </c>
       <c r="T44">
         <v>0.8220864703558001</v>
       </c>
       <c r="U44">
-        <v>0.1077828270931482</v>
+        <v>0.1058828270931482</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.08083712031986115</v>
+        <v>0.07941212031986114</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.573071561291087</v>
+        <v>3.637188058298489</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1115476494365839</v>
+        <v>0.1094197788243547</v>
       </c>
       <c r="C45">
-        <v>3321.436920759512</v>
+        <v>3516.693231070985</v>
       </c>
       <c r="D45">
-        <v>5835.962920759513</v>
+        <v>6031.219231070985</v>
       </c>
       <c r="E45">
         <v>655.6260000000002</v>
@@ -4971,45 +4971,45 @@
         <v>1034.9</v>
       </c>
       <c r="M45">
-        <v>309.4656784521737</v>
+        <v>291.3075868521738</v>
       </c>
       <c r="N45">
-        <v>725.4343215478264</v>
+        <v>743.5924131478264</v>
       </c>
       <c r="O45">
-        <v>181.3585803869566</v>
+        <v>185.8981032869566</v>
       </c>
       <c r="P45">
-        <v>544.0757411608697</v>
+        <v>557.6943098608698</v>
       </c>
       <c r="Q45">
-        <v>1417.67574116087</v>
+        <v>1431.29430986087</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1320560310509536</v>
+        <v>0.1320571352400254</v>
       </c>
       <c r="T45">
         <v>0.8341724225809661</v>
       </c>
       <c r="U45">
-        <v>0.1124828270931482</v>
+        <v>0.1058828270931482</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.08436212031986115</v>
+        <v>0.07941212031986114</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.344151135519018</v>
+        <v>3.55260228950085</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1117955509263398</v>
+        <v>0.1105421785511197</v>
       </c>
       <c r="C46">
-        <v>3235.533080848949</v>
+        <v>3348.151283158997</v>
       </c>
       <c r="D46">
-        <v>5814.04108084895</v>
+        <v>5926.659283158998</v>
       </c>
       <c r="E46">
         <v>719.6080000000006</v>
@@ -5053,37 +5053,37 @@
         <v>1034.9</v>
       </c>
       <c r="M46">
-        <v>316.6625546952476</v>
+        <v>305.9647642952476</v>
       </c>
       <c r="N46">
-        <v>718.2374453047526</v>
+        <v>728.9352357047525</v>
       </c>
       <c r="O46">
-        <v>179.5593613261881</v>
+        <v>182.2338089261881</v>
       </c>
       <c r="P46">
-        <v>538.6780839785645</v>
+        <v>546.7014267785644</v>
       </c>
       <c r="Q46">
-        <v>1412.278083978564</v>
+        <v>1420.301426778564</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1333503892600016</v>
+        <v>0.1333515100185372</v>
       </c>
       <c r="T46">
         <v>0.8466900159570312</v>
       </c>
       <c r="U46">
-        <v>0.1124828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.08436212031986115</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.268147700620858</v>
+        <v>3.382415626792077</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1120434524160957</v>
+        <v>0.1107615782778847</v>
       </c>
       <c r="C47">
-        <v>3149.793316226548</v>
+        <v>3264.152721649487</v>
       </c>
       <c r="D47">
-        <v>5792.283316226549</v>
+        <v>5906.642721649488</v>
       </c>
       <c r="E47">
         <v>783.5900000000006</v>
@@ -5135,37 +5135,37 @@
         <v>1034.9</v>
       </c>
       <c r="M47">
-        <v>323.8594309383214</v>
+        <v>312.9185089383214</v>
       </c>
       <c r="N47">
-        <v>711.0405690616788</v>
+        <v>721.9814910616788</v>
       </c>
       <c r="O47">
-        <v>177.7601422654197</v>
+        <v>180.4953727654197</v>
       </c>
       <c r="P47">
-        <v>533.280426796259</v>
+        <v>541.4861182962591</v>
       </c>
       <c r="Q47">
-        <v>1406.880426796259</v>
+        <v>1415.086118296259</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1346918150402876</v>
+        <v>0.134692952970813</v>
       </c>
       <c r="T47">
         <v>0.8596627945467711</v>
       </c>
       <c r="U47">
-        <v>0.1124828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.08436212031986115</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.195522196162617</v>
+        <v>3.307250835085587</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1122913539058516</v>
+        <v>0.1109809780046496</v>
       </c>
       <c r="C48">
-        <v>3064.215791713482</v>
+        <v>3180.288911972811</v>
       </c>
       <c r="D48">
-        <v>5770.687791713483</v>
+        <v>5886.760911972811</v>
       </c>
       <c r="E48">
         <v>847.5720000000006</v>
@@ -5217,37 +5217,37 @@
         <v>1034.9</v>
       </c>
       <c r="M48">
-        <v>331.0563071813952</v>
+        <v>319.8722535813952</v>
       </c>
       <c r="N48">
-        <v>703.8436928186049</v>
+        <v>715.0277464186049</v>
       </c>
       <c r="O48">
-        <v>175.9609232046512</v>
+        <v>178.7569366046512</v>
       </c>
       <c r="P48">
-        <v>527.8827696139538</v>
+        <v>536.2708098139537</v>
       </c>
       <c r="Q48">
-        <v>1401.482769613954</v>
+        <v>1409.870809813954</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1360829232568805</v>
+        <v>0.1360840789953953</v>
       </c>
       <c r="T48">
         <v>0.8731160464176125</v>
       </c>
       <c r="U48">
-        <v>0.1124828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.08436212031986115</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.126054322332995</v>
+        <v>3.235354077801118</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1125392553956076</v>
+        <v>0.1112003777314146</v>
       </c>
       <c r="C49">
-        <v>2978.798699397839</v>
+        <v>3096.558497966372</v>
       </c>
       <c r="D49">
-        <v>5749.25269939784</v>
+        <v>5867.012497966372</v>
       </c>
       <c r="E49">
         <v>911.5540000000005</v>
@@ -5299,37 +5299,37 @@
         <v>1034.9</v>
       </c>
       <c r="M49">
-        <v>338.253183424469</v>
+        <v>326.825998224469</v>
       </c>
       <c r="N49">
-        <v>696.6468165755311</v>
+        <v>708.0740017755311</v>
       </c>
       <c r="O49">
-        <v>174.1617041438828</v>
+        <v>177.0185004438828</v>
       </c>
       <c r="P49">
-        <v>522.4851124316483</v>
+        <v>531.0555013316483</v>
       </c>
       <c r="Q49">
-        <v>1396.085112431648</v>
+        <v>1404.655501331648</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1375265261231562</v>
+        <v>0.1375277003416601</v>
       </c>
       <c r="T49">
         <v>0.8870769681703726</v>
       </c>
       <c r="U49">
-        <v>0.1124828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.08436212031986115</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.059542528240804</v>
+        <v>3.166516756996839</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1161351568853634</v>
+        <v>0.1114197774581795</v>
       </c>
       <c r="C50">
-        <v>2620.884798734803</v>
+        <v>3012.960141604894</v>
       </c>
       <c r="D50">
-        <v>5455.320798734803</v>
+        <v>5847.396141604895</v>
       </c>
       <c r="E50">
         <v>975.5360000000005</v>
@@ -5381,45 +5381,45 @@
         <v>1034.9</v>
       </c>
       <c r="M50">
-        <v>374.0116244675428</v>
+        <v>333.7797428675428</v>
       </c>
       <c r="N50">
-        <v>660.8883755324573</v>
+        <v>701.1202571324573</v>
       </c>
       <c r="O50">
-        <v>165.2220938831143</v>
+        <v>175.2800642831143</v>
       </c>
       <c r="P50">
-        <v>495.666281649343</v>
+        <v>525.8401928493429</v>
       </c>
       <c r="Q50">
-        <v>1369.266281649343</v>
+        <v>1399.440192849343</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1390256521765963</v>
+        <v>0.1390268455858581</v>
       </c>
       <c r="T50">
         <v>0.901574848452085</v>
       </c>
       <c r="U50">
-        <v>0.1217828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.09133712031986115</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.767026296236977</v>
+        <v>3.100547657892737</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1164528083751194</v>
+        <v>0.1116391771849445</v>
       </c>
       <c r="C51">
-        <v>2532.375949503077</v>
+        <v>2929.492522698226</v>
       </c>
       <c r="D51">
-        <v>5430.793949503078</v>
+        <v>5827.910522698226</v>
       </c>
       <c r="E51">
         <v>1039.518</v>
@@ -5463,45 +5463,45 @@
         <v>1034.9</v>
       </c>
       <c r="M51">
-        <v>381.8035333106166</v>
+        <v>340.7334875106166</v>
       </c>
       <c r="N51">
-        <v>653.0964666893835</v>
+        <v>694.1665124893834</v>
       </c>
       <c r="O51">
-        <v>163.2741166723459</v>
+        <v>173.5416281223459</v>
       </c>
       <c r="P51">
-        <v>489.8223500170376</v>
+        <v>520.6248843670376</v>
       </c>
       <c r="Q51">
-        <v>1363.422350017038</v>
+        <v>1394.224884367037</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1405835674870341</v>
+        <v>0.1405847808396324</v>
       </c>
       <c r="T51">
         <v>0.9166412730585703</v>
       </c>
       <c r="U51">
-        <v>0.1217828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.09133712031986115</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.710556371823977</v>
+        <v>3.0372711750786</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1167704598648753</v>
+        <v>0.1147835769117095</v>
       </c>
       <c r="C52">
-        <v>2444.086656131982</v>
+        <v>2599.86352270811</v>
       </c>
       <c r="D52">
-        <v>5406.486656131982</v>
+        <v>5562.263522708111</v>
       </c>
       <c r="E52">
         <v>1103.5</v>
@@ -5545,37 +5545,37 @@
         <v>1034.9</v>
       </c>
       <c r="M52">
-        <v>389.5954421536904</v>
+        <v>372.6402121536904</v>
       </c>
       <c r="N52">
-        <v>645.3045578463096</v>
+        <v>662.2597878463097</v>
       </c>
       <c r="O52">
-        <v>161.3261394615774</v>
+        <v>165.5649469615774</v>
       </c>
       <c r="P52">
-        <v>483.9784183847322</v>
+        <v>496.6948408847322</v>
       </c>
       <c r="Q52">
-        <v>1357.578418384732</v>
+        <v>1370.294840884732</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1422037994098894</v>
+        <v>0.1422050335035578</v>
       </c>
       <c r="T52">
         <v>0.9323103546493152</v>
       </c>
       <c r="U52">
-        <v>0.1217828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.09133712031986115</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.656345244387498</v>
+        <v>2.777209668325247</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1170881113546312</v>
+        <v>0.1150614766384744</v>
       </c>
       <c r="C53">
-        <v>2356.013983675779</v>
+        <v>2513.563899865276</v>
       </c>
       <c r="D53">
-        <v>5382.395983675779</v>
+        <v>5539.945899865276</v>
       </c>
       <c r="E53">
         <v>1167.482</v>
@@ -5627,37 +5627,37 @@
         <v>1034.9</v>
       </c>
       <c r="M53">
-        <v>397.3873509967642</v>
+        <v>380.0930163967643</v>
       </c>
       <c r="N53">
-        <v>637.5126490032359</v>
+        <v>654.8069836032358</v>
       </c>
       <c r="O53">
-        <v>159.378162250809</v>
+        <v>163.701745900809</v>
       </c>
       <c r="P53">
-        <v>478.1344867524269</v>
+        <v>491.1052377024268</v>
       </c>
       <c r="Q53">
-        <v>1351.734486752427</v>
+        <v>1364.705237702427</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1438901632479632</v>
+        <v>0.143891418929276</v>
       </c>
       <c r="T53">
         <v>0.9486189905907026</v>
       </c>
       <c r="U53">
-        <v>0.1217828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.09133712031986115</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.604260043517155</v>
+        <v>2.722754576789457</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1174057628443871</v>
+        <v>0.1153393763652394</v>
       </c>
       <c r="C54">
-        <v>2268.155049267771</v>
+        <v>2427.442652544748</v>
       </c>
       <c r="D54">
-        <v>5358.519049267771</v>
+        <v>5517.806652544748</v>
       </c>
       <c r="E54">
         <v>1231.464</v>
@@ -5709,37 +5709,37 @@
         <v>1034.9</v>
       </c>
       <c r="M54">
-        <v>405.179259839838</v>
+        <v>387.545820639838</v>
       </c>
       <c r="N54">
-        <v>629.720740160162</v>
+        <v>647.3541793601621</v>
       </c>
       <c r="O54">
-        <v>157.4301850400405</v>
+        <v>161.8385448400405</v>
       </c>
       <c r="P54">
-        <v>472.2905551201215</v>
+        <v>485.5156345201216</v>
       </c>
       <c r="Q54">
-        <v>1345.890555120121</v>
+        <v>1359.115634520122</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1456467922459569</v>
+        <v>0.1456480704143991</v>
       </c>
       <c r="T54">
         <v>0.9656071530296478</v>
       </c>
       <c r="U54">
-        <v>0.1217828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.09133712031986115</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.554178119603363</v>
+        <v>2.670393911851199</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.117723414334143</v>
+        <v>0.1156172760920043</v>
       </c>
       <c r="C55">
-        <v>2180.507020970259</v>
+        <v>2341.497650736094</v>
       </c>
       <c r="D55">
-        <v>5334.853020970259</v>
+        <v>5495.843650736095</v>
       </c>
       <c r="E55">
         <v>1295.446000000001</v>
@@ -5791,37 +5791,37 @@
         <v>1034.9</v>
       </c>
       <c r="M55">
-        <v>412.9711686829119</v>
+        <v>394.9986248829119</v>
       </c>
       <c r="N55">
-        <v>621.9288313170882</v>
+        <v>639.9013751170883</v>
       </c>
       <c r="O55">
-        <v>155.4822078292721</v>
+        <v>159.9753437792721</v>
       </c>
       <c r="P55">
-        <v>466.4466234878162</v>
+        <v>479.9260313378162</v>
       </c>
       <c r="Q55">
-        <v>1340.046623487816</v>
+        <v>1353.526031337816</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1474781714140779</v>
+        <v>0.1474794730265488</v>
       </c>
       <c r="T55">
         <v>0.98331821599791</v>
       </c>
       <c r="U55">
-        <v>0.1217828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.09133712031986115</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.505986079610847</v>
+        <v>2.620009121061553</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1199445658238989</v>
+        <v>0.1158951758187693</v>
       </c>
       <c r="C56">
-        <v>1956.708632493446</v>
+        <v>2255.72679820748</v>
       </c>
       <c r="D56">
-        <v>5175.036632493447</v>
+        <v>5474.05479820748</v>
       </c>
       <c r="E56">
         <v>1359.428000000001</v>
@@ -5873,45 +5873,45 @@
         <v>1034.9</v>
       </c>
       <c r="M56">
-        <v>437.0017091259857</v>
+        <v>402.4514291259857</v>
       </c>
       <c r="N56">
-        <v>597.8982908740144</v>
+        <v>632.4485708740144</v>
       </c>
       <c r="O56">
-        <v>149.4745727185036</v>
+        <v>158.1121427185036</v>
       </c>
       <c r="P56">
-        <v>448.4237181555108</v>
+        <v>474.3364281555108</v>
       </c>
       <c r="Q56">
-        <v>1322.023718155511</v>
+        <v>1347.936428155511</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1493891757634215</v>
+        <v>0.1493905018392267</v>
       </c>
       <c r="T56">
         <v>1.001799325182184</v>
       </c>
       <c r="U56">
-        <v>0.1264828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.09486212031986116</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.3681829576132</v>
+        <v>2.571490433634487</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1202974673136548</v>
+        <v>0.1161730755455343</v>
       </c>
       <c r="C57">
-        <v>1868.211998600467</v>
+        <v>2170.128031838728</v>
       </c>
       <c r="D57">
-        <v>5150.521998600468</v>
+        <v>5452.438031838728</v>
       </c>
       <c r="E57">
         <v>1423.410000000001</v>
@@ -5955,45 +5955,45 @@
         <v>1034.9</v>
       </c>
       <c r="M57">
-        <v>445.0943333690595</v>
+        <v>409.9042333690595</v>
       </c>
       <c r="N57">
-        <v>589.8056666309406</v>
+        <v>624.9957666309406</v>
       </c>
       <c r="O57">
-        <v>147.4514166577351</v>
+        <v>156.2489416577351</v>
       </c>
       <c r="P57">
-        <v>442.3542499732054</v>
+        <v>468.7468249732054</v>
       </c>
       <c r="Q57">
-        <v>1315.954249973205</v>
+        <v>1342.346824973205</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1513851136394027</v>
+        <v>0.1513864652658014</v>
       </c>
       <c r="T57">
         <v>1.021101816996869</v>
       </c>
       <c r="U57">
-        <v>0.1264828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.09486212031986116</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.325125085656596</v>
+        <v>2.52473606211386</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1206503688034107</v>
+        <v>0.1180889752722992</v>
       </c>
       <c r="C58">
-        <v>1779.946525915109</v>
+        <v>1961.638179900681</v>
       </c>
       <c r="D58">
-        <v>5126.23852591511</v>
+        <v>5307.930179900682</v>
       </c>
       <c r="E58">
         <v>1487.392000000001</v>
@@ -6037,37 +6037,37 @@
         <v>1034.9</v>
       </c>
       <c r="M58">
-        <v>453.1869576121334</v>
+        <v>431.3307064121333</v>
       </c>
       <c r="N58">
-        <v>581.7130423878667</v>
+        <v>603.5692935878667</v>
       </c>
       <c r="O58">
-        <v>145.4282605969667</v>
+        <v>150.8923233969667</v>
       </c>
       <c r="P58">
-        <v>436.2847817909001</v>
+        <v>452.6769701909</v>
       </c>
       <c r="Q58">
-        <v>1309.8847817909</v>
+        <v>1326.2769701909</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.153471775964292</v>
+        <v>0.1534731543026749</v>
       </c>
       <c r="T58">
         <v>1.041281694803131</v>
       </c>
       <c r="U58">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.2836049948413</v>
+        <v>2.399319094641875</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1210032702931667</v>
+        <v>0.1183961249990642</v>
       </c>
       <c r="C59">
-        <v>1691.908960171926</v>
+        <v>1875.198654730224</v>
       </c>
       <c r="D59">
-        <v>5102.182960171926</v>
+        <v>5285.472654730225</v>
       </c>
       <c r="E59">
         <v>1551.374000000001</v>
@@ -6119,37 +6119,37 @@
         <v>1034.9</v>
       </c>
       <c r="M59">
-        <v>461.2795818552071</v>
+        <v>439.0330404552072</v>
       </c>
       <c r="N59">
-        <v>573.6204181447929</v>
+        <v>595.866959544793</v>
       </c>
       <c r="O59">
-        <v>143.4051045361982</v>
+        <v>148.9667398861982</v>
       </c>
       <c r="P59">
-        <v>430.2153136085947</v>
+        <v>446.9002196585947</v>
       </c>
       <c r="Q59">
-        <v>1303.815313608595</v>
+        <v>1320.500219658595</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1556554923508042</v>
+        <v>0.1556568986435891</v>
       </c>
       <c r="T59">
         <v>1.062400171577127</v>
       </c>
       <c r="U59">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.243541749317768</v>
+        <v>2.357225777192017</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1213561717829226</v>
+        <v>0.1187032747258291</v>
       </c>
       <c r="C60">
-        <v>1604.096107904489</v>
+        <v>1788.948361737499</v>
       </c>
       <c r="D60">
-        <v>5078.352107904489</v>
+        <v>5263.204361737499</v>
       </c>
       <c r="E60">
         <v>1615.356</v>
@@ -6201,37 +6201,37 @@
         <v>1034.9</v>
       </c>
       <c r="M60">
-        <v>469.3722060982809</v>
+        <v>446.7353744982809</v>
       </c>
       <c r="N60">
-        <v>565.5277939017192</v>
+        <v>588.1646255017192</v>
       </c>
       <c r="O60">
-        <v>141.3819484754298</v>
+        <v>147.0411563754298</v>
       </c>
       <c r="P60">
-        <v>424.1458454262894</v>
+        <v>441.1234691262894</v>
       </c>
       <c r="Q60">
-        <v>1297.745845426289</v>
+        <v>1314.723469126289</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1579431952319121</v>
+        <v>0.1579446308102611</v>
       </c>
       <c r="T60">
         <v>1.084524290102264</v>
       </c>
       <c r="U60">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.204859995019186</v>
+        <v>2.316583953447328</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1217090732726785</v>
+        <v>0.1190104244525941</v>
       </c>
       <c r="C61">
-        <v>1516.504835032103</v>
+        <v>1702.884919187434</v>
       </c>
       <c r="D61">
-        <v>5054.742835032103</v>
+        <v>5241.122919187434</v>
       </c>
       <c r="E61">
         <v>1679.338</v>
@@ -6283,37 +6283,37 @@
         <v>1034.9</v>
       </c>
       <c r="M61">
-        <v>477.4648303413547</v>
+        <v>454.4377085413547</v>
       </c>
       <c r="N61">
-        <v>557.4351696586455</v>
+        <v>580.4622914586454</v>
       </c>
       <c r="O61">
-        <v>139.3587924146614</v>
+        <v>145.1155728646613</v>
       </c>
       <c r="P61">
-        <v>418.0763772439841</v>
+        <v>435.3467185939841</v>
       </c>
       <c r="Q61">
-        <v>1291.676377243984</v>
+        <v>1308.946718593984</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1603424933755132</v>
+        <v>0.1603439596679902</v>
       </c>
       <c r="T61">
         <v>1.107727633921312</v>
       </c>
       <c r="U61">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.167489486629031</v>
+        <v>2.277319818643136</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1220619747624344</v>
+        <v>0.119317574179359</v>
       </c>
       <c r="C62">
-        <v>1429.132065485777</v>
+        <v>1617.005985147654</v>
       </c>
       <c r="D62">
-        <v>5031.352065485778</v>
+        <v>5219.225985147655</v>
       </c>
       <c r="E62">
         <v>1743.32</v>
@@ -6365,37 +6365,37 @@
         <v>1034.9</v>
       </c>
       <c r="M62">
-        <v>485.5574545844285</v>
+        <v>462.1400425844286</v>
       </c>
       <c r="N62">
-        <v>549.3425454155715</v>
+        <v>572.7599574155715</v>
       </c>
       <c r="O62">
-        <v>137.3356363538929</v>
+        <v>143.1899893538929</v>
       </c>
       <c r="P62">
-        <v>412.0069090616786</v>
+        <v>429.5699680616787</v>
       </c>
       <c r="Q62">
-        <v>1285.606909061679</v>
+        <v>1303.169968061678</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1628617564262943</v>
+        <v>0.1628632549686058</v>
       </c>
       <c r="T62">
         <v>1.132091144931311</v>
       </c>
       <c r="U62">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.13136466185188</v>
+        <v>2.239364488332416</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1224148762521903</v>
+        <v>0.119624723906124</v>
       </c>
       <c r="C63">
-        <v>1341.974779872161</v>
+        <v>1531.309256660471</v>
       </c>
       <c r="D63">
-        <v>5008.176779872161</v>
+        <v>5197.511256660472</v>
       </c>
       <c r="E63">
         <v>1807.302000000001</v>
@@ -6447,37 +6447,37 @@
         <v>1034.9</v>
       </c>
       <c r="M63">
-        <v>493.6500788275024</v>
+        <v>469.8423766275024</v>
       </c>
       <c r="N63">
-        <v>541.2499211724977</v>
+        <v>565.0576233724977</v>
       </c>
       <c r="O63">
-        <v>135.3124802931244</v>
+        <v>141.2644058431244</v>
       </c>
       <c r="P63">
-        <v>405.9374408793733</v>
+        <v>423.7932175293732</v>
       </c>
       <c r="Q63">
-        <v>1279.537440879373</v>
+        <v>1297.393217529373</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1655102124540385</v>
+        <v>0.1655117449000223</v>
       </c>
       <c r="T63">
         <v>1.157704066762337</v>
       </c>
       <c r="U63">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.096424257559226</v>
+        <v>2.202653595081065</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1227677777419462</v>
+        <v>0.119931873632889</v>
       </c>
       <c r="C64">
-        <v>1255.030014174241</v>
+        <v>1445.792468935468</v>
       </c>
       <c r="D64">
-        <v>4985.214014174242</v>
+        <v>5175.976468935469</v>
       </c>
       <c r="E64">
         <v>1871.284000000001</v>
@@ -6529,37 +6529,37 @@
         <v>1034.9</v>
       </c>
       <c r="M64">
-        <v>501.7427030705762</v>
+        <v>477.5447106705762</v>
       </c>
       <c r="N64">
-        <v>533.1572969294239</v>
+        <v>557.3552893294238</v>
       </c>
       <c r="O64">
-        <v>133.289324232356</v>
+        <v>139.338822332356</v>
       </c>
       <c r="P64">
-        <v>399.8679726970679</v>
+        <v>418.0164669970679</v>
       </c>
       <c r="Q64">
-        <v>1273.467972697068</v>
+        <v>1291.616466997068</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1682980609042956</v>
+        <v>0.1682996290383554</v>
       </c>
       <c r="T64">
         <v>1.184665037110784</v>
       </c>
       <c r="U64">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.062610963082464</v>
+        <v>2.167126924192661</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1231206792317021</v>
+        <v>0.1202390233596539</v>
       </c>
       <c r="C65">
-        <v>1168.29485848762</v>
+        <v>1360.453394562068</v>
       </c>
       <c r="D65">
-        <v>4962.46085848762</v>
+        <v>5154.619394562069</v>
       </c>
       <c r="E65">
         <v>1935.266000000001</v>
@@ -6611,37 +6611,37 @@
         <v>1034.9</v>
       </c>
       <c r="M65">
-        <v>509.83532731365</v>
+        <v>485.24704471365</v>
       </c>
       <c r="N65">
-        <v>525.0646726863501</v>
+        <v>549.6529552863501</v>
       </c>
       <c r="O65">
-        <v>131.2661681715875</v>
+        <v>137.4132388215875</v>
       </c>
       <c r="P65">
-        <v>393.7985045147626</v>
+        <v>412.2397164647626</v>
       </c>
       <c r="Q65">
-        <v>1267.398504514762</v>
+        <v>1285.839716464762</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1712366038653773</v>
+        <v>0.1712382096165984</v>
       </c>
       <c r="T65">
         <v>1.213083357207796</v>
       </c>
       <c r="U65">
-        <v>0.1264828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.09486212031986116</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.0298711065256</v>
+        <v>2.132728084126111</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.131297580721458</v>
+        <v>0.1205461730864189</v>
       </c>
       <c r="C66">
-        <v>629.7081592175905</v>
+        <v>1275.289842741527</v>
       </c>
       <c r="D66">
-        <v>4487.856159217591</v>
+        <v>5133.437842741528</v>
       </c>
       <c r="E66">
         <v>1999.248000000001</v>
@@ -6693,45 +6693,45 @@
         <v>1034.9</v>
       </c>
       <c r="M66">
-        <v>584.6739739567238</v>
+        <v>492.9493787567238</v>
       </c>
       <c r="N66">
-        <v>450.2260260432763</v>
+        <v>541.9506212432763</v>
       </c>
       <c r="O66">
-        <v>112.5565065108191</v>
+        <v>135.4876553108191</v>
       </c>
       <c r="P66">
-        <v>337.6695195324572</v>
+        <v>406.4629659324572</v>
       </c>
       <c r="Q66">
-        <v>1211.269519532457</v>
+        <v>1280.062965932457</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1743383992131859</v>
+        <v>0.1743400446714104</v>
       </c>
       <c r="T66">
         <v>1.243080472865754</v>
       </c>
       <c r="U66">
-        <v>0.1427828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.1070871203198612</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.770046292631115</v>
+        <v>2.099404207811641</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.131772732211214</v>
+        <v>0.1208533228131838</v>
       </c>
       <c r="C67">
-        <v>540.92281186527</v>
+        <v>1190.299658537776</v>
       </c>
       <c r="D67">
-        <v>4463.052811865271</v>
+        <v>5112.429658537777</v>
       </c>
       <c r="E67">
         <v>2063.230000000001</v>
@@ -6775,45 +6775,45 @@
         <v>1034.9</v>
       </c>
       <c r="M67">
-        <v>593.8095047997977</v>
+        <v>500.6517127997977</v>
       </c>
       <c r="N67">
-        <v>441.0904952002024</v>
+        <v>534.2482872002024</v>
       </c>
       <c r="O67">
-        <v>110.2726238000506</v>
+        <v>133.5620718000506</v>
       </c>
       <c r="P67">
-        <v>330.8178714001518</v>
+        <v>400.6862154001518</v>
       </c>
       <c r="Q67">
-        <v>1204.417871400152</v>
+        <v>1274.286215400152</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1776174400094406</v>
+        <v>0.1776191274436402</v>
       </c>
       <c r="T67">
         <v>1.274791709418452</v>
       </c>
       <c r="U67">
-        <v>0.1427828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.1070871203198612</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.742814811206021</v>
+        <v>2.067105681537615</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1322478837009699</v>
+        <v>0.1211604725399488</v>
       </c>
       <c r="C68">
-        <v>452.4101223720199</v>
+        <v>1105.480722146586</v>
       </c>
       <c r="D68">
-        <v>4438.522122372021</v>
+        <v>5091.592722146587</v>
       </c>
       <c r="E68">
         <v>2127.212000000001</v>
@@ -6857,45 +6857,45 @@
         <v>1034.9</v>
       </c>
       <c r="M68">
-        <v>602.9450356428715</v>
+        <v>508.3540468428715</v>
       </c>
       <c r="N68">
-        <v>431.9549643571286</v>
+        <v>526.5459531571287</v>
       </c>
       <c r="O68">
-        <v>107.9887410892821</v>
+        <v>131.6364882892822</v>
       </c>
       <c r="P68">
-        <v>323.9662232678464</v>
+        <v>394.9094648678465</v>
       </c>
       <c r="Q68">
-        <v>1197.566223267846</v>
+        <v>1268.509464867846</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1810893655584162</v>
+        <v>0.1810910974377659</v>
       </c>
       <c r="T68">
         <v>1.30836831282719</v>
       </c>
       <c r="U68">
-        <v>0.1427828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.1070871203198612</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.716408526187748</v>
+        <v>2.035785898484015</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1327230351907258</v>
+        <v>0.1214676222667138</v>
       </c>
       <c r="C69">
-        <v>364.165619410267</v>
+        <v>1020.830948182532</v>
       </c>
       <c r="D69">
-        <v>4414.259619410268</v>
+        <v>5070.924948182533</v>
       </c>
       <c r="E69">
         <v>2191.194000000001</v>
@@ -6939,45 +6939,45 @@
         <v>1034.9</v>
       </c>
       <c r="M69">
-        <v>612.0805664859453</v>
+        <v>516.0563808859453</v>
       </c>
       <c r="N69">
-        <v>422.8194335140548</v>
+        <v>518.8436191140548</v>
       </c>
       <c r="O69">
-        <v>105.7048583785137</v>
+        <v>129.7109047785137</v>
       </c>
       <c r="P69">
-        <v>317.1145751355411</v>
+        <v>389.1327143355411</v>
       </c>
       <c r="Q69">
-        <v>1190.714575135541</v>
+        <v>1262.732714335541</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1847717108376328</v>
+        <v>0.1847734898557781</v>
       </c>
       <c r="T69">
         <v>1.343979861897065</v>
       </c>
       <c r="U69">
-        <v>0.1427828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.1070871203198612</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.690790488483453</v>
+        <v>2.005401034327537</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1331981866804817</v>
+        <v>0.1290167719934787</v>
       </c>
       <c r="C70">
-        <v>276.1849288882286</v>
+        <v>496.8314448597921</v>
       </c>
       <c r="D70">
-        <v>4390.26092888823</v>
+        <v>4610.907444859793</v>
       </c>
       <c r="E70">
         <v>2255.176000000001</v>
@@ -7021,37 +7021,37 @@
         <v>1034.9</v>
       </c>
       <c r="M70">
-        <v>621.2160973290191</v>
+        <v>585.5397341290191</v>
       </c>
       <c r="N70">
-        <v>413.683902670981</v>
+        <v>449.360265870981</v>
       </c>
       <c r="O70">
-        <v>103.4209756677452</v>
+        <v>112.3400664677453</v>
       </c>
       <c r="P70">
-        <v>310.2629270032357</v>
+        <v>337.0201994032358</v>
       </c>
       <c r="Q70">
-        <v>1183.862927003236</v>
+        <v>1210.620199403236</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1886842026968004</v>
+        <v>0.188686031799916</v>
       </c>
       <c r="T70">
         <v>1.381817132783807</v>
       </c>
       <c r="U70">
-        <v>0.1427828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.1070871203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.665925922476343</v>
+        <v>1.767429159251502</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1336733381702376</v>
+        <v>0.1294304217202437</v>
       </c>
       <c r="C71">
-        <v>188.4637713210368</v>
+        <v>410.0431434509001</v>
       </c>
       <c r="D71">
-        <v>4366.521771321038</v>
+        <v>4588.101143450901</v>
       </c>
       <c r="E71">
         <v>2319.158000000001</v>
@@ -7103,37 +7103,37 @@
         <v>1034.9</v>
       </c>
       <c r="M71">
-        <v>630.3516281720929</v>
+        <v>594.1506125720929</v>
       </c>
       <c r="N71">
-        <v>404.5483718279072</v>
+        <v>440.7493874279072</v>
       </c>
       <c r="O71">
-        <v>101.1370929569768</v>
+        <v>110.1873468569768</v>
       </c>
       <c r="P71">
-        <v>303.4112788709304</v>
+        <v>330.5620405709304</v>
       </c>
       <c r="Q71">
-        <v>1177.01127887093</v>
+        <v>1204.16204057093</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1928491133855917</v>
+        <v>0.192850995804966</v>
       </c>
       <c r="T71">
         <v>1.422095517921306</v>
       </c>
       <c r="U71">
-        <v>0.1427828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.1070871203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.641782068527411</v>
+        <v>1.741814243900031</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1341484896599935</v>
+        <v>0.1298440714470086</v>
       </c>
       <c r="C72">
-        <v>100.9979592866775</v>
+        <v>323.4793390275499</v>
       </c>
       <c r="D72">
-        <v>4343.037959286678</v>
+        <v>4565.519339027551</v>
       </c>
       <c r="E72">
         <v>2383.140000000001</v>
@@ -7185,37 +7185,37 @@
         <v>1034.9</v>
       </c>
       <c r="M72">
-        <v>639.4871590151668</v>
+        <v>602.7614910151667</v>
       </c>
       <c r="N72">
-        <v>395.4128409848333</v>
+        <v>432.1385089848334</v>
       </c>
       <c r="O72">
-        <v>98.85321024620833</v>
+        <v>108.0346272462083</v>
       </c>
       <c r="P72">
-        <v>296.559630738625</v>
+        <v>324.103881738625</v>
       </c>
       <c r="Q72">
-        <v>1170.159630738625</v>
+        <v>1197.703881738625</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1972916847869691</v>
+        <v>0.1972936240770194</v>
       </c>
       <c r="T72">
         <v>1.465059128734638</v>
       </c>
       <c r="U72">
-        <v>0.1427828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.1070871203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.618328038977019</v>
+        <v>1.716931183272887</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1346236411497495</v>
+        <v>0.1302577211737736</v>
       </c>
       <c r="C73">
-        <v>13.78339496359968</v>
+        <v>237.1367330239473</v>
       </c>
       <c r="D73">
-        <v>4319.805394963601</v>
+        <v>4543.158733023948</v>
       </c>
       <c r="E73">
         <v>2447.122000000001</v>
@@ -7267,37 +7267,37 @@
         <v>1034.9</v>
       </c>
       <c r="M73">
-        <v>648.6226898582405</v>
+        <v>611.3723694582404</v>
       </c>
       <c r="N73">
-        <v>386.2773101417596</v>
+        <v>423.5276305417597</v>
       </c>
       <c r="O73">
-        <v>96.5693275354399</v>
+        <v>105.8819076354399</v>
       </c>
       <c r="P73">
-        <v>289.7079826063197</v>
+        <v>317.6457229063197</v>
       </c>
       <c r="Q73">
-        <v>1163.307982606319</v>
+        <v>1191.24572290632</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2020406404229242</v>
+        <v>0.202042640505766</v>
       </c>
       <c r="T73">
         <v>1.510985747190269</v>
       </c>
       <c r="U73">
-        <v>0.1427828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.1070871203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.595534686315371</v>
+        <v>1.692749053931016</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1350987926395054</v>
+        <v>0.1306713709005385</v>
       </c>
       <c r="C74">
-        <v>-73.18393225306954</v>
+        <v>151.0120911810618</v>
       </c>
       <c r="D74">
-        <v>4296.820067746931</v>
+        <v>4521.016091181063</v>
       </c>
       <c r="E74">
         <v>2511.104000000001</v>
@@ -7349,37 +7349,37 @@
         <v>1034.9</v>
       </c>
       <c r="M74">
-        <v>657.7582207013144</v>
+        <v>619.9832479013143</v>
       </c>
       <c r="N74">
-        <v>377.1417792986857</v>
+        <v>414.9167520986858</v>
       </c>
       <c r="O74">
-        <v>94.28544482467143</v>
+        <v>103.7291880246715</v>
       </c>
       <c r="P74">
-        <v>282.8563344740143</v>
+        <v>311.1875640740144</v>
       </c>
       <c r="Q74">
-        <v>1156.456334474014</v>
+        <v>1184.787564074014</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2071288071757333</v>
+        <v>0.2071308723937089</v>
       </c>
       <c r="T74">
         <v>1.560192838392731</v>
       </c>
       <c r="U74">
-        <v>0.1427828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.1070871203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.573374482338769</v>
+        <v>1.669238650404196</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1355739441292613</v>
+        <v>0.1310850206273035</v>
       </c>
       <c r="C75">
-        <v>-159.9079480596092</v>
+        <v>65.10224198712967</v>
       </c>
       <c r="D75">
-        <v>4274.078051940392</v>
+        <v>4499.08824198713</v>
       </c>
       <c r="E75">
         <v>2575.086000000001</v>
@@ -7431,37 +7431,37 @@
         <v>1034.9</v>
       </c>
       <c r="M75">
-        <v>666.8937515443881</v>
+        <v>628.5941263443881</v>
       </c>
       <c r="N75">
-        <v>368.006248455612</v>
+        <v>406.305873655612</v>
       </c>
       <c r="O75">
-        <v>92.00156211390299</v>
+        <v>101.576468413903</v>
       </c>
       <c r="P75">
-        <v>276.004686341709</v>
+        <v>304.729405241709</v>
       </c>
       <c r="Q75">
-        <v>1149.604686341709</v>
+        <v>1178.329405241709</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2125938751694912</v>
+        <v>0.2125960103474253</v>
       </c>
       <c r="T75">
         <v>1.613044899313894</v>
       </c>
       <c r="U75">
-        <v>0.1427828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.1070871203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.551821407238238</v>
+        <v>1.646372367521947</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1360490956190172</v>
+        <v>0.1314986703540684</v>
       </c>
       <c r="C76">
-        <v>-246.3924954788718</v>
+        <v>-20.59592483669985</v>
       </c>
       <c r="D76">
-        <v>4251.575504521129</v>
+        <v>4477.372075163301</v>
       </c>
       <c r="E76">
         <v>2639.068000000001</v>
@@ -7513,37 +7513,37 @@
         <v>1034.9</v>
       </c>
       <c r="M76">
-        <v>676.029282387462</v>
+        <v>637.2050047874619</v>
       </c>
       <c r="N76">
-        <v>358.8707176125381</v>
+        <v>397.6949952125382</v>
       </c>
       <c r="O76">
-        <v>89.71767940313453</v>
+        <v>99.42374880313454</v>
       </c>
       <c r="P76">
-        <v>269.1530382094036</v>
+        <v>298.2712464094036</v>
       </c>
       <c r="Q76">
-        <v>1142.753038209403</v>
+        <v>1171.871246409404</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2184793330089227</v>
+        <v>0.2184815435283507</v>
       </c>
       <c r="T76">
         <v>1.669962503382839</v>
       </c>
       <c r="U76">
-        <v>0.1427828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.1070871203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.530850847680964</v>
+        <v>1.624124092285164</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1365242471087731</v>
+        <v>0.1319123200808334</v>
       </c>
       <c r="C77">
-        <v>-332.6413370252221</v>
+        <v>-106.08545980705</v>
       </c>
       <c r="D77">
-        <v>4229.308662974779</v>
+        <v>4455.864540192951</v>
       </c>
       <c r="E77">
         <v>2703.050000000001</v>
@@ -7595,37 +7595,37 @@
         <v>1034.9</v>
       </c>
       <c r="M77">
-        <v>685.1648132305357</v>
+        <v>645.8158832305356</v>
       </c>
       <c r="N77">
-        <v>349.7351867694643</v>
+        <v>389.0841167694645</v>
       </c>
       <c r="O77">
-        <v>87.43379669236609</v>
+        <v>97.27102919236611</v>
       </c>
       <c r="P77">
-        <v>262.3013900770983</v>
+        <v>291.8130875770984</v>
       </c>
       <c r="Q77">
-        <v>1135.901390077098</v>
+        <v>1165.413087577098</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2248356274755089</v>
+        <v>0.2248379193637501</v>
       </c>
       <c r="T77">
         <v>1.7314335157773</v>
       </c>
       <c r="U77">
-        <v>0.1427828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.1070871203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.510439503045218</v>
+        <v>1.602469104388029</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.174277398598529</v>
+        <v>0.1323259698075984</v>
       </c>
       <c r="C78">
-        <v>-1639.407923201082</v>
+        <v>-191.3693551068191</v>
       </c>
       <c r="D78">
-        <v>2986.524076798919</v>
+        <v>4434.562644893182</v>
       </c>
       <c r="E78">
         <v>2767.032000000001</v>
@@ -7677,45 +7677,45 @@
         <v>1034.9</v>
       </c>
       <c r="M78">
-        <v>1012.31647687361</v>
+        <v>654.4267616736095</v>
       </c>
       <c r="N78">
-        <v>22.58352312639056</v>
+        <v>380.4732383263906</v>
       </c>
       <c r="O78">
-        <v>5.64588078159764</v>
+        <v>95.11830958159766</v>
       </c>
       <c r="P78">
-        <v>16.93764234479292</v>
+        <v>285.354928744793</v>
       </c>
       <c r="Q78">
-        <v>890.5376423447929</v>
+        <v>1158.954928744793</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2317216131476438</v>
+        <v>0.2317239931854328</v>
       </c>
       <c r="T78">
         <v>1.798027112537965</v>
       </c>
       <c r="U78">
-        <v>0.2081828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.1561371203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.022308757826541</v>
+        <v>1.581383984593449</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1752430500882849</v>
+        <v>0.1327396195343633</v>
       </c>
       <c r="C79">
-        <v>-1725.669539001125</v>
+        <v>-276.4505459729244</v>
       </c>
       <c r="D79">
-        <v>2964.244460998876</v>
+        <v>4413.463454027076</v>
       </c>
       <c r="E79">
         <v>2831.014000000001</v>
@@ -7759,45 +7759,45 @@
         <v>1034.9</v>
       </c>
       <c r="M79">
-        <v>1025.636430516683</v>
+        <v>663.0376401166833</v>
       </c>
       <c r="N79">
-        <v>9.263569483316815</v>
+        <v>371.8623598833168</v>
       </c>
       <c r="O79">
-        <v>2.315892370829204</v>
+        <v>92.9655899708292</v>
       </c>
       <c r="P79">
-        <v>6.947677112487611</v>
+        <v>278.8967699124876</v>
       </c>
       <c r="Q79">
-        <v>880.5476771124875</v>
+        <v>1152.496769912487</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2392063801825731</v>
+        <v>0.2392088560350879</v>
       </c>
       <c r="T79">
         <v>1.870411456843036</v>
       </c>
       <c r="U79">
-        <v>0.2081828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.1561371203198612</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.009032020711911</v>
+        <v>1.56084653024808</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1764091390526013</v>
+        <v>0.1331532692611283</v>
       </c>
       <c r="C80">
-        <v>-1816.116553460142</v>
+        <v>-361.331912044594</v>
       </c>
       <c r="D80">
-        <v>2937.779446539859</v>
+        <v>4392.564087955407</v>
       </c>
       <c r="E80">
         <v>2894.996000000001</v>
@@ -7841,45 +7841,45 @@
         <v>1034.9</v>
       </c>
       <c r="M80">
-        <v>1038.956384159757</v>
+        <v>671.6485185597571</v>
       </c>
       <c r="N80">
-        <v>-4.056384159757044</v>
+        <v>363.251481440243</v>
       </c>
       <c r="O80">
-        <v>-1.014096039939261</v>
+        <v>90.81287036006074</v>
       </c>
       <c r="P80">
-        <v>-3.042288119817783</v>
+        <v>272.4386110801822</v>
       </c>
       <c r="Q80">
-        <v>870.5577118801821</v>
+        <v>1146.038611080182</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2475622187252925</v>
+        <v>0.2473741609619844</v>
       </c>
       <c r="T80">
-        <v>1.95121983621025</v>
+        <v>1.949376196084932</v>
       </c>
       <c r="U80">
-        <v>0.2081828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V80">
-        <v>0.2490239281885164</v>
+        <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.1563403217090217</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.9960957127540656</v>
+        <v>1.540835677296181</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1780329673235328</v>
+        <v>0.1335669189878932</v>
       </c>
       <c r="C81">
-        <v>-1916.174650182535</v>
+        <v>-446.0162786735391</v>
       </c>
       <c r="D81">
-        <v>2901.703349817466</v>
+        <v>4371.861721326462</v>
       </c>
       <c r="E81">
         <v>2958.978000000001</v>
@@ -7923,45 +7923,45 @@
         <v>1034.9</v>
       </c>
       <c r="M81">
-        <v>1052.276337802831</v>
+        <v>680.259397002831</v>
       </c>
       <c r="N81">
-        <v>-17.3763378028309</v>
+        <v>354.6406029971691</v>
       </c>
       <c r="O81">
-        <v>-4.344084450707726</v>
+        <v>88.66015074929228</v>
       </c>
       <c r="P81">
-        <v>-13.03225335212318</v>
+        <v>265.9804522478769</v>
       </c>
       <c r="Q81">
-        <v>860.5677466478767</v>
+        <v>1139.580452247877</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2571699434264969</v>
+        <v>0.2563171139771568</v>
       </c>
       <c r="T81">
-        <v>2.044135066505976</v>
+        <v>2.035861386683199</v>
       </c>
       <c r="U81">
-        <v>0.2081828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V81">
-        <v>0.2458717265658769</v>
+        <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.1569965559543904</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.9834869062635078</v>
+        <v>1.521331428216483</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1796567955944643</v>
+        <v>0.1339805687146582</v>
       </c>
       <c r="C82">
-        <v>-2015.357462456314</v>
+        <v>-530.5064181972566</v>
       </c>
       <c r="D82">
-        <v>2866.502537543688</v>
+        <v>4351.353581802745</v>
       </c>
       <c r="E82">
         <v>3022.960000000001</v>
@@ -8005,45 +8005,45 @@
         <v>1034.9</v>
       </c>
       <c r="M82">
-        <v>1065.596291445905</v>
+        <v>688.8702754459048</v>
       </c>
       <c r="N82">
-        <v>-30.69629144590476</v>
+        <v>346.0297245540953</v>
       </c>
       <c r="O82">
-        <v>-7.674072861476191</v>
+        <v>86.50743113852383</v>
       </c>
       <c r="P82">
-        <v>-23.02221858442857</v>
+        <v>259.5222934155715</v>
       </c>
       <c r="Q82">
-        <v>850.5777814155713</v>
+        <v>1133.122293415571</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2677384405978218</v>
+        <v>0.2661543622938464</v>
       </c>
       <c r="T82">
-        <v>2.146341819831275</v>
+        <v>2.130995096341292</v>
       </c>
       <c r="U82">
-        <v>0.2081828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V82">
-        <v>0.2427983299838035</v>
+        <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.1576363843436249</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.9711933199352139</v>
+        <v>1.502314785363777</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1812806238653958</v>
+        <v>0.1689002184414232</v>
       </c>
       <c r="C83">
-        <v>-2113.696462936212</v>
+        <v>-1828.830199533411</v>
       </c>
       <c r="D83">
-        <v>2832.145537063789</v>
+        <v>3117.01180046659</v>
       </c>
       <c r="E83">
         <v>3086.942000000001</v>
@@ -8087,37 +8087,37 @@
         <v>1034.9</v>
       </c>
       <c r="M83">
-        <v>1078.916245088979</v>
+        <v>991.8495394889787</v>
       </c>
       <c r="N83">
-        <v>-44.01624508897862</v>
+        <v>43.05046051102136</v>
       </c>
       <c r="O83">
-        <v>-11.00406127224466</v>
+        <v>10.76261512775534</v>
       </c>
       <c r="P83">
-        <v>-33.01218381673397</v>
+        <v>32.28784538326602</v>
       </c>
       <c r="Q83">
-        <v>840.5878161832659</v>
+        <v>905.8878453832659</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2794194111556019</v>
+        <v>0.2770271104333454</v>
       </c>
       <c r="T83">
-        <v>2.259307178769764</v>
+        <v>2.236142880700238</v>
       </c>
       <c r="U83">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V83">
-        <v>0.2398008197370898</v>
+        <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.1582604145010264</v>
+        <v>0.1435371203198612</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9592032789483593</v>
+        <v>1.043404224932344</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1829044521363273</v>
+        <v>0.1697398681681881</v>
       </c>
       <c r="C84">
-        <v>-2211.221633262321</v>
+        <v>-1913.928876073951</v>
       </c>
       <c r="D84">
-        <v>2798.60236673768</v>
+        <v>3095.89512392605</v>
       </c>
       <c r="E84">
         <v>3150.924000000001</v>
@@ -8169,37 +8169,37 @@
         <v>1034.9</v>
       </c>
       <c r="M84">
-        <v>1092.236198732053</v>
+        <v>1004.094595532053</v>
       </c>
       <c r="N84">
-        <v>-57.33619873205248</v>
+        <v>30.80540446794748</v>
       </c>
       <c r="O84">
-        <v>-14.33404968301312</v>
+        <v>7.701351116986871</v>
       </c>
       <c r="P84">
-        <v>-43.00214904903936</v>
+        <v>23.10405335096061</v>
       </c>
       <c r="Q84">
-        <v>830.5978509509605</v>
+        <v>896.7040533509605</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2923982673309132</v>
+        <v>0.2891079416994553</v>
       </c>
       <c r="T84">
-        <v>2.384824244256973</v>
+        <v>2.352973752210177</v>
       </c>
       <c r="U84">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V84">
-        <v>0.2368764194963936</v>
+        <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.1588692244106865</v>
+        <v>0.1435371203198612</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9475056779855744</v>
+        <v>1.030679783164876</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1845282804072587</v>
+        <v>0.1705795178949531</v>
       </c>
       <c r="C85">
-        <v>-2307.961551322455</v>
+        <v>-1998.74336155515</v>
       </c>
       <c r="D85">
-        <v>2765.844448677547</v>
+        <v>3075.062638444851</v>
       </c>
       <c r="E85">
         <v>3214.906000000001</v>
@@ -8251,37 +8251,37 @@
         <v>1034.9</v>
       </c>
       <c r="M85">
-        <v>1105.556152375126</v>
+        <v>1016.339651575126</v>
       </c>
       <c r="N85">
-        <v>-70.65615237512634</v>
+        <v>18.56034842487372</v>
       </c>
       <c r="O85">
-        <v>-17.66403809378158</v>
+        <v>4.640087106218431</v>
       </c>
       <c r="P85">
-        <v>-52.99211428134475</v>
+        <v>13.92026131865529</v>
       </c>
       <c r="Q85">
-        <v>820.6078857186551</v>
+        <v>887.5202613186552</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3069040477621433</v>
+        <v>0.3026100472321666</v>
       </c>
       <c r="T85">
-        <v>2.525108023330912</v>
+        <v>2.483549432133051</v>
       </c>
       <c r="U85">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V85">
-        <v>0.2340224867313768</v>
+        <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.1594633642020414</v>
+        <v>0.1435371203198612</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9360899469255073</v>
+        <v>1.018261954452046</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1861521086781902</v>
+        <v>0.171419167621718</v>
       </c>
       <c r="C86">
-        <v>-2403.943472456944</v>
+        <v>-2083.27935465221</v>
       </c>
       <c r="D86">
-        <v>2733.844527543056</v>
+        <v>3054.508645347791</v>
       </c>
       <c r="E86">
         <v>3278.888</v>
@@ -8333,37 +8333,37 @@
         <v>1034.9</v>
       </c>
       <c r="M86">
-        <v>1118.8761060182</v>
+        <v>1028.5847076182</v>
       </c>
       <c r="N86">
-        <v>-83.97610601819974</v>
+        <v>6.315292381799964</v>
       </c>
       <c r="O86">
-        <v>-20.99402650454994</v>
+        <v>1.578823095449991</v>
       </c>
       <c r="P86">
-        <v>-62.98207951364981</v>
+        <v>4.736469286349973</v>
       </c>
       <c r="Q86">
-        <v>810.6179204863502</v>
+        <v>878.3364692863499</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3232230507472771</v>
+        <v>0.3177999159564665</v>
       </c>
       <c r="T86">
-        <v>2.682927274789093</v>
+        <v>2.630447072046282</v>
       </c>
       <c r="U86">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V86">
-        <v>0.2312365047464796</v>
+        <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.1600433578078879</v>
+        <v>0.1435371203198612</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9249460189859182</v>
+        <v>1.006139788327617</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1877759369491217</v>
+        <v>0.1725572066026605</v>
       </c>
       <c r="C87">
-        <v>-2499.193405090814</v>
+        <v>-2174.685041235397</v>
       </c>
       <c r="D87">
-        <v>2702.576594909186</v>
+        <v>3027.084958764604</v>
       </c>
       <c r="E87">
         <v>3342.87</v>
@@ -8415,37 +8415,37 @@
         <v>1034.9</v>
       </c>
       <c r="M87">
-        <v>1132.196059661274</v>
+        <v>1040.829763661274</v>
       </c>
       <c r="N87">
-        <v>-97.2960596612736</v>
+        <v>-5.929763661273682</v>
       </c>
       <c r="O87">
-        <v>-24.3240149153184</v>
+        <v>-1.482440915318421</v>
       </c>
       <c r="P87">
-        <v>-72.9720447459552</v>
+        <v>-4.447322745955262</v>
       </c>
       <c r="Q87">
-        <v>800.6279552540448</v>
+        <v>869.1526772540446</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3417179207970956</v>
+        <v>0.3354597184873546</v>
       </c>
       <c r="T87">
-        <v>2.861789093108366</v>
+        <v>2.801230859596146</v>
       </c>
       <c r="U87">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V87">
-        <v>0.2285160752788739</v>
+        <v>0.2485757124103526</v>
       </c>
       <c r="W87">
-        <v>0.1606097045053616</v>
+        <v>0.1438097045053616</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9140643011154956</v>
+        <v>0.9943028496414102</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1893997652200532</v>
+        <v>0.174013034873592</v>
       </c>
       <c r="C88">
-        <v>-2593.736181234468</v>
+        <v>-2273.038865175341</v>
       </c>
       <c r="D88">
-        <v>2672.015818765532</v>
+        <v>2992.713134824659</v>
       </c>
       <c r="E88">
         <v>3406.852</v>
@@ -8497,37 +8497,37 @@
         <v>1034.9</v>
       </c>
       <c r="M88">
-        <v>1145.516013304348</v>
+        <v>1053.074819704348</v>
       </c>
       <c r="N88">
-        <v>-110.6160133043475</v>
+        <v>-18.17481970434756</v>
       </c>
       <c r="O88">
-        <v>-27.65400332608687</v>
+        <v>-4.543704926086889</v>
       </c>
       <c r="P88">
-        <v>-82.9620099782606</v>
+        <v>-13.63111477826067</v>
       </c>
       <c r="Q88">
-        <v>790.6379900217394</v>
+        <v>859.9688852217392</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3628549151397454</v>
+        <v>0.3561496983793085</v>
       </c>
       <c r="T88">
-        <v>3.066202599758964</v>
+        <v>3.001318778138728</v>
       </c>
       <c r="U88">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V88">
-        <v>0.2258589116128405</v>
+        <v>0.2456852971497671</v>
       </c>
       <c r="W88">
-        <v>0.1611628803494056</v>
+        <v>0.1443628803494056</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9034356464513619</v>
+        <v>0.9827411885990682</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1910235934909847</v>
+        <v>0.1754688631445235</v>
       </c>
       <c r="C89">
-        <v>-2687.595522254521</v>
+        <v>-2370.620885124692</v>
       </c>
       <c r="D89">
-        <v>2642.13847774548</v>
+        <v>2959.113114875309</v>
       </c>
       <c r="E89">
         <v>3470.834</v>
@@ -8579,37 +8579,37 @@
         <v>1034.9</v>
       </c>
       <c r="M89">
-        <v>1158.835966947421</v>
+        <v>1065.319875747422</v>
       </c>
       <c r="N89">
-        <v>-123.9359669474213</v>
+        <v>-30.41987574742143</v>
       </c>
       <c r="O89">
-        <v>-30.98399173685533</v>
+        <v>-7.604968936855357</v>
       </c>
       <c r="P89">
-        <v>-92.95197521056599</v>
+        <v>-22.81490681056607</v>
       </c>
       <c r="Q89">
-        <v>780.648024789434</v>
+        <v>850.7850931894338</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3872437547658796</v>
+        <v>0.3800227521007938</v>
       </c>
       <c r="T89">
-        <v>3.302064338201961</v>
+        <v>3.232189453380169</v>
       </c>
       <c r="U89">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V89">
-        <v>0.2232628321690147</v>
+        <v>0.2428613282170111</v>
       </c>
       <c r="W89">
-        <v>0.1617033395073797</v>
+        <v>0.1449033395073797</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8930513286760589</v>
+        <v>0.9714453128680444</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1926474217619161</v>
+        <v>0.176924691415455</v>
       </c>
       <c r="C90">
-        <v>-2780.794100280896</v>
+        <v>-2467.456808234188</v>
       </c>
       <c r="D90">
-        <v>2612.921899719105</v>
+        <v>2926.259191765813</v>
       </c>
       <c r="E90">
         <v>3534.816000000001</v>
@@ -8661,37 +8661,37 @@
         <v>1034.9</v>
       </c>
       <c r="M90">
-        <v>1172.155920590495</v>
+        <v>1077.564931790495</v>
       </c>
       <c r="N90">
-        <v>-137.2559205904952</v>
+        <v>-42.6649317904953</v>
       </c>
       <c r="O90">
-        <v>-34.31398014762379</v>
+        <v>-10.66623294762383</v>
       </c>
       <c r="P90">
-        <v>-102.9419404428714</v>
+        <v>-31.99869884287148</v>
       </c>
       <c r="Q90">
-        <v>770.6580595571286</v>
+        <v>841.6013011571284</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4156974009963696</v>
+        <v>0.4078746481091934</v>
       </c>
       <c r="T90">
-        <v>3.577236366385458</v>
+        <v>3.501538574495184</v>
       </c>
       <c r="U90">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V90">
-        <v>0.2207257545307304</v>
+        <v>0.2401015403963632</v>
       </c>
       <c r="W90">
-        <v>0.1622315155026725</v>
+        <v>0.1454315155026725</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8829030181229218</v>
+        <v>0.9604061615854529</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1942712500328476</v>
+        <v>0.1783805196863865</v>
       </c>
       <c r="C91">
-        <v>-2873.353595584271</v>
+        <v>-2563.571212523468</v>
       </c>
       <c r="D91">
-        <v>2584.34440441573</v>
+        <v>2894.126787476534</v>
       </c>
       <c r="E91">
         <v>3598.798000000001</v>
@@ -8743,37 +8743,37 @@
         <v>1034.9</v>
       </c>
       <c r="M91">
-        <v>1185.475874233569</v>
+        <v>1089.809987833569</v>
       </c>
       <c r="N91">
-        <v>-150.575874233569</v>
+        <v>-54.90998783356918</v>
       </c>
       <c r="O91">
-        <v>-37.64396855839226</v>
+        <v>-13.72749695839229</v>
       </c>
       <c r="P91">
-        <v>-112.9319056751768</v>
+        <v>-41.18249087517688</v>
       </c>
       <c r="Q91">
-        <v>760.6680943248232</v>
+        <v>832.417509124823</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.449324437450585</v>
+        <v>0.4407905252100291</v>
       </c>
       <c r="T91">
-        <v>3.902439672420499</v>
+        <v>3.819860263085655</v>
       </c>
       <c r="U91">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V91">
-        <v>0.2182456898730818</v>
+        <v>0.2374037702795501</v>
       </c>
       <c r="W91">
-        <v>0.1627478223744756</v>
+        <v>0.1459478223744756</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8729827594923271</v>
+        <v>0.9496150811182006</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1958950783037791</v>
+        <v>0.179836347957318</v>
       </c>
       <c r="C92">
-        <v>-2965.294750229038</v>
+        <v>-2658.98760820105</v>
       </c>
       <c r="D92">
-        <v>2556.385249770963</v>
+        <v>2862.692391798951</v>
       </c>
       <c r="E92">
         <v>3662.780000000001</v>
@@ -8825,37 +8825,37 @@
         <v>1034.9</v>
       </c>
       <c r="M92">
-        <v>1198.795827876643</v>
+        <v>1102.055043876643</v>
       </c>
       <c r="N92">
-        <v>-163.8958278766429</v>
+        <v>-67.15504387664282</v>
       </c>
       <c r="O92">
-        <v>-40.97395696916072</v>
+        <v>-16.78876096916071</v>
       </c>
       <c r="P92">
-        <v>-122.9218709074822</v>
+        <v>-50.36628290748212</v>
       </c>
       <c r="Q92">
-        <v>750.6781290925178</v>
+        <v>823.2337170925177</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4896768811956436</v>
+        <v>0.480289577731032</v>
       </c>
       <c r="T92">
-        <v>4.292683639662551</v>
+        <v>4.20184628939422</v>
       </c>
       <c r="U92">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V92">
-        <v>0.2158207377633809</v>
+        <v>0.2347659506097774</v>
       </c>
       <c r="W92">
-        <v>0.1632526557602386</v>
+        <v>0.1464526557602386</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8632829510535234</v>
+        <v>0.9390638024391096</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1975189065747106</v>
+        <v>0.1812921762282494</v>
       </c>
       <c r="C93">
-        <v>-3056.637418280822</v>
+        <v>-2753.728495031096</v>
       </c>
       <c r="D93">
-        <v>2529.024581719179</v>
+        <v>2831.933504968905</v>
       </c>
       <c r="E93">
         <v>3726.762000000001</v>
@@ -8907,37 +8907,37 @@
         <v>1034.9</v>
       </c>
       <c r="M93">
-        <v>1212.115781519717</v>
+        <v>1114.300099919717</v>
       </c>
       <c r="N93">
-        <v>-177.2157815197168</v>
+        <v>-79.40009991971669</v>
       </c>
       <c r="O93">
-        <v>-44.30394537992919</v>
+        <v>-19.85002497992917</v>
       </c>
       <c r="P93">
-        <v>-132.9118361397876</v>
+        <v>-59.55007493978752</v>
       </c>
       <c r="Q93">
-        <v>740.6881638602124</v>
+        <v>814.0499250602124</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5389965346618262</v>
+        <v>0.5285661974789245</v>
       </c>
       <c r="T93">
-        <v>4.769648488513945</v>
+        <v>4.668718099326912</v>
       </c>
       <c r="U93">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V93">
-        <v>0.2134490813044426</v>
+        <v>0.2321861049986809</v>
       </c>
       <c r="W93">
-        <v>0.1637463939067541</v>
+        <v>0.1469463939067541</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8537963252177704</v>
+        <v>0.9287444199947238</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.199142734845642</v>
+        <v>0.1827480044991809</v>
       </c>
       <c r="C94">
-        <v>-3147.400612823949</v>
+        <v>-2847.815416041146</v>
       </c>
       <c r="D94">
-        <v>2502.243387176052</v>
+        <v>2801.828583958855</v>
       </c>
       <c r="E94">
         <v>3790.744000000001</v>
@@ -8989,37 +8989,37 @@
         <v>1034.9</v>
       </c>
       <c r="M94">
-        <v>1225.43573516279</v>
+        <v>1126.545155962791</v>
       </c>
       <c r="N94">
-        <v>-190.5357351627904</v>
+        <v>-91.64515596279057</v>
       </c>
       <c r="O94">
-        <v>-47.6339337906976</v>
+        <v>-22.91128899069764</v>
       </c>
       <c r="P94">
-        <v>-142.9018013720928</v>
+        <v>-68.73386697209293</v>
       </c>
       <c r="Q94">
-        <v>730.6981986279071</v>
+        <v>804.8661330279069</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.6006461014945547</v>
+        <v>0.5889119721637903</v>
       </c>
       <c r="T94">
-        <v>5.36585454957819</v>
+        <v>5.252307861742779</v>
       </c>
       <c r="U94">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V94">
-        <v>0.2111289825946117</v>
+        <v>0.2296623429878257</v>
       </c>
       <c r="W94">
-        <v>0.1642293986153018</v>
+        <v>0.1474293986153019</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.844515930378447</v>
+        <v>0.9186493719513028</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2007665631165735</v>
+        <v>0.1842038327701124</v>
       </c>
       <c r="C95">
-        <v>-3237.602550022862</v>
+        <v>-2941.269007840243</v>
       </c>
       <c r="D95">
-        <v>2476.02344997714</v>
+        <v>2772.356992159758</v>
       </c>
       <c r="E95">
         <v>3854.726000000001</v>
@@ -9071,37 +9071,37 @@
         <v>1034.9</v>
       </c>
       <c r="M95">
-        <v>1238.755688805864</v>
+        <v>1138.790212005865</v>
       </c>
       <c r="N95">
-        <v>-203.8556888058642</v>
+        <v>-103.8902120058644</v>
       </c>
       <c r="O95">
-        <v>-50.96392220146606</v>
+        <v>-25.97255300146611</v>
       </c>
       <c r="P95">
-        <v>-152.8917666043982</v>
+        <v>-77.91765900439833</v>
       </c>
       <c r="Q95">
-        <v>720.7082333956017</v>
+        <v>795.6823409956016</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.679909830279491</v>
+        <v>0.6664993967586176</v>
       </c>
       <c r="T95">
-        <v>6.132405199517931</v>
+        <v>6.002637556277461</v>
       </c>
       <c r="U95">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V95">
-        <v>0.2088587784806912</v>
+        <v>0.2271928554288168</v>
       </c>
       <c r="W95">
-        <v>0.1647020161258163</v>
+        <v>0.1479020161258164</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8354351139227647</v>
+        <v>0.9087714217152673</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.202390391387505</v>
+        <v>0.1856596610410439</v>
       </c>
       <c r="C96">
-        <v>-3327.260690442056</v>
+        <v>-3034.109047794424</v>
       </c>
       <c r="D96">
-        <v>2450.347309557945</v>
+        <v>2743.498952205577</v>
       </c>
       <c r="E96">
         <v>3918.708000000001</v>
@@ -9153,37 +9153,37 @@
         <v>1034.9</v>
       </c>
       <c r="M96">
-        <v>1252.075642448938</v>
+        <v>1151.035268048938</v>
       </c>
       <c r="N96">
-        <v>-217.1756424489381</v>
+        <v>-116.1352680489381</v>
       </c>
       <c r="O96">
-        <v>-54.29391061223453</v>
+        <v>-29.03381701223452</v>
       </c>
       <c r="P96">
-        <v>-162.8817318367036</v>
+        <v>-87.10145103670357</v>
       </c>
       <c r="Q96">
-        <v>710.7182681632963</v>
+        <v>786.4985489632963</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7855948019927398</v>
+        <v>0.7699492962183871</v>
       </c>
       <c r="T96">
-        <v>7.154472732770922</v>
+        <v>7.003077148990372</v>
       </c>
       <c r="U96">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V96">
-        <v>0.2066368765819604</v>
+        <v>0.2247759101582975</v>
       </c>
       <c r="W96">
-        <v>0.1651645779446177</v>
+        <v>0.1483645779446177</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8265475063278416</v>
+        <v>0.89910364063319</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2040142196584365</v>
+        <v>0.1871154893119754</v>
       </c>
       <c r="C97">
-        <v>-3416.391777821503</v>
+        <v>-3126.354498286214</v>
       </c>
       <c r="D97">
-        <v>2425.198222178498</v>
+        <v>2715.235501713787</v>
       </c>
       <c r="E97">
         <v>3982.690000000001</v>
@@ -9235,37 +9235,37 @@
         <v>1034.9</v>
       </c>
       <c r="M97">
-        <v>1265.395596092012</v>
+        <v>1163.280324092012</v>
       </c>
       <c r="N97">
-        <v>-230.495596092012</v>
+        <v>-128.380324092012</v>
       </c>
       <c r="O97">
-        <v>-57.62389902300299</v>
+        <v>-32.09508102300299</v>
       </c>
       <c r="P97">
-        <v>-172.871697069009</v>
+        <v>-96.28524306900897</v>
       </c>
       <c r="Q97">
-        <v>700.7283029309909</v>
+        <v>777.3147569309909</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.9335537623912881</v>
+        <v>0.9147791554620653</v>
       </c>
       <c r="T97">
-        <v>8.58536727932511</v>
+        <v>8.403692578788453</v>
       </c>
       <c r="U97">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V97">
-        <v>0.2044617515653082</v>
+        <v>0.2224098479461049</v>
       </c>
       <c r="W97">
-        <v>0.1656174016198654</v>
+        <v>0.1488174016198655</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8178470062612327</v>
+        <v>0.8896393917844195</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.205638047929368</v>
+        <v>0.1885713175829068</v>
       </c>
       <c r="C98">
-        <v>-3505.011875488502</v>
+        <v>-3218.023548266236</v>
       </c>
       <c r="D98">
-        <v>2400.560124511499</v>
+        <v>2687.548451733765</v>
       </c>
       <c r="E98">
         <v>4046.672000000001</v>
@@ -9317,37 +9317,37 @@
         <v>1034.9</v>
       </c>
       <c r="M98">
-        <v>1278.715549735086</v>
+        <v>1175.525380135086</v>
       </c>
       <c r="N98">
-        <v>-243.8155497350856</v>
+        <v>-140.6253801350858</v>
       </c>
       <c r="O98">
-        <v>-60.9538874337714</v>
+        <v>-35.15634503377146</v>
       </c>
       <c r="P98">
-        <v>-182.8616623013142</v>
+        <v>-105.4690351013144</v>
       </c>
       <c r="Q98">
-        <v>690.7383376986857</v>
+        <v>768.1309648986855</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.155492202989108</v>
+        <v>1.132023944327579</v>
       </c>
       <c r="T98">
-        <v>10.73170909915636</v>
+        <v>10.50461572348554</v>
       </c>
       <c r="U98">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V98">
-        <v>0.2023319416531696</v>
+        <v>0.2200930786966663</v>
       </c>
       <c r="W98">
-        <v>0.1660607914685454</v>
+        <v>0.1492607914685455</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8093277666126784</v>
+        <v>0.8803723147866651</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2072618762002995</v>
+        <v>0.1900271458538383</v>
       </c>
       <c r="C99">
-        <v>-3593.13640057236</v>
+        <v>-3309.133652288327</v>
       </c>
       <c r="D99">
-        <v>2376.417599427641</v>
+        <v>2660.420347711674</v>
       </c>
       <c r="E99">
         <v>4110.654</v>
@@ -9399,37 +9399,37 @@
         <v>1034.9</v>
       </c>
       <c r="M99">
-        <v>1292.03550337816</v>
+        <v>1187.77043617816</v>
       </c>
       <c r="N99">
-        <v>-257.1355033781595</v>
+        <v>-152.8704361781595</v>
       </c>
       <c r="O99">
-        <v>-64.28387584453986</v>
+        <v>-38.21760904453987</v>
       </c>
       <c r="P99">
-        <v>-192.8516275336196</v>
+        <v>-114.6528271336196</v>
       </c>
       <c r="Q99">
-        <v>680.7483724663803</v>
+        <v>758.9471728663802</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.525389603985477</v>
+        <v>1.494098592436772</v>
       </c>
       <c r="T99">
-        <v>14.30894546554182</v>
+        <v>14.00615429798072</v>
       </c>
       <c r="U99">
-        <v>0.2081828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V99">
-        <v>0.2002460453474668</v>
+        <v>0.2178240778853605</v>
       </c>
       <c r="W99">
-        <v>0.1664950392584898</v>
+        <v>0.1496950392584898</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8009841813898672</v>
+        <v>0.8712963115414419</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2621868163554432</v>
+        <v>0.1914829741247698</v>
       </c>
       <c r="C100">
-        <v>-4260.318709309238</v>
+        <v>-3399.701567204114</v>
       </c>
       <c r="D100">
-        <v>1773.217290690762</v>
+        <v>2633.834432795887</v>
       </c>
       <c r="E100">
         <v>4174.636</v>
@@ -9481,45 +9481,45 @@
         <v>1034.9</v>
       </c>
       <c r="M100">
-        <v>1632.661776221233</v>
+        <v>1200.015492221233</v>
       </c>
       <c r="N100">
-        <v>-597.7617762212333</v>
+        <v>-165.1154922212334</v>
       </c>
       <c r="O100">
-        <v>-149.4404440553083</v>
+        <v>-41.27887305530834</v>
       </c>
       <c r="P100">
-        <v>-448.321332165925</v>
+        <v>-123.836619165925</v>
       </c>
       <c r="Q100">
-        <v>425.278667834075</v>
+        <v>749.763380834075</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.372440000188829</v>
+        <v>2.218247888655158</v>
       </c>
       <c r="T100">
-        <v>22.5006750459548</v>
+        <v>21.00923144697108</v>
       </c>
       <c r="U100">
-        <v>0.2603828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V100">
-        <v>0.1584682166068801</v>
+        <v>0.2156013832130609</v>
       </c>
       <c r="W100">
-        <v>0.2191204248486394</v>
+        <v>0.1501204248486394</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.6338728664275204</v>
+        <v>0.8624055328522435</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2643326446263747</v>
+        <v>0.1929388023957013</v>
       </c>
       <c r="C101">
-        <v>-4341.712386175064</v>
+        <v>-3489.743386679232</v>
       </c>
       <c r="D101">
-        <v>1755.805613824936</v>
+        <v>2607.774613320769</v>
       </c>
       <c r="E101">
         <v>4238.618</v>
@@ -9563,45 +9563,45 @@
         <v>1034.9</v>
       </c>
       <c r="M101">
-        <v>1649.321590264307</v>
+        <v>1212.260548264307</v>
       </c>
       <c r="N101">
-        <v>-614.421590264307</v>
+        <v>-177.3605482643072</v>
       </c>
       <c r="O101">
-        <v>-153.6053975660768</v>
+        <v>-44.34013706607681</v>
       </c>
       <c r="P101">
-        <v>-460.8161926982303</v>
+        <v>-133.0204111982304</v>
       </c>
       <c r="Q101">
-        <v>412.7838073017696</v>
+        <v>740.5795888017694</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.699080000377656</v>
+        <v>4.390695777310316</v>
       </c>
       <c r="T101">
-        <v>45.00135009190958</v>
+        <v>42.01846289394216</v>
       </c>
       <c r="U101">
-        <v>0.2603828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V101">
-        <v>0.156867527550245</v>
+        <v>0.213423591463434</v>
       </c>
       <c r="W101">
-        <v>0.2195372167905031</v>
+        <v>0.1505372167905031</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.6274701102009799</v>
+        <v>0.8536943658537359</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/turkey/turkey_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_telecom_services.xlsx
@@ -1127,43 +1127,43 @@
         <v>1.31159420289855</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>170.47196184372</v>
       </c>
       <c r="G2">
         <v>1.83005851017378</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0558745961051437</v>
       </c>
       <c r="I2">
         <v>0.327529617704979</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>4302.6</v>
       </c>
       <c r="L2">
-        <v>7201.93235623997</v>
+        <v>7123.32711594643</v>
       </c>
       <c r="M2">
         <v>6161.5</v>
       </c>
       <c r="N2">
-        <v>6965.23235623997</v>
+        <v>6950.60911594643</v>
       </c>
       <c r="O2">
         <v>2095.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>63.982</v>
       </c>
       <c r="Q2">
         <v>0.108074581436652</v>
       </c>
       <c r="R2">
-        <v>0.100888590573462</v>
+        <v>0.101004490300227</v>
       </c>
       <c r="S2">
         <v>0.0815121203198611</v>
@@ -1185,13 +1185,13 @@
         <v>0.121011943384392</v>
       </c>
       <c r="X2">
-        <v>0.100888590573462</v>
+        <v>0.101305928380836</v>
       </c>
       <c r="Y2">
         <v>0.727356975691306</v>
       </c>
       <c r="Z2">
-        <v>0.532748774085323</v>
+        <v>0.536784749646575</v>
       </c>
       <c r="AA2">
         <v>2095.6</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1008885905734616</v>
+        <v>0.1010044903002265</v>
       </c>
       <c r="C2">
-        <v>7201.932356239973</v>
+        <v>7123.327115946431</v>
       </c>
       <c r="D2">
-        <v>6965.232356239973</v>
+        <v>6950.609115946431</v>
       </c>
       <c r="E2">
-        <v>-2095.6</v>
+        <v>-2031.618</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>63.98200000000001</v>
       </c>
       <c r="G2">
         <v>236.7</v>
@@ -1445,28 +1445,28 @@
         <v>1034.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.070793043073808</v>
       </c>
       <c r="N2">
-        <v>1034.9</v>
+        <v>1028.829206956926</v>
       </c>
       <c r="O2">
-        <v>258.725</v>
+        <v>257.2073017392316</v>
       </c>
       <c r="P2">
-        <v>776.1750000000001</v>
+        <v>771.6219052176948</v>
       </c>
       <c r="Q2">
-        <v>1649.775</v>
+        <v>1645.221905217695</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1008885905734616</v>
+        <v>0.1013059283808363</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5367847496465754</v>
       </c>
       <c r="U2">
         <v>0.09488282709314819</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>170.4719618437202</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1010044903002265</v>
+        <v>0.1011203900269915</v>
       </c>
       <c r="C3">
-        <v>7123.327115946431</v>
+        <v>7044.783148885189</v>
       </c>
       <c r="D3">
-        <v>6950.609115946431</v>
+        <v>6936.047148885189</v>
       </c>
       <c r="E3">
-        <v>-2031.618</v>
+        <v>-1967.636</v>
       </c>
       <c r="F3">
-        <v>63.98200000000001</v>
+        <v>127.964</v>
       </c>
       <c r="G3">
         <v>236.7</v>
@@ -1527,28 +1527,28 @@
         <v>1034.9</v>
       </c>
       <c r="M3">
-        <v>6.070793043073808</v>
+        <v>12.14158608614762</v>
       </c>
       <c r="N3">
-        <v>1028.829206956926</v>
+        <v>1022.758413913852</v>
       </c>
       <c r="O3">
-        <v>257.2073017392316</v>
+        <v>255.6896034784631</v>
       </c>
       <c r="P3">
-        <v>771.6219052176948</v>
+        <v>767.0688104353893</v>
       </c>
       <c r="Q3">
-        <v>1645.221905217695</v>
+        <v>1640.668810435389</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1013059283808363</v>
+        <v>0.1017317832863207</v>
       </c>
       <c r="T3">
-        <v>0.5367847496465754</v>
+        <v>0.5409030920560167</v>
       </c>
       <c r="U3">
         <v>0.09488282709314819</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>170.4719618437202</v>
+        <v>85.23598092186009</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1011203900269915</v>
+        <v>0.1012362897537564</v>
       </c>
       <c r="C4">
-        <v>7044.783148885189</v>
+        <v>6966.300070747468</v>
       </c>
       <c r="D4">
-        <v>6936.047148885189</v>
+        <v>6921.546070747468</v>
       </c>
       <c r="E4">
-        <v>-1967.636</v>
+        <v>-1903.654</v>
       </c>
       <c r="F4">
-        <v>127.964</v>
+        <v>191.946</v>
       </c>
       <c r="G4">
         <v>236.7</v>
@@ -1609,28 +1609,28 @@
         <v>1034.9</v>
       </c>
       <c r="M4">
-        <v>12.14158608614762</v>
+        <v>18.21237912922142</v>
       </c>
       <c r="N4">
-        <v>1022.758413913852</v>
+        <v>1016.687620870779</v>
       </c>
       <c r="O4">
-        <v>255.6896034784631</v>
+        <v>254.1719052176947</v>
       </c>
       <c r="P4">
-        <v>767.0688104353893</v>
+        <v>762.515715653084</v>
       </c>
       <c r="Q4">
-        <v>1640.668810435389</v>
+        <v>1636.115715653084</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1017317832863207</v>
+        <v>0.1021664187053202</v>
       </c>
       <c r="T4">
-        <v>0.5409030920560167</v>
+        <v>0.5451063487419412</v>
       </c>
       <c r="U4">
         <v>0.09488282709314819</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>85.23598092186009</v>
+        <v>56.82398728124006</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1012362897537564</v>
+        <v>0.1013521894805214</v>
       </c>
       <c r="C5">
-        <v>6966.300070747468</v>
+        <v>6887.877500431655</v>
       </c>
       <c r="D5">
-        <v>6921.546070747468</v>
+        <v>6907.105500431655</v>
       </c>
       <c r="E5">
-        <v>-1903.654</v>
+        <v>-1839.672</v>
       </c>
       <c r="F5">
-        <v>191.946</v>
+        <v>255.928</v>
       </c>
       <c r="G5">
         <v>236.7</v>
@@ -1691,28 +1691,28 @@
         <v>1034.9</v>
       </c>
       <c r="M5">
-        <v>18.21237912922142</v>
+        <v>24.28317217229523</v>
       </c>
       <c r="N5">
-        <v>1016.687620870779</v>
+        <v>1010.616827827705</v>
       </c>
       <c r="O5">
-        <v>254.1719052176947</v>
+        <v>252.6542069569262</v>
       </c>
       <c r="P5">
-        <v>762.515715653084</v>
+        <v>757.9626208707787</v>
       </c>
       <c r="Q5">
-        <v>1636.115715653084</v>
+        <v>1631.562620870779</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1021664187053202</v>
+        <v>0.1026101090288823</v>
       </c>
       <c r="T5">
-        <v>0.5451063487419412</v>
+        <v>0.5493971732754893</v>
       </c>
       <c r="U5">
         <v>0.09488282709314819</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.82398728124006</v>
+        <v>42.61799046093005</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1013521894805214</v>
+        <v>0.1014680892072864</v>
       </c>
       <c r="C6">
-        <v>6887.877500431655</v>
+        <v>6809.51506000993</v>
       </c>
       <c r="D6">
-        <v>6907.105500431655</v>
+        <v>6892.725060009931</v>
       </c>
       <c r="E6">
-        <v>-1839.672</v>
+        <v>-1775.69</v>
       </c>
       <c r="F6">
-        <v>255.928</v>
+        <v>319.9100000000001</v>
       </c>
       <c r="G6">
         <v>236.7</v>
@@ -1773,28 +1773,28 @@
         <v>1034.9</v>
       </c>
       <c r="M6">
-        <v>24.28317217229523</v>
+        <v>30.35396521536904</v>
       </c>
       <c r="N6">
-        <v>1010.616827827705</v>
+        <v>1004.546034784631</v>
       </c>
       <c r="O6">
-        <v>252.6542069569262</v>
+        <v>251.1365086961578</v>
       </c>
       <c r="P6">
-        <v>757.9626208707787</v>
+        <v>753.4095260884733</v>
       </c>
       <c r="Q6">
-        <v>1631.562620870779</v>
+        <v>1627.009526088473</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1026101090288823</v>
+        <v>0.1030631402013614</v>
       </c>
       <c r="T6">
-        <v>0.5493971732754893</v>
+        <v>0.553778330957112</v>
       </c>
       <c r="U6">
         <v>0.09488282709314819</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.61799046093005</v>
+        <v>34.09439236874403</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1014680892072864</v>
+        <v>0.1015839889340513</v>
       </c>
       <c r="C7">
-        <v>6809.51506000993</v>
+        <v>6731.212374695269</v>
       </c>
       <c r="D7">
-        <v>6892.725060009931</v>
+        <v>6878.404374695269</v>
       </c>
       <c r="E7">
-        <v>-1775.69</v>
+        <v>-1711.708</v>
       </c>
       <c r="F7">
-        <v>319.9100000000001</v>
+        <v>383.8920000000001</v>
       </c>
       <c r="G7">
         <v>236.7</v>
@@ -1855,28 +1855,28 @@
         <v>1034.9</v>
       </c>
       <c r="M7">
-        <v>30.35396521536904</v>
+        <v>36.42475825844285</v>
       </c>
       <c r="N7">
-        <v>1004.546034784631</v>
+        <v>998.4752417415573</v>
       </c>
       <c r="O7">
-        <v>251.1365086961578</v>
+        <v>249.6188104353893</v>
       </c>
       <c r="P7">
-        <v>753.4095260884733</v>
+        <v>748.8564313061679</v>
       </c>
       <c r="Q7">
-        <v>1627.009526088473</v>
+        <v>1622.456431306168</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1030631402013614</v>
+        <v>0.1035258103349571</v>
       </c>
       <c r="T7">
-        <v>0.553778330957112</v>
+        <v>0.5582527047596203</v>
       </c>
       <c r="U7">
         <v>0.09488282709314819</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.09439236874403</v>
+        <v>28.41199364062003</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1015839889340513</v>
+        <v>0.1016998886608163</v>
       </c>
       <c r="C8">
-        <v>6731.212374695269</v>
+        <v>6652.969072808904</v>
       </c>
       <c r="D8">
-        <v>6878.404374695269</v>
+        <v>6864.143072808904</v>
       </c>
       <c r="E8">
-        <v>-1711.708</v>
+        <v>-1647.726</v>
       </c>
       <c r="F8">
-        <v>383.8920000000001</v>
+        <v>447.874</v>
       </c>
       <c r="G8">
         <v>236.7</v>
@@ -1937,28 +1937,28 @@
         <v>1034.9</v>
       </c>
       <c r="M8">
-        <v>36.42475825844285</v>
+        <v>42.49555130151666</v>
       </c>
       <c r="N8">
-        <v>998.4752417415573</v>
+        <v>992.4044486984834</v>
       </c>
       <c r="O8">
-        <v>249.6188104353893</v>
+        <v>248.1011121746209</v>
       </c>
       <c r="P8">
-        <v>748.8564313061679</v>
+        <v>744.3033365238625</v>
       </c>
       <c r="Q8">
-        <v>1622.456431306168</v>
+        <v>1617.903336523862</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1035258103349571</v>
+        <v>0.1039984303638989</v>
       </c>
       <c r="T8">
-        <v>0.5582527047596203</v>
+        <v>0.5628233016546557</v>
       </c>
       <c r="U8">
         <v>0.09488282709314819</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.41199364062003</v>
+        <v>24.35313740624574</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1016998886608163</v>
+        <v>0.1018157883875812</v>
       </c>
       <c r="C9">
-        <v>6652.969072808904</v>
+        <v>6574.78478574816</v>
       </c>
       <c r="D9">
-        <v>6864.143072808904</v>
+        <v>6849.94078574816</v>
       </c>
       <c r="E9">
-        <v>-1647.726</v>
+        <v>-1583.744</v>
       </c>
       <c r="F9">
-        <v>447.8740000000001</v>
+        <v>511.8560000000001</v>
       </c>
       <c r="G9">
         <v>236.7</v>
@@ -2019,28 +2019,28 @@
         <v>1034.9</v>
       </c>
       <c r="M9">
-        <v>42.49555130151666</v>
+        <v>48.56634434459046</v>
       </c>
       <c r="N9">
-        <v>992.4044486984834</v>
+        <v>986.3336556554096</v>
       </c>
       <c r="O9">
-        <v>248.1011121746209</v>
+        <v>246.5834139138524</v>
       </c>
       <c r="P9">
-        <v>744.3033365238625</v>
+        <v>739.7502417415573</v>
       </c>
       <c r="Q9">
-        <v>1617.903336523862</v>
+        <v>1613.350241741557</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1039984303638989</v>
+        <v>0.104481324741296</v>
       </c>
       <c r="T9">
-        <v>0.5628233016546557</v>
+        <v>0.5674932593517571</v>
       </c>
       <c r="U9">
         <v>0.09488282709314819</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.35313740624574</v>
+        <v>21.30899523046502</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1018157883875812</v>
+        <v>0.1019316881143462</v>
       </c>
       <c r="C10">
-        <v>6574.78478574816</v>
+        <v>6496.65914795471</v>
       </c>
       <c r="D10">
-        <v>6849.94078574816</v>
+        <v>6835.79714795471</v>
       </c>
       <c r="E10">
-        <v>-1583.744</v>
+        <v>-1519.762</v>
       </c>
       <c r="F10">
-        <v>511.8560000000001</v>
+        <v>575.8380000000001</v>
       </c>
       <c r="G10">
         <v>236.7</v>
@@ -2101,28 +2101,28 @@
         <v>1034.9</v>
       </c>
       <c r="M10">
-        <v>48.56634434459046</v>
+        <v>54.63713738766427</v>
       </c>
       <c r="N10">
-        <v>986.3336556554096</v>
+        <v>980.2628626123358</v>
       </c>
       <c r="O10">
-        <v>246.5834139138524</v>
+        <v>245.0657156530839</v>
       </c>
       <c r="P10">
-        <v>739.7502417415573</v>
+        <v>735.1971469592518</v>
       </c>
       <c r="Q10">
-        <v>1613.350241741557</v>
+        <v>1608.797146959252</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.104481324741296</v>
+        <v>0.1049748321819326</v>
       </c>
       <c r="T10">
-        <v>0.5674932593517571</v>
+        <v>0.5722658534817617</v>
       </c>
       <c r="U10">
         <v>0.09488282709314819</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.30899523046502</v>
+        <v>18.94132909374668</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1019316881143462</v>
+        <v>0.1020475878411111</v>
       </c>
       <c r="C11">
-        <v>6496.65914795471</v>
+        <v>6418.591796883183</v>
       </c>
       <c r="D11">
-        <v>6835.79714795471</v>
+        <v>6821.711796883183</v>
       </c>
       <c r="E11">
-        <v>-1519.762</v>
+        <v>-1455.78</v>
       </c>
       <c r="F11">
-        <v>575.8380000000001</v>
+        <v>639.8200000000001</v>
       </c>
       <c r="G11">
         <v>236.7</v>
@@ -2183,28 +2183,28 @@
         <v>1034.9</v>
       </c>
       <c r="M11">
-        <v>54.63713738766427</v>
+        <v>60.70793043073808</v>
       </c>
       <c r="N11">
-        <v>980.2628626123358</v>
+        <v>974.192069569262</v>
       </c>
       <c r="O11">
-        <v>245.0657156530839</v>
+        <v>243.5480173923155</v>
       </c>
       <c r="P11">
-        <v>735.1971469592518</v>
+        <v>730.6440521769465</v>
       </c>
       <c r="Q11">
-        <v>1608.797146959252</v>
+        <v>1604.244052176946</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1049748321819326</v>
+        <v>0.1054793064545834</v>
       </c>
       <c r="T11">
-        <v>0.5722658534817617</v>
+        <v>0.5771445052590998</v>
       </c>
       <c r="U11">
         <v>0.09488282709314819</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.94132909374668</v>
+        <v>17.04719618437202</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1020475878411111</v>
+        <v>0.1021634875678761</v>
       </c>
       <c r="C12">
-        <v>6418.591796883182</v>
+        <v>6340.58237297021</v>
       </c>
       <c r="D12">
-        <v>6821.711796883183</v>
+        <v>6807.68437297021</v>
       </c>
       <c r="E12">
-        <v>-1455.78</v>
+        <v>-1391.798</v>
       </c>
       <c r="F12">
-        <v>639.8200000000002</v>
+        <v>703.8020000000001</v>
       </c>
       <c r="G12">
         <v>236.7</v>
@@ -2265,28 +2265,28 @@
         <v>1034.9</v>
       </c>
       <c r="M12">
-        <v>60.70793043073809</v>
+        <v>66.77872347381189</v>
       </c>
       <c r="N12">
-        <v>974.192069569262</v>
+        <v>968.1212765261882</v>
       </c>
       <c r="O12">
-        <v>243.5480173923155</v>
+        <v>242.0303191315471</v>
       </c>
       <c r="P12">
-        <v>730.6440521769465</v>
+        <v>726.0909573946412</v>
       </c>
       <c r="Q12">
-        <v>1604.244052176946</v>
+        <v>1599.690957394641</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1054793064545834</v>
+        <v>0.1059951172277431</v>
       </c>
       <c r="T12">
-        <v>0.5771445052590998</v>
+        <v>0.5821327896606479</v>
       </c>
       <c r="U12">
         <v>0.09488282709314819</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.04719618437202</v>
+        <v>15.49745107670183</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1021634875678761</v>
+        <v>0.1022793872946411</v>
       </c>
       <c r="C13">
-        <v>6340.58237297021</v>
+        <v>6262.630519603827</v>
       </c>
       <c r="D13">
-        <v>6807.68437297021</v>
+        <v>6793.714519603827</v>
       </c>
       <c r="E13">
-        <v>-1391.798</v>
+        <v>-1327.816</v>
       </c>
       <c r="F13">
-        <v>703.8020000000001</v>
+        <v>767.7840000000001</v>
       </c>
       <c r="G13">
         <v>236.7</v>
@@ -2347,28 +2347,28 @@
         <v>1034.9</v>
       </c>
       <c r="M13">
-        <v>66.77872347381189</v>
+        <v>72.8495165168857</v>
       </c>
       <c r="N13">
-        <v>968.1212765261882</v>
+        <v>962.0504834831144</v>
       </c>
       <c r="O13">
-        <v>242.0303191315471</v>
+        <v>240.5126208707786</v>
       </c>
       <c r="P13">
-        <v>726.0909573946412</v>
+        <v>721.5378626123357</v>
       </c>
       <c r="Q13">
-        <v>1599.690957394641</v>
+        <v>1595.137862612336</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1059951172277431</v>
+        <v>0.1065226509730202</v>
       </c>
       <c r="T13">
-        <v>0.5821327896606479</v>
+        <v>0.587234444162231</v>
       </c>
       <c r="U13">
         <v>0.09488282709314819</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.49745107670183</v>
+        <v>14.20599682031001</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1022793872946411</v>
+        <v>0.102395287021406</v>
       </c>
       <c r="C14">
-        <v>6262.630519603827</v>
+        <v>6184.735883093241</v>
       </c>
       <c r="D14">
-        <v>6793.714519603827</v>
+        <v>6779.801883093241</v>
       </c>
       <c r="E14">
-        <v>-1327.816</v>
+        <v>-1263.834</v>
       </c>
       <c r="F14">
-        <v>767.7840000000001</v>
+        <v>831.7660000000001</v>
       </c>
       <c r="G14">
         <v>236.7</v>
@@ -2429,28 +2429,28 @@
         <v>1034.9</v>
       </c>
       <c r="M14">
-        <v>72.8495165168857</v>
+        <v>78.92030955995951</v>
       </c>
       <c r="N14">
-        <v>962.0504834831144</v>
+        <v>955.9796904400406</v>
       </c>
       <c r="O14">
-        <v>240.5126208707786</v>
+        <v>238.9949226100101</v>
       </c>
       <c r="P14">
-        <v>721.5378626123357</v>
+        <v>716.9847678300305</v>
       </c>
       <c r="Q14">
-        <v>1595.137862612336</v>
+        <v>1590.58476783003</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1065226509730202</v>
+        <v>0.1070623119308323</v>
       </c>
       <c r="T14">
-        <v>0.587234444162231</v>
+        <v>0.5924533780776436</v>
       </c>
       <c r="U14">
         <v>0.09488282709314819</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.20599682031001</v>
+        <v>13.11322783413232</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.102395287021406</v>
+        <v>0.102668686748171</v>
       </c>
       <c r="C15">
-        <v>6184.735883093241</v>
+        <v>6088.159566460495</v>
       </c>
       <c r="D15">
-        <v>6779.801883093241</v>
+        <v>6747.207566460495</v>
       </c>
       <c r="E15">
-        <v>-1263.834</v>
+        <v>-1199.852</v>
       </c>
       <c r="F15">
-        <v>831.7660000000001</v>
+        <v>895.7480000000002</v>
       </c>
       <c r="G15">
         <v>236.7</v>
@@ -2511,45 +2511,45 @@
         <v>1034.9</v>
       </c>
       <c r="M15">
-        <v>78.92030955995951</v>
+        <v>86.33472460303332</v>
       </c>
       <c r="N15">
-        <v>955.9796904400406</v>
+        <v>948.5652753969667</v>
       </c>
       <c r="O15">
-        <v>238.9949226100101</v>
+        <v>237.1413188492417</v>
       </c>
       <c r="P15">
-        <v>716.9847678300305</v>
+        <v>711.4239565477251</v>
       </c>
       <c r="Q15">
-        <v>1590.58476783003</v>
+        <v>1585.023956547725</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1070623119308323</v>
+        <v>0.1076145231434772</v>
       </c>
       <c r="T15">
-        <v>0.5924533780776436</v>
+        <v>0.5977936825492287</v>
       </c>
       <c r="U15">
-        <v>0.09488282709314819</v>
+        <v>0.09638282709314819</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.07116212031986113</v>
+        <v>0.07228712031986115</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.11322783413232</v>
+        <v>11.98706551458252</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.102668686748171</v>
+        <v>0.1027958364749359</v>
       </c>
       <c r="C16">
-        <v>6088.159566460495</v>
+        <v>6009.125491579917</v>
       </c>
       <c r="D16">
-        <v>6747.207566460495</v>
+        <v>6732.155491579918</v>
       </c>
       <c r="E16">
-        <v>-1199.852</v>
+        <v>-1135.87</v>
       </c>
       <c r="F16">
-        <v>895.7480000000002</v>
+        <v>959.7300000000002</v>
       </c>
       <c r="G16">
         <v>236.7</v>
@@ -2593,28 +2593,28 @@
         <v>1034.9</v>
       </c>
       <c r="M16">
-        <v>86.33472460303332</v>
+        <v>92.50149064610713</v>
       </c>
       <c r="N16">
-        <v>948.5652753969667</v>
+        <v>942.3985093538929</v>
       </c>
       <c r="O16">
-        <v>237.1413188492417</v>
+        <v>235.5996273384732</v>
       </c>
       <c r="P16">
-        <v>711.4239565477251</v>
+        <v>706.7988820154196</v>
       </c>
       <c r="Q16">
-        <v>1585.023956547725</v>
+        <v>1580.39888201542</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1076145231434772</v>
+        <v>0.1081797275611256</v>
       </c>
       <c r="T16">
-        <v>0.5977936825492287</v>
+        <v>0.6032596412436745</v>
       </c>
       <c r="U16">
         <v>0.09638282709314819</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.98706551458252</v>
+        <v>11.18792781361035</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1027958364749359</v>
+        <v>0.1029229862017009</v>
       </c>
       <c r="C17">
-        <v>6009.125491579918</v>
+        <v>5930.158425353319</v>
       </c>
       <c r="D17">
-        <v>6732.155491579918</v>
+        <v>6717.17042535332</v>
       </c>
       <c r="E17">
-        <v>-1135.87</v>
+        <v>-1071.888</v>
       </c>
       <c r="F17">
-        <v>959.73</v>
+        <v>1023.712</v>
       </c>
       <c r="G17">
         <v>236.7</v>
@@ -2675,28 +2675,28 @@
         <v>1034.9</v>
       </c>
       <c r="M17">
-        <v>92.50149064610711</v>
+        <v>98.66825668918092</v>
       </c>
       <c r="N17">
-        <v>942.398509353893</v>
+        <v>936.2317433108192</v>
       </c>
       <c r="O17">
-        <v>235.5996273384733</v>
+        <v>234.0579358277048</v>
       </c>
       <c r="P17">
-        <v>706.7988820154197</v>
+        <v>702.1738074831144</v>
       </c>
       <c r="Q17">
-        <v>1580.39888201542</v>
+        <v>1575.773807483114</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1081797275611256</v>
+        <v>0.1087583892268132</v>
       </c>
       <c r="T17">
-        <v>0.6032596412436745</v>
+        <v>0.6088557418117976</v>
       </c>
       <c r="U17">
         <v>0.09638282709314819</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.18792781361036</v>
+        <v>10.48868232525971</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1029229862017009</v>
+        <v>0.1030501359284658</v>
       </c>
       <c r="C18">
-        <v>5930.158425353319</v>
+        <v>5851.257921311958</v>
       </c>
       <c r="D18">
-        <v>6717.17042535332</v>
+        <v>6702.251921311959</v>
       </c>
       <c r="E18">
-        <v>-1071.888</v>
+        <v>-1007.906</v>
       </c>
       <c r="F18">
-        <v>1023.712</v>
+        <v>1087.694</v>
       </c>
       <c r="G18">
         <v>236.7</v>
@@ -2757,28 +2757,28 @@
         <v>1034.9</v>
       </c>
       <c r="M18">
-        <v>98.66825668918092</v>
+        <v>104.8350227322547</v>
       </c>
       <c r="N18">
-        <v>936.2317433108192</v>
+        <v>930.0649772677453</v>
       </c>
       <c r="O18">
-        <v>234.0579358277048</v>
+        <v>232.5162443169363</v>
       </c>
       <c r="P18">
-        <v>702.1738074831144</v>
+        <v>697.548732950809</v>
       </c>
       <c r="Q18">
-        <v>1575.773807483114</v>
+        <v>1571.148732950809</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1087583892268132</v>
+        <v>0.1093509945470957</v>
       </c>
       <c r="T18">
-        <v>0.6088557418117976</v>
+        <v>0.6145866881767431</v>
       </c>
       <c r="U18">
         <v>0.09638282709314819</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.48868232525971</v>
+        <v>9.871701012009138</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1030501359284658</v>
+        <v>0.1034067856552308</v>
       </c>
       <c r="C19">
-        <v>5851.257921311958</v>
+        <v>5745.781568012125</v>
       </c>
       <c r="D19">
-        <v>6702.251921311959</v>
+        <v>6660.757568012125</v>
       </c>
       <c r="E19">
-        <v>-1007.906</v>
+        <v>-943.9239999999998</v>
       </c>
       <c r="F19">
-        <v>1087.694</v>
+        <v>1151.676</v>
       </c>
       <c r="G19">
         <v>236.7</v>
@@ -2839,45 +2839,45 @@
         <v>1034.9</v>
       </c>
       <c r="M19">
-        <v>104.8350227322547</v>
+        <v>112.9596379753286</v>
       </c>
       <c r="N19">
-        <v>930.0649772677453</v>
+        <v>921.9403620246716</v>
       </c>
       <c r="O19">
-        <v>232.5162443169363</v>
+        <v>230.4850905061679</v>
       </c>
       <c r="P19">
-        <v>697.548732950809</v>
+        <v>691.4552715185037</v>
       </c>
       <c r="Q19">
-        <v>1571.148732950809</v>
+        <v>1565.055271518504</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1093509945470957</v>
+        <v>0.1099580536556778</v>
       </c>
       <c r="T19">
-        <v>0.6145866881767431</v>
+        <v>0.6204574137213212</v>
       </c>
       <c r="U19">
-        <v>0.09638282709314819</v>
+        <v>0.09808282709314819</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.07228712031986115</v>
+        <v>0.07356212031986115</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.871701012009138</v>
+        <v>9.161679503842176</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1034067856552308</v>
+        <v>0.1035466853819958</v>
       </c>
       <c r="C20">
-        <v>5745.781568012125</v>
+        <v>5665.66291605282</v>
       </c>
       <c r="D20">
-        <v>6660.757568012125</v>
+        <v>6644.620916052821</v>
       </c>
       <c r="E20">
-        <v>-943.9239999999998</v>
+        <v>-879.9419999999998</v>
       </c>
       <c r="F20">
-        <v>1151.676</v>
+        <v>1215.658</v>
       </c>
       <c r="G20">
         <v>236.7</v>
@@ -2921,28 +2921,28 @@
         <v>1034.9</v>
       </c>
       <c r="M20">
-        <v>112.9596379753286</v>
+        <v>119.2351734184024</v>
       </c>
       <c r="N20">
-        <v>921.9403620246716</v>
+        <v>915.6648265815977</v>
       </c>
       <c r="O20">
-        <v>230.4850905061679</v>
+        <v>228.9162066453994</v>
       </c>
       <c r="P20">
-        <v>691.4552715185037</v>
+        <v>686.7486199361983</v>
       </c>
       <c r="Q20">
-        <v>1565.055271518504</v>
+        <v>1560.348619936198</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1099580536556778</v>
+        <v>0.1105801018780521</v>
       </c>
       <c r="T20">
-        <v>0.6204574137213212</v>
+        <v>0.6264730954521854</v>
       </c>
       <c r="U20">
         <v>0.09808282709314819</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.161679503842176</v>
+        <v>8.679485845745221</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1035466853819958</v>
+        <v>0.1036865851087607</v>
       </c>
       <c r="C21">
-        <v>5665.66291605282</v>
+        <v>5585.622261895458</v>
       </c>
       <c r="D21">
-        <v>6644.620916052821</v>
+        <v>6628.562261895459</v>
       </c>
       <c r="E21">
-        <v>-879.9419999999998</v>
+        <v>-815.9599999999996</v>
       </c>
       <c r="F21">
-        <v>1215.658</v>
+        <v>1279.64</v>
       </c>
       <c r="G21">
         <v>236.7</v>
@@ -3003,28 +3003,28 @@
         <v>1034.9</v>
       </c>
       <c r="M21">
-        <v>119.2351734184024</v>
+        <v>125.5107088614762</v>
       </c>
       <c r="N21">
-        <v>915.6648265815977</v>
+        <v>909.389291138524</v>
       </c>
       <c r="O21">
-        <v>228.9162066453994</v>
+        <v>227.347322784631</v>
       </c>
       <c r="P21">
-        <v>686.7486199361983</v>
+        <v>682.041968353893</v>
       </c>
       <c r="Q21">
-        <v>1560.348619936198</v>
+        <v>1555.641968353893</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1105801018780521</v>
+        <v>0.1112177013059856</v>
       </c>
       <c r="T21">
-        <v>0.6264730954521854</v>
+        <v>0.632639169226321</v>
       </c>
       <c r="U21">
         <v>0.09808282709314819</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.679485845745221</v>
+        <v>8.245511553457959</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1036865851087607</v>
+        <v>0.1038264848355257</v>
       </c>
       <c r="C22">
-        <v>5585.622261895458</v>
+        <v>5505.65904139051</v>
       </c>
       <c r="D22">
-        <v>6628.562261895459</v>
+        <v>6612.58104139051</v>
       </c>
       <c r="E22">
-        <v>-815.9599999999996</v>
+        <v>-751.9779999999996</v>
       </c>
       <c r="F22">
-        <v>1279.64</v>
+        <v>1343.622</v>
       </c>
       <c r="G22">
         <v>236.7</v>
@@ -3085,28 +3085,28 @@
         <v>1034.9</v>
       </c>
       <c r="M22">
-        <v>125.5107088614762</v>
+        <v>131.78624430455</v>
       </c>
       <c r="N22">
-        <v>909.389291138524</v>
+        <v>903.1137556954501</v>
       </c>
       <c r="O22">
-        <v>227.347322784631</v>
+        <v>225.7784389238625</v>
       </c>
       <c r="P22">
-        <v>682.041968353893</v>
+        <v>677.3353167715876</v>
       </c>
       <c r="Q22">
-        <v>1555.641968353893</v>
+        <v>1550.935316771588</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1112177013059856</v>
+        <v>0.1118714424915884</v>
       </c>
       <c r="T22">
-        <v>0.632639169226321</v>
+        <v>0.638961346133979</v>
       </c>
       <c r="U22">
         <v>0.09808282709314819</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.245511553457959</v>
+        <v>7.852868146150437</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1038264848355257</v>
+        <v>0.1040983845622906</v>
       </c>
       <c r="C23">
-        <v>5505.65904139051</v>
+        <v>5410.836410181522</v>
       </c>
       <c r="D23">
-        <v>6612.58104139051</v>
+        <v>6581.740410181523</v>
       </c>
       <c r="E23">
-        <v>-751.9779999999998</v>
+        <v>-687.9959999999996</v>
       </c>
       <c r="F23">
-        <v>1343.622</v>
+        <v>1407.604</v>
       </c>
       <c r="G23">
         <v>236.7</v>
@@ -3167,45 +3167,45 @@
         <v>1034.9</v>
       </c>
       <c r="M23">
-        <v>131.78624430455</v>
+        <v>139.1878629476238</v>
       </c>
       <c r="N23">
-        <v>903.1137556954501</v>
+        <v>895.7121370523763</v>
       </c>
       <c r="O23">
-        <v>225.7784389238625</v>
+        <v>223.9280342630941</v>
       </c>
       <c r="P23">
-        <v>677.3353167715876</v>
+        <v>671.7841027892822</v>
       </c>
       <c r="Q23">
-        <v>1550.935316771588</v>
+        <v>1545.384102789282</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1118714424915884</v>
+        <v>0.1125419462716938</v>
       </c>
       <c r="T23">
-        <v>0.638961346133979</v>
+        <v>0.6454456301418335</v>
       </c>
       <c r="U23">
-        <v>0.09808282709314819</v>
+        <v>0.09888282709314819</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.07356212031986115</v>
+        <v>0.07416212031986114</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.852868146150438</v>
+        <v>7.435274729301876</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1040983845622906</v>
+        <v>0.1042442842890556</v>
       </c>
       <c r="C24">
-        <v>5410.836410181522</v>
+        <v>5330.423819249244</v>
       </c>
       <c r="D24">
-        <v>6581.740410181523</v>
+        <v>6565.309819249244</v>
       </c>
       <c r="E24">
-        <v>-687.9959999999996</v>
+        <v>-624.0139999999997</v>
       </c>
       <c r="F24">
-        <v>1407.604</v>
+        <v>1471.586</v>
       </c>
       <c r="G24">
         <v>236.7</v>
@@ -3249,28 +3249,28 @@
         <v>1034.9</v>
       </c>
       <c r="M24">
-        <v>139.1878629476238</v>
+        <v>145.5145839906976</v>
       </c>
       <c r="N24">
-        <v>895.7121370523763</v>
+        <v>889.3854160093025</v>
       </c>
       <c r="O24">
-        <v>223.9280342630941</v>
+        <v>222.3463540023256</v>
       </c>
       <c r="P24">
-        <v>671.7841027892822</v>
+        <v>667.0390620069769</v>
       </c>
       <c r="Q24">
-        <v>1545.384102789282</v>
+        <v>1540.639062006977</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1125419462716938</v>
+        <v>0.1132298657343994</v>
       </c>
       <c r="T24">
-        <v>0.6454456301418335</v>
+        <v>0.652098337110931</v>
       </c>
       <c r="U24">
         <v>0.09888282709314819</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.435274729301876</v>
+        <v>7.112001914984404</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1042442842890556</v>
+        <v>0.1043901840158206</v>
       </c>
       <c r="C25">
-        <v>5330.423819249244</v>
+        <v>5250.093058362996</v>
       </c>
       <c r="D25">
-        <v>6565.309819249244</v>
+        <v>6548.961058362996</v>
       </c>
       <c r="E25">
-        <v>-624.0139999999997</v>
+        <v>-560.0319999999997</v>
       </c>
       <c r="F25">
-        <v>1471.586</v>
+        <v>1535.568</v>
       </c>
       <c r="G25">
         <v>236.7</v>
@@ -3331,28 +3331,28 @@
         <v>1034.9</v>
       </c>
       <c r="M25">
-        <v>145.5145839906976</v>
+        <v>151.8413050337714</v>
       </c>
       <c r="N25">
-        <v>889.3854160093025</v>
+        <v>883.0586949662287</v>
       </c>
       <c r="O25">
-        <v>222.3463540023256</v>
+        <v>220.7646737415572</v>
       </c>
       <c r="P25">
-        <v>667.0390620069769</v>
+        <v>662.2940212246715</v>
       </c>
       <c r="Q25">
-        <v>1540.639062006977</v>
+        <v>1535.894021224671</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1132298657343994</v>
+        <v>0.1139358883408604</v>
       </c>
       <c r="T25">
-        <v>0.652098337110931</v>
+        <v>0.6589261153160574</v>
       </c>
       <c r="U25">
         <v>0.09888282709314819</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.112001914984404</v>
+        <v>6.815668501860054</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1043901840158206</v>
+        <v>0.1045360837425855</v>
       </c>
       <c r="C26">
-        <v>5250.093058362996</v>
+        <v>5169.843517728234</v>
       </c>
       <c r="D26">
-        <v>6548.961058362996</v>
+        <v>6532.693517728234</v>
       </c>
       <c r="E26">
-        <v>-560.0319999999997</v>
+        <v>-496.0499999999997</v>
       </c>
       <c r="F26">
-        <v>1535.568</v>
+        <v>1599.55</v>
       </c>
       <c r="G26">
         <v>236.7</v>
@@ -3413,28 +3413,28 @@
         <v>1034.9</v>
       </c>
       <c r="M26">
-        <v>151.8413050337714</v>
+        <v>158.1680260768452</v>
       </c>
       <c r="N26">
-        <v>883.0586949662287</v>
+        <v>876.7319739231549</v>
       </c>
       <c r="O26">
-        <v>220.7646737415572</v>
+        <v>219.1829934807887</v>
       </c>
       <c r="P26">
-        <v>662.2940212246715</v>
+        <v>657.5489804423662</v>
       </c>
       <c r="Q26">
-        <v>1535.894021224671</v>
+        <v>1531.148980442366</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1139358883408604</v>
+        <v>0.114660738216827</v>
       </c>
       <c r="T26">
-        <v>0.6589261153160574</v>
+        <v>0.6659359676066536</v>
       </c>
       <c r="U26">
         <v>0.09888282709314819</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.815668501860054</v>
+        <v>6.543041761785652</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1045360837425855</v>
+        <v>0.1046819834693505</v>
       </c>
       <c r="C27">
-        <v>5169.843517728234</v>
+        <v>5089.674593594265</v>
       </c>
       <c r="D27">
-        <v>6532.693517728234</v>
+        <v>6516.506593594266</v>
       </c>
       <c r="E27">
-        <v>-496.0499999999997</v>
+        <v>-432.0679999999998</v>
       </c>
       <c r="F27">
-        <v>1599.55</v>
+        <v>1663.532</v>
       </c>
       <c r="G27">
         <v>236.7</v>
@@ -3495,28 +3495,28 @@
         <v>1034.9</v>
       </c>
       <c r="M27">
-        <v>158.1680260768452</v>
+        <v>164.494747119919</v>
       </c>
       <c r="N27">
-        <v>876.7319739231549</v>
+        <v>870.4052528800811</v>
       </c>
       <c r="O27">
-        <v>219.1829934807887</v>
+        <v>217.6013132200203</v>
       </c>
       <c r="P27">
-        <v>657.5489804423662</v>
+        <v>652.8039396600608</v>
       </c>
       <c r="Q27">
-        <v>1531.148980442366</v>
+        <v>1526.403939660061</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.114660738216827</v>
+        <v>0.1154051786299819</v>
       </c>
       <c r="T27">
-        <v>0.6659359676066536</v>
+        <v>0.6731352753645635</v>
       </c>
       <c r="U27">
         <v>0.09888282709314819</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.543041761785652</v>
+        <v>6.291386309409281</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1046819834693505</v>
+        <v>0.1050303831961154</v>
       </c>
       <c r="C28">
-        <v>5089.674593594265</v>
+        <v>4987.361774272145</v>
       </c>
       <c r="D28">
-        <v>6516.506593594266</v>
+        <v>6478.175774272146</v>
       </c>
       <c r="E28">
-        <v>-432.0679999999998</v>
+        <v>-368.0859999999996</v>
       </c>
       <c r="F28">
-        <v>1663.532</v>
+        <v>1727.514</v>
       </c>
       <c r="G28">
         <v>236.7</v>
@@ -3577,45 +3577,45 @@
         <v>1034.9</v>
       </c>
       <c r="M28">
-        <v>164.494747119919</v>
+        <v>172.5489821629928</v>
       </c>
       <c r="N28">
-        <v>870.4052528800811</v>
+        <v>862.3510178370072</v>
       </c>
       <c r="O28">
-        <v>217.6013132200203</v>
+        <v>215.5877544592518</v>
       </c>
       <c r="P28">
-        <v>652.8039396600608</v>
+        <v>646.7632633777555</v>
       </c>
       <c r="Q28">
-        <v>1526.403939660061</v>
+        <v>1520.363263377755</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1154051786299819</v>
+        <v>0.1161700146708944</v>
       </c>
       <c r="T28">
-        <v>0.6731352753645635</v>
+        <v>0.6805318244309092</v>
       </c>
       <c r="U28">
-        <v>0.09888282709314819</v>
+        <v>0.09988282709314819</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.07416212031986114</v>
+        <v>0.07491212031986114</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.291386309409281</v>
+        <v>5.997717210655089</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1050303831961154</v>
+        <v>0.1051837829228804</v>
       </c>
       <c r="C29">
-        <v>4987.361774272145</v>
+        <v>4906.645400933228</v>
       </c>
       <c r="D29">
-        <v>6478.175774272146</v>
+        <v>6461.441400933229</v>
       </c>
       <c r="E29">
-        <v>-368.0859999999996</v>
+        <v>-304.1039999999996</v>
       </c>
       <c r="F29">
-        <v>1727.514</v>
+        <v>1791.496</v>
       </c>
       <c r="G29">
         <v>236.7</v>
@@ -3659,28 +3659,28 @@
         <v>1034.9</v>
       </c>
       <c r="M29">
-        <v>172.5489821629928</v>
+        <v>178.9396852060667</v>
       </c>
       <c r="N29">
-        <v>862.3510178370072</v>
+        <v>855.9603147939334</v>
       </c>
       <c r="O29">
-        <v>215.5877544592518</v>
+        <v>213.9900786984834</v>
       </c>
       <c r="P29">
-        <v>646.7632633777555</v>
+        <v>641.9702360954501</v>
       </c>
       <c r="Q29">
-        <v>1520.363263377755</v>
+        <v>1515.57023609545</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1161700146708944</v>
+        <v>0.1169560961573879</v>
       </c>
       <c r="T29">
-        <v>0.6805318244309092</v>
+        <v>0.6881338331935422</v>
       </c>
       <c r="U29">
         <v>0.09988282709314819</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.997717210655089</v>
+        <v>5.783513024560264</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1051837829228804</v>
+        <v>0.1053371826496453</v>
       </c>
       <c r="C30">
-        <v>4906.645400933228</v>
+        <v>4826.015261043176</v>
       </c>
       <c r="D30">
-        <v>6461.441400933229</v>
+        <v>6444.793261043177</v>
       </c>
       <c r="E30">
-        <v>-304.1039999999996</v>
+        <v>-240.1219999999994</v>
       </c>
       <c r="F30">
-        <v>1791.496</v>
+        <v>1855.478000000001</v>
       </c>
       <c r="G30">
         <v>236.7</v>
@@ -3741,28 +3741,28 @@
         <v>1034.9</v>
       </c>
       <c r="M30">
-        <v>178.9396852060667</v>
+        <v>185.3303882491405</v>
       </c>
       <c r="N30">
-        <v>855.9603147939334</v>
+        <v>849.5696117508596</v>
       </c>
       <c r="O30">
-        <v>213.9900786984834</v>
+        <v>212.3924029377149</v>
       </c>
       <c r="P30">
-        <v>641.9702360954501</v>
+        <v>637.1772088131447</v>
       </c>
       <c r="Q30">
-        <v>1515.57023609545</v>
+        <v>1510.777208813145</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1169560961573879</v>
+        <v>0.1177643207843459</v>
       </c>
       <c r="T30">
-        <v>0.6881338331935422</v>
+        <v>0.6959499830480803</v>
       </c>
       <c r="U30">
         <v>0.09988282709314819</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.783513024560264</v>
+        <v>5.584081540954737</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1053371826496453</v>
+        <v>0.1054905823764103</v>
       </c>
       <c r="C31">
-        <v>4826.015261043177</v>
+        <v>4745.470689764068</v>
       </c>
       <c r="D31">
-        <v>6444.793261043177</v>
+        <v>6428.230689764068</v>
       </c>
       <c r="E31">
-        <v>-240.1219999999998</v>
+        <v>-176.1399999999999</v>
       </c>
       <c r="F31">
-        <v>1855.478</v>
+        <v>1919.46</v>
       </c>
       <c r="G31">
         <v>236.7</v>
@@ -3823,28 +3823,28 @@
         <v>1034.9</v>
       </c>
       <c r="M31">
-        <v>185.3303882491404</v>
+        <v>191.7210912922142</v>
       </c>
       <c r="N31">
-        <v>849.5696117508596</v>
+        <v>843.1789087077859</v>
       </c>
       <c r="O31">
-        <v>212.3924029377149</v>
+        <v>210.7947271769465</v>
       </c>
       <c r="P31">
-        <v>637.1772088131447</v>
+        <v>632.3841815308394</v>
       </c>
       <c r="Q31">
-        <v>1510.777208813145</v>
+        <v>1505.984181530839</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1177643207843459</v>
+        <v>0.1185956375435028</v>
       </c>
       <c r="T31">
-        <v>0.6959499830480803</v>
+        <v>0.703989451469891</v>
       </c>
       <c r="U31">
         <v>0.09988282709314819</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.584081540954739</v>
+        <v>5.397945489589581</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1054905823764103</v>
+        <v>0.1056439821031752</v>
       </c>
       <c r="C32">
-        <v>4745.470689764068</v>
+        <v>4665.011029074783</v>
       </c>
       <c r="D32">
-        <v>6428.230689764068</v>
+        <v>6411.753029074784</v>
       </c>
       <c r="E32">
-        <v>-176.1399999999999</v>
+        <v>-112.1579999999997</v>
       </c>
       <c r="F32">
-        <v>1919.46</v>
+        <v>1983.442</v>
       </c>
       <c r="G32">
         <v>236.7</v>
@@ -3905,28 +3905,28 @@
         <v>1034.9</v>
       </c>
       <c r="M32">
-        <v>191.7210912922142</v>
+        <v>198.1117943352881</v>
       </c>
       <c r="N32">
-        <v>843.1789087077859</v>
+        <v>836.788205664712</v>
       </c>
       <c r="O32">
-        <v>210.7947271769465</v>
+        <v>209.197051416178</v>
       </c>
       <c r="P32">
-        <v>632.3841815308394</v>
+        <v>627.5911542485339</v>
       </c>
       <c r="Q32">
-        <v>1505.984181530839</v>
+        <v>1501.191154248534</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1185956375435028</v>
+        <v>0.1194510504406062</v>
       </c>
       <c r="T32">
-        <v>0.703989451469891</v>
+        <v>0.7122619479618991</v>
       </c>
       <c r="U32">
         <v>0.09988282709314819</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.397945489589581</v>
+        <v>5.223818215731852</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1056439821031752</v>
+        <v>0.1057973818299402</v>
       </c>
       <c r="C33">
-        <v>4665.011029074783</v>
+        <v>4584.63562768383</v>
       </c>
       <c r="D33">
-        <v>6411.753029074784</v>
+        <v>6395.35962768383</v>
       </c>
       <c r="E33">
-        <v>-112.1579999999997</v>
+        <v>-48.1759999999997</v>
       </c>
       <c r="F33">
-        <v>1983.442</v>
+        <v>2047.424</v>
       </c>
       <c r="G33">
         <v>236.7</v>
@@ -3987,28 +3987,28 @@
         <v>1034.9</v>
       </c>
       <c r="M33">
-        <v>198.1117943352881</v>
+        <v>204.5024973783619</v>
       </c>
       <c r="N33">
-        <v>836.788205664712</v>
+        <v>830.3975026216383</v>
       </c>
       <c r="O33">
-        <v>209.197051416178</v>
+        <v>207.5993756554096</v>
       </c>
       <c r="P33">
-        <v>627.5911542485339</v>
+        <v>622.7981269662287</v>
       </c>
       <c r="Q33">
-        <v>1501.191154248534</v>
+        <v>1496.398126966229</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1194510504406062</v>
+        <v>0.1203316225405657</v>
       </c>
       <c r="T33">
-        <v>0.7122619479618991</v>
+        <v>0.7207777531742605</v>
       </c>
       <c r="U33">
         <v>0.09988282709314819</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.223818215731852</v>
+        <v>5.060573896490232</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1057973818299402</v>
+        <v>0.1059507815567052</v>
       </c>
       <c r="C34">
-        <v>4584.63562768383</v>
+        <v>4504.343840943558</v>
       </c>
       <c r="D34">
-        <v>6395.35962768383</v>
+        <v>6379.04984094356</v>
       </c>
       <c r="E34">
-        <v>-48.1759999999997</v>
+        <v>15.80600000000049</v>
       </c>
       <c r="F34">
-        <v>2047.424</v>
+        <v>2111.406</v>
       </c>
       <c r="G34">
         <v>236.7</v>
@@ -4069,28 +4069,28 @@
         <v>1034.9</v>
       </c>
       <c r="M34">
-        <v>204.5024973783619</v>
+        <v>210.8932004214357</v>
       </c>
       <c r="N34">
-        <v>830.3975026216383</v>
+        <v>824.0067995785644</v>
       </c>
       <c r="O34">
-        <v>207.5993756554096</v>
+        <v>206.0016998946411</v>
       </c>
       <c r="P34">
-        <v>622.7981269662287</v>
+        <v>618.0050996839233</v>
       </c>
       <c r="Q34">
-        <v>1496.398126966229</v>
+        <v>1491.605099683923</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1203316225405657</v>
+        <v>0.1212384803748522</v>
       </c>
       <c r="T34">
-        <v>0.7207777531742605</v>
+        <v>0.7295477615272893</v>
       </c>
       <c r="U34">
         <v>0.09988282709314819</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.060573896490232</v>
+        <v>4.907223172354163</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1059507815567052</v>
+        <v>0.1061041812834701</v>
       </c>
       <c r="C35">
-        <v>4504.343840943558</v>
+        <v>4424.135030765656</v>
       </c>
       <c r="D35">
-        <v>6379.04984094356</v>
+        <v>6362.823030765657</v>
       </c>
       <c r="E35">
-        <v>15.80600000000049</v>
+        <v>79.78800000000047</v>
       </c>
       <c r="F35">
-        <v>2111.406</v>
+        <v>2175.388</v>
       </c>
       <c r="G35">
         <v>236.7</v>
@@ -4151,28 +4151,28 @@
         <v>1034.9</v>
       </c>
       <c r="M35">
-        <v>210.8932004214357</v>
+        <v>217.2839034645095</v>
       </c>
       <c r="N35">
-        <v>824.0067995785644</v>
+        <v>817.6160965354906</v>
       </c>
       <c r="O35">
-        <v>206.0016998946411</v>
+        <v>204.4040241338726</v>
       </c>
       <c r="P35">
-        <v>618.0050996839233</v>
+        <v>613.2120724016179</v>
       </c>
       <c r="Q35">
-        <v>1491.605099683923</v>
+        <v>1486.812072401618</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1212384803748522</v>
+        <v>0.1221728187495717</v>
       </c>
       <c r="T35">
-        <v>0.7295477615272893</v>
+        <v>0.7385835277091978</v>
       </c>
       <c r="U35">
         <v>0.09988282709314819</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.907223172354163</v>
+        <v>4.762893079049629</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1061041812834701</v>
+        <v>0.1062575810102351</v>
       </c>
       <c r="C36">
-        <v>4424.135030765656</v>
+        <v>4344.008565537915</v>
       </c>
       <c r="D36">
-        <v>6362.823030765657</v>
+        <v>6346.678565537915</v>
       </c>
       <c r="E36">
-        <v>79.78800000000047</v>
+        <v>143.7700000000004</v>
       </c>
       <c r="F36">
-        <v>2175.388</v>
+        <v>2239.37</v>
       </c>
       <c r="G36">
         <v>236.7</v>
@@ -4233,28 +4233,28 @@
         <v>1034.9</v>
       </c>
       <c r="M36">
-        <v>217.2839034645095</v>
+        <v>223.6746065075833</v>
       </c>
       <c r="N36">
-        <v>817.6160965354906</v>
+        <v>811.2253934924167</v>
       </c>
       <c r="O36">
-        <v>204.4040241338726</v>
+        <v>202.8063483731042</v>
       </c>
       <c r="P36">
-        <v>613.2120724016179</v>
+        <v>608.4190451193126</v>
       </c>
       <c r="Q36">
-        <v>1486.812072401618</v>
+        <v>1482.019045119313</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1221728187495717</v>
+        <v>0.1231359059973595</v>
       </c>
       <c r="T36">
-        <v>0.7385835277091978</v>
+        <v>0.7478973174659342</v>
       </c>
       <c r="U36">
         <v>0.09988282709314819</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.762893079049629</v>
+        <v>4.626810419648212</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1062575810102351</v>
+        <v>0.1070859807370001</v>
       </c>
       <c r="C37">
-        <v>4344.008565537915</v>
+        <v>4194.238809083156</v>
       </c>
       <c r="D37">
-        <v>6346.678565537915</v>
+        <v>6260.890809083156</v>
       </c>
       <c r="E37">
-        <v>143.7700000000004</v>
+        <v>207.7520000000004</v>
       </c>
       <c r="F37">
-        <v>2239.37</v>
+        <v>2303.352</v>
       </c>
       <c r="G37">
         <v>236.7</v>
@@ -4315,45 +4315,45 @@
         <v>1034.9</v>
       </c>
       <c r="M37">
-        <v>223.6746065075833</v>
+        <v>235.8236895506571</v>
       </c>
       <c r="N37">
-        <v>811.2253934924167</v>
+        <v>799.0763104493429</v>
       </c>
       <c r="O37">
-        <v>202.8063483731042</v>
+        <v>199.7690776123357</v>
       </c>
       <c r="P37">
-        <v>608.4190451193126</v>
+        <v>599.3072328370072</v>
       </c>
       <c r="Q37">
-        <v>1482.019045119313</v>
+        <v>1472.907232837007</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1231359059973595</v>
+        <v>0.1241290897216407</v>
       </c>
       <c r="T37">
-        <v>0.7478973174659342</v>
+        <v>0.7575021631525686</v>
       </c>
       <c r="U37">
-        <v>0.09988282709314819</v>
+        <v>0.1023828270931482</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.07491212031986114</v>
+        <v>0.07678712031986115</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.626810419648212</v>
+        <v>4.388448005253068</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1070859807370001</v>
+        <v>0.107258130463765</v>
       </c>
       <c r="C38">
-        <v>4194.238809083156</v>
+        <v>4112.719493288554</v>
       </c>
       <c r="D38">
-        <v>6260.890809083156</v>
+        <v>6243.353493288555</v>
       </c>
       <c r="E38">
-        <v>207.7520000000004</v>
+        <v>271.7340000000004</v>
       </c>
       <c r="F38">
-        <v>2303.352</v>
+        <v>2367.334</v>
       </c>
       <c r="G38">
         <v>236.7</v>
@@ -4397,28 +4397,28 @@
         <v>1034.9</v>
       </c>
       <c r="M38">
-        <v>235.8236895506571</v>
+        <v>242.3743475937309</v>
       </c>
       <c r="N38">
-        <v>799.0763104493429</v>
+        <v>792.5256524062692</v>
       </c>
       <c r="O38">
-        <v>199.7690776123357</v>
+        <v>198.1314131015673</v>
       </c>
       <c r="P38">
-        <v>599.3072328370072</v>
+        <v>594.3942393047018</v>
       </c>
       <c r="Q38">
-        <v>1472.907232837007</v>
+        <v>1467.994239304702</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1241290897216407</v>
+        <v>0.1251538030879625</v>
       </c>
       <c r="T38">
-        <v>0.7575021631525686</v>
+        <v>0.7674119245752866</v>
       </c>
       <c r="U38">
         <v>0.1023828270931482</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.388448005253068</v>
+        <v>4.269841302408391</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.107258130463765</v>
+        <v>0.10743028019053</v>
       </c>
       <c r="C39">
-        <v>4112.719493288554</v>
+        <v>4031.298150247374</v>
       </c>
       <c r="D39">
-        <v>6243.353493288555</v>
+        <v>6225.914150247374</v>
       </c>
       <c r="E39">
-        <v>271.7340000000004</v>
+        <v>335.7160000000003</v>
       </c>
       <c r="F39">
-        <v>2367.334</v>
+        <v>2431.316</v>
       </c>
       <c r="G39">
         <v>236.7</v>
@@ -4479,28 +4479,28 @@
         <v>1034.9</v>
       </c>
       <c r="M39">
-        <v>242.3743475937309</v>
+        <v>248.9250056368047</v>
       </c>
       <c r="N39">
-        <v>792.5256524062692</v>
+        <v>785.9749943631954</v>
       </c>
       <c r="O39">
-        <v>198.1314131015673</v>
+        <v>196.4937485907988</v>
       </c>
       <c r="P39">
-        <v>594.3942393047018</v>
+        <v>589.4812457723965</v>
       </c>
       <c r="Q39">
-        <v>1467.994239304702</v>
+        <v>1463.081245772396</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1251538030879625</v>
+        <v>0.1262115717241657</v>
       </c>
       <c r="T39">
-        <v>0.7674119245752866</v>
+        <v>0.7776413557213182</v>
       </c>
       <c r="U39">
         <v>0.1023828270931482</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.269841302408391</v>
+        <v>4.157477057608171</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.10743028019053</v>
+        <v>0.1076024299172949</v>
       </c>
       <c r="C40">
-        <v>4031.298150247374</v>
+        <v>3949.973961254782</v>
       </c>
       <c r="D40">
-        <v>6225.914150247374</v>
+        <v>6208.571961254783</v>
       </c>
       <c r="E40">
-        <v>335.7160000000003</v>
+        <v>399.6980000000003</v>
       </c>
       <c r="F40">
-        <v>2431.316</v>
+        <v>2495.298</v>
       </c>
       <c r="G40">
         <v>236.7</v>
@@ -4561,28 +4561,28 @@
         <v>1034.9</v>
       </c>
       <c r="M40">
-        <v>248.9250056368047</v>
+        <v>255.4756636798785</v>
       </c>
       <c r="N40">
-        <v>785.9749943631954</v>
+        <v>779.4243363201216</v>
       </c>
       <c r="O40">
-        <v>196.4937485907988</v>
+        <v>194.8560840800304</v>
       </c>
       <c r="P40">
-        <v>589.4812457723965</v>
+        <v>584.5682522400912</v>
       </c>
       <c r="Q40">
-        <v>1463.081245772396</v>
+        <v>1458.168252240091</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1262115717241657</v>
+        <v>0.1273040212992608</v>
       </c>
       <c r="T40">
-        <v>0.7776413557213182</v>
+        <v>0.7882061780524655</v>
       </c>
       <c r="U40">
         <v>0.1023828270931482</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.157477057608171</v>
+        <v>4.050875081772063</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1076024299172949</v>
+        <v>0.1088245796440599</v>
       </c>
       <c r="C41">
-        <v>3949.973961254782</v>
+        <v>3765.597591805573</v>
       </c>
       <c r="D41">
-        <v>6208.571961254783</v>
+        <v>6088.177591805574</v>
       </c>
       <c r="E41">
-        <v>399.6980000000003</v>
+        <v>463.6800000000007</v>
       </c>
       <c r="F41">
-        <v>2495.298</v>
+        <v>2559.280000000001</v>
       </c>
       <c r="G41">
         <v>236.7</v>
@@ -4643,45 +4643,45 @@
         <v>1034.9</v>
       </c>
       <c r="M41">
-        <v>255.4756636798785</v>
+        <v>270.9838017229524</v>
       </c>
       <c r="N41">
-        <v>779.4243363201216</v>
+        <v>763.9161982770477</v>
       </c>
       <c r="O41">
-        <v>194.8560840800304</v>
+        <v>190.9790495692619</v>
       </c>
       <c r="P41">
-        <v>584.5682522400912</v>
+        <v>572.9371487077858</v>
       </c>
       <c r="Q41">
-        <v>1458.168252240091</v>
+        <v>1446.537148707786</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1273040212992608</v>
+        <v>0.1284328858601924</v>
       </c>
       <c r="T41">
-        <v>0.7882061780524655</v>
+        <v>0.7991231611279844</v>
       </c>
       <c r="U41">
-        <v>0.1023828270931482</v>
+        <v>0.1058828270931482</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.07678712031986115</v>
+        <v>0.07941212031986114</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.050875081772063</v>
+        <v>3.819047461213413</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1088245796440599</v>
+        <v>0.1090229793708248</v>
       </c>
       <c r="C42">
-        <v>3765.597591805573</v>
+        <v>3682.510311055893</v>
       </c>
       <c r="D42">
-        <v>6088.177591805574</v>
+        <v>6069.072311055894</v>
       </c>
       <c r="E42">
-        <v>463.6800000000007</v>
+        <v>527.6620000000007</v>
       </c>
       <c r="F42">
-        <v>2559.280000000001</v>
+        <v>2623.262000000001</v>
       </c>
       <c r="G42">
         <v>236.7</v>
@@ -4725,28 +4725,28 @@
         <v>1034.9</v>
       </c>
       <c r="M42">
-        <v>270.9838017229524</v>
+        <v>277.7583967660262</v>
       </c>
       <c r="N42">
-        <v>763.9161982770477</v>
+        <v>757.1416032339739</v>
       </c>
       <c r="O42">
-        <v>190.9790495692619</v>
+        <v>189.2854008084935</v>
       </c>
       <c r="P42">
-        <v>572.9371487077858</v>
+        <v>567.8562024254804</v>
       </c>
       <c r="Q42">
-        <v>1446.537148707786</v>
+        <v>1441.45620242548</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1284328858601924</v>
+        <v>0.1296000170164098</v>
       </c>
       <c r="T42">
-        <v>0.7991231611279844</v>
+        <v>0.8104102114264023</v>
       </c>
       <c r="U42">
         <v>0.1058828270931482</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.819047461213413</v>
+        <v>3.725899962159427</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1090229793708248</v>
+        <v>0.1092213790975898</v>
       </c>
       <c r="C43">
-        <v>3682.510311055893</v>
+        <v>3599.542563578258</v>
       </c>
       <c r="D43">
-        <v>6069.072311055894</v>
+        <v>6050.086563578258</v>
       </c>
       <c r="E43">
-        <v>527.6620000000007</v>
+        <v>591.6440000000007</v>
       </c>
       <c r="F43">
-        <v>2623.262000000001</v>
+        <v>2687.244000000001</v>
       </c>
       <c r="G43">
         <v>236.7</v>
@@ -4807,28 +4807,28 @@
         <v>1034.9</v>
       </c>
       <c r="M43">
-        <v>277.7583967660262</v>
+        <v>284.5329918091</v>
       </c>
       <c r="N43">
-        <v>757.1416032339739</v>
+        <v>750.3670081909002</v>
       </c>
       <c r="O43">
-        <v>189.2854008084935</v>
+        <v>187.591752047725</v>
       </c>
       <c r="P43">
-        <v>567.8562024254804</v>
+        <v>562.7752561431751</v>
       </c>
       <c r="Q43">
-        <v>1441.45620242548</v>
+        <v>1436.375256143175</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1296000170164098</v>
+        <v>0.1308073940745657</v>
       </c>
       <c r="T43">
-        <v>0.8104102114264023</v>
+        <v>0.8220864703558001</v>
       </c>
       <c r="U43">
         <v>0.1058828270931482</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.725899962159427</v>
+        <v>3.637188058298488</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1092213790975898</v>
+        <v>0.1094197788243547</v>
       </c>
       <c r="C44">
-        <v>3599.542563578256</v>
+        <v>3516.693231070985</v>
       </c>
       <c r="D44">
-        <v>6050.086563578257</v>
+        <v>6031.219231070985</v>
       </c>
       <c r="E44">
-        <v>591.6440000000002</v>
+        <v>655.6260000000002</v>
       </c>
       <c r="F44">
-        <v>2687.244</v>
+        <v>2751.226</v>
       </c>
       <c r="G44">
         <v>236.7</v>
@@ -4889,28 +4889,28 @@
         <v>1034.9</v>
       </c>
       <c r="M44">
-        <v>284.5329918090999</v>
+        <v>291.3075868521738</v>
       </c>
       <c r="N44">
-        <v>750.3670081909002</v>
+        <v>743.5924131478264</v>
       </c>
       <c r="O44">
-        <v>187.591752047725</v>
+        <v>185.8981032869566</v>
       </c>
       <c r="P44">
-        <v>562.7752561431751</v>
+        <v>557.6943098608698</v>
       </c>
       <c r="Q44">
-        <v>1436.375256143175</v>
+        <v>1431.29430986087</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1308073940745657</v>
+        <v>0.1320571352400254</v>
       </c>
       <c r="T44">
-        <v>0.8220864703558001</v>
+        <v>0.8341724225809661</v>
       </c>
       <c r="U44">
         <v>0.1058828270931482</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.637188058298489</v>
+        <v>3.55260228950085</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1094197788243547</v>
+        <v>0.1105421785511197</v>
       </c>
       <c r="C45">
-        <v>3516.693231070985</v>
+        <v>3348.151283158997</v>
       </c>
       <c r="D45">
-        <v>6031.219231070985</v>
+        <v>5926.659283158998</v>
       </c>
       <c r="E45">
-        <v>655.6260000000002</v>
+        <v>719.6080000000006</v>
       </c>
       <c r="F45">
-        <v>2751.226</v>
+        <v>2815.208000000001</v>
       </c>
       <c r="G45">
         <v>236.7</v>
@@ -4971,45 +4971,45 @@
         <v>1034.9</v>
       </c>
       <c r="M45">
-        <v>291.3075868521738</v>
+        <v>305.9647642952476</v>
       </c>
       <c r="N45">
-        <v>743.5924131478264</v>
+        <v>728.9352357047525</v>
       </c>
       <c r="O45">
-        <v>185.8981032869566</v>
+        <v>182.2338089261881</v>
       </c>
       <c r="P45">
-        <v>557.6943098608698</v>
+        <v>546.7014267785644</v>
       </c>
       <c r="Q45">
-        <v>1431.29430986087</v>
+        <v>1420.301426778564</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1320571352400254</v>
+        <v>0.1333515100185372</v>
       </c>
       <c r="T45">
-        <v>0.8341724225809661</v>
+        <v>0.8466900159570312</v>
       </c>
       <c r="U45">
-        <v>0.1058828270931482</v>
+        <v>0.1086828270931482</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.07941212031986114</v>
+        <v>0.08151212031986114</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.55260228950085</v>
+        <v>3.382415626792077</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1105421785511197</v>
+        <v>0.1107615782778847</v>
       </c>
       <c r="C46">
-        <v>3348.151283158997</v>
+        <v>3264.152721649487</v>
       </c>
       <c r="D46">
-        <v>5926.659283158998</v>
+        <v>5906.642721649488</v>
       </c>
       <c r="E46">
-        <v>719.6080000000006</v>
+        <v>783.5900000000006</v>
       </c>
       <c r="F46">
-        <v>2815.208000000001</v>
+        <v>2879.190000000001</v>
       </c>
       <c r="G46">
         <v>236.7</v>
@@ -5053,28 +5053,28 @@
         <v>1034.9</v>
       </c>
       <c r="M46">
-        <v>305.9647642952476</v>
+        <v>312.9185089383214</v>
       </c>
       <c r="N46">
-        <v>728.9352357047525</v>
+        <v>721.9814910616788</v>
       </c>
       <c r="O46">
-        <v>182.2338089261881</v>
+        <v>180.4953727654197</v>
       </c>
       <c r="P46">
-        <v>546.7014267785644</v>
+        <v>541.4861182962591</v>
       </c>
       <c r="Q46">
-        <v>1420.301426778564</v>
+        <v>1415.086118296259</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1333515100185372</v>
+        <v>0.134692952970813</v>
       </c>
       <c r="T46">
-        <v>0.8466900159570312</v>
+        <v>0.8596627945467711</v>
       </c>
       <c r="U46">
         <v>0.1086828270931482</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.382415626792077</v>
+        <v>3.307250835085587</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1107615782778847</v>
+        <v>0.1109809780046496</v>
       </c>
       <c r="C47">
-        <v>3264.152721649487</v>
+        <v>3180.288911972811</v>
       </c>
       <c r="D47">
-        <v>5906.642721649488</v>
+        <v>5886.760911972811</v>
       </c>
       <c r="E47">
-        <v>783.5900000000006</v>
+        <v>847.5720000000006</v>
       </c>
       <c r="F47">
-        <v>2879.190000000001</v>
+        <v>2943.172</v>
       </c>
       <c r="G47">
         <v>236.7</v>
@@ -5135,28 +5135,28 @@
         <v>1034.9</v>
       </c>
       <c r="M47">
-        <v>312.9185089383214</v>
+        <v>319.8722535813952</v>
       </c>
       <c r="N47">
-        <v>721.9814910616788</v>
+        <v>715.0277464186049</v>
       </c>
       <c r="O47">
-        <v>180.4953727654197</v>
+        <v>178.7569366046512</v>
       </c>
       <c r="P47">
-        <v>541.4861182962591</v>
+        <v>536.2708098139537</v>
       </c>
       <c r="Q47">
-        <v>1415.086118296259</v>
+        <v>1409.870809813954</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.134692952970813</v>
+        <v>0.1360840789953953</v>
       </c>
       <c r="T47">
-        <v>0.8596627945467711</v>
+        <v>0.8731160464176125</v>
       </c>
       <c r="U47">
         <v>0.1086828270931482</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.307250835085587</v>
+        <v>3.235354077801118</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1109809780046496</v>
+        <v>0.1112003777314146</v>
       </c>
       <c r="C48">
-        <v>3180.288911972811</v>
+        <v>3096.558497966372</v>
       </c>
       <c r="D48">
-        <v>5886.760911972811</v>
+        <v>5867.012497966372</v>
       </c>
       <c r="E48">
-        <v>847.5720000000006</v>
+        <v>911.5540000000005</v>
       </c>
       <c r="F48">
-        <v>2943.172</v>
+        <v>3007.154</v>
       </c>
       <c r="G48">
         <v>236.7</v>
@@ -5217,28 +5217,28 @@
         <v>1034.9</v>
       </c>
       <c r="M48">
-        <v>319.8722535813952</v>
+        <v>326.825998224469</v>
       </c>
       <c r="N48">
-        <v>715.0277464186049</v>
+        <v>708.0740017755311</v>
       </c>
       <c r="O48">
-        <v>178.7569366046512</v>
+        <v>177.0185004438828</v>
       </c>
       <c r="P48">
-        <v>536.2708098139537</v>
+        <v>531.0555013316483</v>
       </c>
       <c r="Q48">
-        <v>1409.870809813954</v>
+        <v>1404.655501331648</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1360840789953953</v>
+        <v>0.1375277003416601</v>
       </c>
       <c r="T48">
-        <v>0.8731160464176125</v>
+        <v>0.8870769681703726</v>
       </c>
       <c r="U48">
         <v>0.1086828270931482</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.235354077801118</v>
+        <v>3.166516756996839</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1112003777314146</v>
+        <v>0.1114197774581795</v>
       </c>
       <c r="C49">
-        <v>3096.558497966372</v>
+        <v>3012.960141604894</v>
       </c>
       <c r="D49">
-        <v>5867.012497966372</v>
+        <v>5847.396141604895</v>
       </c>
       <c r="E49">
-        <v>911.5540000000005</v>
+        <v>975.5360000000005</v>
       </c>
       <c r="F49">
-        <v>3007.154</v>
+        <v>3071.136</v>
       </c>
       <c r="G49">
         <v>236.7</v>
@@ -5299,28 +5299,28 @@
         <v>1034.9</v>
       </c>
       <c r="M49">
-        <v>326.825998224469</v>
+        <v>333.7797428675428</v>
       </c>
       <c r="N49">
-        <v>708.0740017755311</v>
+        <v>701.1202571324573</v>
       </c>
       <c r="O49">
-        <v>177.0185004438828</v>
+        <v>175.2800642831143</v>
       </c>
       <c r="P49">
-        <v>531.0555013316483</v>
+        <v>525.8401928493429</v>
       </c>
       <c r="Q49">
-        <v>1404.655501331648</v>
+        <v>1399.440192849343</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1375277003416601</v>
+        <v>0.1390268455858581</v>
       </c>
       <c r="T49">
-        <v>0.8870769681703726</v>
+        <v>0.901574848452085</v>
       </c>
       <c r="U49">
         <v>0.1086828270931482</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.166516756996839</v>
+        <v>3.100547657892737</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1114197774581795</v>
+        <v>0.1116391771849445</v>
       </c>
       <c r="C50">
-        <v>3012.960141604894</v>
+        <v>2929.492522698226</v>
       </c>
       <c r="D50">
-        <v>5847.396141604895</v>
+        <v>5827.910522698226</v>
       </c>
       <c r="E50">
-        <v>975.5360000000005</v>
+        <v>1039.518</v>
       </c>
       <c r="F50">
-        <v>3071.136</v>
+        <v>3135.118</v>
       </c>
       <c r="G50">
         <v>236.7</v>
@@ -5381,28 +5381,28 @@
         <v>1034.9</v>
       </c>
       <c r="M50">
-        <v>333.7797428675428</v>
+        <v>340.7334875106166</v>
       </c>
       <c r="N50">
-        <v>701.1202571324573</v>
+        <v>694.1665124893834</v>
       </c>
       <c r="O50">
-        <v>175.2800642831143</v>
+        <v>173.5416281223459</v>
       </c>
       <c r="P50">
-        <v>525.8401928493429</v>
+        <v>520.6248843670376</v>
       </c>
       <c r="Q50">
-        <v>1399.440192849343</v>
+        <v>1394.224884367037</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1390268455858581</v>
+        <v>0.1405847808396324</v>
       </c>
       <c r="T50">
-        <v>0.901574848452085</v>
+        <v>0.9166412730585703</v>
       </c>
       <c r="U50">
         <v>0.1086828270931482</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.100547657892737</v>
+        <v>3.0372711750786</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1116391771849445</v>
+        <v>0.1147835769117095</v>
       </c>
       <c r="C51">
-        <v>2929.492522698226</v>
+        <v>2599.86352270811</v>
       </c>
       <c r="D51">
-        <v>5827.910522698226</v>
+        <v>5562.263522708111</v>
       </c>
       <c r="E51">
-        <v>1039.518</v>
+        <v>1103.5</v>
       </c>
       <c r="F51">
-        <v>3135.118</v>
+        <v>3199.1</v>
       </c>
       <c r="G51">
         <v>236.7</v>
@@ -5463,45 +5463,45 @@
         <v>1034.9</v>
       </c>
       <c r="M51">
-        <v>340.7334875106166</v>
+        <v>372.6402121536904</v>
       </c>
       <c r="N51">
-        <v>694.1665124893834</v>
+        <v>662.2597878463097</v>
       </c>
       <c r="O51">
-        <v>173.5416281223459</v>
+        <v>165.5649469615774</v>
       </c>
       <c r="P51">
-        <v>520.6248843670376</v>
+        <v>496.6948408847322</v>
       </c>
       <c r="Q51">
-        <v>1394.224884367037</v>
+        <v>1370.294840884732</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1405847808396324</v>
+        <v>0.1422050335035578</v>
       </c>
       <c r="T51">
-        <v>0.9166412730585703</v>
+        <v>0.9323103546493152</v>
       </c>
       <c r="U51">
-        <v>0.1086828270931482</v>
+        <v>0.1164828270931482</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.08151212031986114</v>
+        <v>0.08736212031986115</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.0372711750786</v>
+        <v>2.777209668325247</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1147835769117095</v>
+        <v>0.1150614766384744</v>
       </c>
       <c r="C52">
-        <v>2599.86352270811</v>
+        <v>2513.563899865276</v>
       </c>
       <c r="D52">
-        <v>5562.263522708111</v>
+        <v>5539.945899865276</v>
       </c>
       <c r="E52">
-        <v>1103.5</v>
+        <v>1167.482</v>
       </c>
       <c r="F52">
-        <v>3199.1</v>
+        <v>3263.082</v>
       </c>
       <c r="G52">
         <v>236.7</v>
@@ -5545,28 +5545,28 @@
         <v>1034.9</v>
       </c>
       <c r="M52">
-        <v>372.6402121536904</v>
+        <v>380.0930163967643</v>
       </c>
       <c r="N52">
-        <v>662.2597878463097</v>
+        <v>654.8069836032358</v>
       </c>
       <c r="O52">
-        <v>165.5649469615774</v>
+        <v>163.701745900809</v>
       </c>
       <c r="P52">
-        <v>496.6948408847322</v>
+        <v>491.1052377024268</v>
       </c>
       <c r="Q52">
-        <v>1370.294840884732</v>
+        <v>1364.705237702427</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1422050335035578</v>
+        <v>0.143891418929276</v>
       </c>
       <c r="T52">
-        <v>0.9323103546493152</v>
+        <v>0.9486189905907026</v>
       </c>
       <c r="U52">
         <v>0.1164828270931482</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.777209668325247</v>
+        <v>2.722754576789457</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1150614766384744</v>
+        <v>0.1153393763652394</v>
       </c>
       <c r="C53">
-        <v>2513.563899865276</v>
+        <v>2427.442652544748</v>
       </c>
       <c r="D53">
-        <v>5539.945899865276</v>
+        <v>5517.806652544748</v>
       </c>
       <c r="E53">
-        <v>1167.482</v>
+        <v>1231.464</v>
       </c>
       <c r="F53">
-        <v>3263.082</v>
+        <v>3327.064</v>
       </c>
       <c r="G53">
         <v>236.7</v>
@@ -5627,28 +5627,28 @@
         <v>1034.9</v>
       </c>
       <c r="M53">
-        <v>380.0930163967643</v>
+        <v>387.545820639838</v>
       </c>
       <c r="N53">
-        <v>654.8069836032358</v>
+        <v>647.3541793601621</v>
       </c>
       <c r="O53">
-        <v>163.701745900809</v>
+        <v>161.8385448400405</v>
       </c>
       <c r="P53">
-        <v>491.1052377024268</v>
+        <v>485.5156345201216</v>
       </c>
       <c r="Q53">
-        <v>1364.705237702427</v>
+        <v>1359.115634520122</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.143891418929276</v>
+        <v>0.1456480704143991</v>
       </c>
       <c r="T53">
-        <v>0.9486189905907026</v>
+        <v>0.9656071530296478</v>
       </c>
       <c r="U53">
         <v>0.1164828270931482</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.722754576789457</v>
+        <v>2.670393911851199</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1153393763652394</v>
+        <v>0.1156172760920043</v>
       </c>
       <c r="C54">
-        <v>2427.442652544748</v>
+        <v>2341.497650736094</v>
       </c>
       <c r="D54">
-        <v>5517.806652544748</v>
+        <v>5495.843650736095</v>
       </c>
       <c r="E54">
-        <v>1231.464</v>
+        <v>1295.446000000001</v>
       </c>
       <c r="F54">
-        <v>3327.064</v>
+        <v>3391.046000000001</v>
       </c>
       <c r="G54">
         <v>236.7</v>
@@ -5709,28 +5709,28 @@
         <v>1034.9</v>
       </c>
       <c r="M54">
-        <v>387.545820639838</v>
+        <v>394.9986248829119</v>
       </c>
       <c r="N54">
-        <v>647.3541793601621</v>
+        <v>639.9013751170883</v>
       </c>
       <c r="O54">
-        <v>161.8385448400405</v>
+        <v>159.9753437792721</v>
       </c>
       <c r="P54">
-        <v>485.5156345201216</v>
+        <v>479.9260313378162</v>
       </c>
       <c r="Q54">
-        <v>1359.115634520122</v>
+        <v>1353.526031337816</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1456480704143991</v>
+        <v>0.1474794730265488</v>
       </c>
       <c r="T54">
-        <v>0.9656071530296478</v>
+        <v>0.98331821599791</v>
       </c>
       <c r="U54">
         <v>0.1164828270931482</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.670393911851199</v>
+        <v>2.620009121061553</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1156172760920043</v>
+        <v>0.1158951758187693</v>
       </c>
       <c r="C55">
-        <v>2341.497650736094</v>
+        <v>2255.72679820748</v>
       </c>
       <c r="D55">
-        <v>5495.843650736095</v>
+        <v>5474.05479820748</v>
       </c>
       <c r="E55">
-        <v>1295.446000000001</v>
+        <v>1359.428000000001</v>
       </c>
       <c r="F55">
-        <v>3391.046000000001</v>
+        <v>3455.028000000001</v>
       </c>
       <c r="G55">
         <v>236.7</v>
@@ -5791,28 +5791,28 @@
         <v>1034.9</v>
       </c>
       <c r="M55">
-        <v>394.9986248829119</v>
+        <v>402.4514291259857</v>
       </c>
       <c r="N55">
-        <v>639.9013751170883</v>
+        <v>632.4485708740144</v>
       </c>
       <c r="O55">
-        <v>159.9753437792721</v>
+        <v>158.1121427185036</v>
       </c>
       <c r="P55">
-        <v>479.9260313378162</v>
+        <v>474.3364281555108</v>
       </c>
       <c r="Q55">
-        <v>1353.526031337816</v>
+        <v>1347.936428155511</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1474794730265488</v>
+        <v>0.1493905018392267</v>
       </c>
       <c r="T55">
-        <v>0.98331821599791</v>
+        <v>1.001799325182184</v>
       </c>
       <c r="U55">
         <v>0.1164828270931482</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.620009121061553</v>
+        <v>2.571490433634487</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1158951758187693</v>
+        <v>0.1161730755455343</v>
       </c>
       <c r="C56">
-        <v>2255.72679820748</v>
+        <v>2170.128031838728</v>
       </c>
       <c r="D56">
-        <v>5474.05479820748</v>
+        <v>5452.438031838728</v>
       </c>
       <c r="E56">
-        <v>1359.428000000001</v>
+        <v>1423.410000000001</v>
       </c>
       <c r="F56">
-        <v>3455.028000000001</v>
+        <v>3519.010000000001</v>
       </c>
       <c r="G56">
         <v>236.7</v>
@@ -5873,28 +5873,28 @@
         <v>1034.9</v>
       </c>
       <c r="M56">
-        <v>402.4514291259857</v>
+        <v>409.9042333690595</v>
       </c>
       <c r="N56">
-        <v>632.4485708740144</v>
+        <v>624.9957666309406</v>
       </c>
       <c r="O56">
-        <v>158.1121427185036</v>
+        <v>156.2489416577351</v>
       </c>
       <c r="P56">
-        <v>474.3364281555108</v>
+        <v>468.7468249732054</v>
       </c>
       <c r="Q56">
-        <v>1347.936428155511</v>
+        <v>1342.346824973205</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1493905018392267</v>
+        <v>0.1513864652658014</v>
       </c>
       <c r="T56">
-        <v>1.001799325182184</v>
+        <v>1.021101816996869</v>
       </c>
       <c r="U56">
         <v>0.1164828270931482</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.571490433634487</v>
+        <v>2.52473606211386</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1161730755455343</v>
+        <v>0.1180889752722992</v>
       </c>
       <c r="C57">
-        <v>2170.128031838728</v>
+        <v>1961.638179900681</v>
       </c>
       <c r="D57">
-        <v>5452.438031838728</v>
+        <v>5307.930179900682</v>
       </c>
       <c r="E57">
-        <v>1423.410000000001</v>
+        <v>1487.392000000001</v>
       </c>
       <c r="F57">
-        <v>3519.010000000001</v>
+        <v>3582.992000000001</v>
       </c>
       <c r="G57">
         <v>236.7</v>
@@ -5955,45 +5955,45 @@
         <v>1034.9</v>
       </c>
       <c r="M57">
-        <v>409.9042333690595</v>
+        <v>431.3307064121333</v>
       </c>
       <c r="N57">
-        <v>624.9957666309406</v>
+        <v>603.5692935878667</v>
       </c>
       <c r="O57">
-        <v>156.2489416577351</v>
+        <v>150.8923233969667</v>
       </c>
       <c r="P57">
-        <v>468.7468249732054</v>
+        <v>452.6769701909</v>
       </c>
       <c r="Q57">
-        <v>1342.346824973205</v>
+        <v>1326.2769701909</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1513864652658014</v>
+        <v>0.1534731543026749</v>
       </c>
       <c r="T57">
-        <v>1.021101816996869</v>
+        <v>1.041281694803131</v>
       </c>
       <c r="U57">
-        <v>0.1164828270931482</v>
+        <v>0.1203828270931482</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.08736212031986115</v>
+        <v>0.09028712031986116</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.52473606211386</v>
+        <v>2.399319094641875</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1180889752722992</v>
+        <v>0.1183961249990642</v>
       </c>
       <c r="C58">
-        <v>1961.638179900681</v>
+        <v>1875.198654730224</v>
       </c>
       <c r="D58">
-        <v>5307.930179900682</v>
+        <v>5285.472654730225</v>
       </c>
       <c r="E58">
-        <v>1487.392000000001</v>
+        <v>1551.374000000001</v>
       </c>
       <c r="F58">
-        <v>3582.992000000001</v>
+        <v>3646.974000000001</v>
       </c>
       <c r="G58">
         <v>236.7</v>
@@ -6037,28 +6037,28 @@
         <v>1034.9</v>
       </c>
       <c r="M58">
-        <v>431.3307064121333</v>
+        <v>439.0330404552072</v>
       </c>
       <c r="N58">
-        <v>603.5692935878667</v>
+        <v>595.866959544793</v>
       </c>
       <c r="O58">
-        <v>150.8923233969667</v>
+        <v>148.9667398861982</v>
       </c>
       <c r="P58">
-        <v>452.6769701909</v>
+        <v>446.9002196585947</v>
       </c>
       <c r="Q58">
-        <v>1326.2769701909</v>
+        <v>1320.500219658595</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1534731543026749</v>
+        <v>0.1556568986435891</v>
       </c>
       <c r="T58">
-        <v>1.041281694803131</v>
+        <v>1.062400171577127</v>
       </c>
       <c r="U58">
         <v>0.1203828270931482</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.399319094641875</v>
+        <v>2.357225777192017</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1183961249990642</v>
+        <v>0.1187032747258291</v>
       </c>
       <c r="C59">
-        <v>1875.198654730224</v>
+        <v>1788.948361737498</v>
       </c>
       <c r="D59">
-        <v>5285.472654730225</v>
+        <v>5263.204361737499</v>
       </c>
       <c r="E59">
-        <v>1551.374000000001</v>
+        <v>1615.356000000001</v>
       </c>
       <c r="F59">
-        <v>3646.974000000001</v>
+        <v>3710.956000000001</v>
       </c>
       <c r="G59">
         <v>236.7</v>
@@ -6119,28 +6119,28 @@
         <v>1034.9</v>
       </c>
       <c r="M59">
-        <v>439.0330404552072</v>
+        <v>446.735374498281</v>
       </c>
       <c r="N59">
-        <v>595.866959544793</v>
+        <v>588.164625501719</v>
       </c>
       <c r="O59">
-        <v>148.9667398861982</v>
+        <v>147.0411563754298</v>
       </c>
       <c r="P59">
-        <v>446.9002196585947</v>
+        <v>441.1234691262893</v>
       </c>
       <c r="Q59">
-        <v>1320.500219658595</v>
+        <v>1314.723469126289</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1556568986435891</v>
+        <v>0.1579446308102611</v>
       </c>
       <c r="T59">
-        <v>1.062400171577127</v>
+        <v>1.084524290102265</v>
       </c>
       <c r="U59">
         <v>0.1203828270931482</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.357225777192017</v>
+        <v>2.316583953447327</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1187032747258291</v>
+        <v>0.1190104244525941</v>
       </c>
       <c r="C60">
-        <v>1788.948361737499</v>
+        <v>1702.884919187434</v>
       </c>
       <c r="D60">
-        <v>5263.204361737499</v>
+        <v>5241.122919187434</v>
       </c>
       <c r="E60">
-        <v>1615.356</v>
+        <v>1679.338</v>
       </c>
       <c r="F60">
-        <v>3710.956</v>
+        <v>3774.938</v>
       </c>
       <c r="G60">
         <v>236.7</v>
@@ -6201,28 +6201,28 @@
         <v>1034.9</v>
       </c>
       <c r="M60">
-        <v>446.7353744982809</v>
+        <v>454.4377085413547</v>
       </c>
       <c r="N60">
-        <v>588.1646255017192</v>
+        <v>580.4622914586454</v>
       </c>
       <c r="O60">
-        <v>147.0411563754298</v>
+        <v>145.1155728646613</v>
       </c>
       <c r="P60">
-        <v>441.1234691262894</v>
+        <v>435.3467185939841</v>
       </c>
       <c r="Q60">
-        <v>1314.723469126289</v>
+        <v>1308.946718593984</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1579446308102611</v>
+        <v>0.1603439596679902</v>
       </c>
       <c r="T60">
-        <v>1.084524290102264</v>
+        <v>1.107727633921312</v>
       </c>
       <c r="U60">
         <v>0.1203828270931482</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.316583953447328</v>
+        <v>2.277319818643136</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1190104244525941</v>
+        <v>0.119317574179359</v>
       </c>
       <c r="C61">
-        <v>1702.884919187434</v>
+        <v>1617.005985147654</v>
       </c>
       <c r="D61">
-        <v>5241.122919187434</v>
+        <v>5219.225985147655</v>
       </c>
       <c r="E61">
-        <v>1679.338</v>
+        <v>1743.32</v>
       </c>
       <c r="F61">
-        <v>3774.938</v>
+        <v>3838.92</v>
       </c>
       <c r="G61">
         <v>236.7</v>
@@ -6283,28 +6283,28 @@
         <v>1034.9</v>
       </c>
       <c r="M61">
-        <v>454.4377085413547</v>
+        <v>462.1400425844286</v>
       </c>
       <c r="N61">
-        <v>580.4622914586454</v>
+        <v>572.7599574155715</v>
       </c>
       <c r="O61">
-        <v>145.1155728646613</v>
+        <v>143.1899893538929</v>
       </c>
       <c r="P61">
-        <v>435.3467185939841</v>
+        <v>429.5699680616787</v>
       </c>
       <c r="Q61">
-        <v>1308.946718593984</v>
+        <v>1303.169968061678</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1603439596679902</v>
+        <v>0.1628632549686058</v>
       </c>
       <c r="T61">
-        <v>1.107727633921312</v>
+        <v>1.132091144931311</v>
       </c>
       <c r="U61">
         <v>0.1203828270931482</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.277319818643136</v>
+        <v>2.239364488332416</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.119317574179359</v>
+        <v>0.119624723906124</v>
       </c>
       <c r="C62">
-        <v>1617.005985147654</v>
+        <v>1531.309256660471</v>
       </c>
       <c r="D62">
-        <v>5219.225985147655</v>
+        <v>5197.511256660472</v>
       </c>
       <c r="E62">
-        <v>1743.32</v>
+        <v>1807.302000000001</v>
       </c>
       <c r="F62">
-        <v>3838.92</v>
+        <v>3902.902</v>
       </c>
       <c r="G62">
         <v>236.7</v>
@@ -6365,28 +6365,28 @@
         <v>1034.9</v>
       </c>
       <c r="M62">
-        <v>462.1400425844286</v>
+        <v>469.8423766275024</v>
       </c>
       <c r="N62">
-        <v>572.7599574155715</v>
+        <v>565.0576233724977</v>
       </c>
       <c r="O62">
-        <v>143.1899893538929</v>
+        <v>141.2644058431244</v>
       </c>
       <c r="P62">
-        <v>429.5699680616787</v>
+        <v>423.7932175293732</v>
       </c>
       <c r="Q62">
-        <v>1303.169968061678</v>
+        <v>1297.393217529373</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1628632549686058</v>
+        <v>0.1655117449000223</v>
       </c>
       <c r="T62">
-        <v>1.132091144931311</v>
+        <v>1.157704066762337</v>
       </c>
       <c r="U62">
         <v>0.1203828270931482</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.239364488332416</v>
+        <v>2.202653595081065</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.119624723906124</v>
+        <v>0.119931873632889</v>
       </c>
       <c r="C63">
-        <v>1531.309256660471</v>
+        <v>1445.792468935468</v>
       </c>
       <c r="D63">
-        <v>5197.511256660472</v>
+        <v>5175.976468935469</v>
       </c>
       <c r="E63">
-        <v>1807.302000000001</v>
+        <v>1871.284000000001</v>
       </c>
       <c r="F63">
-        <v>3902.902</v>
+        <v>3966.884</v>
       </c>
       <c r="G63">
         <v>236.7</v>
@@ -6447,28 +6447,28 @@
         <v>1034.9</v>
       </c>
       <c r="M63">
-        <v>469.8423766275024</v>
+        <v>477.5447106705762</v>
       </c>
       <c r="N63">
-        <v>565.0576233724977</v>
+        <v>557.3552893294238</v>
       </c>
       <c r="O63">
-        <v>141.2644058431244</v>
+        <v>139.338822332356</v>
       </c>
       <c r="P63">
-        <v>423.7932175293732</v>
+        <v>418.0164669970679</v>
       </c>
       <c r="Q63">
-        <v>1297.393217529373</v>
+        <v>1291.616466997068</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1655117449000223</v>
+        <v>0.1682996290383554</v>
       </c>
       <c r="T63">
-        <v>1.157704066762337</v>
+        <v>1.184665037110784</v>
       </c>
       <c r="U63">
         <v>0.1203828270931482</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.202653595081065</v>
+        <v>2.167126924192661</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.119931873632889</v>
+        <v>0.1202390233596539</v>
       </c>
       <c r="C64">
-        <v>1445.792468935468</v>
+        <v>1360.453394562068</v>
       </c>
       <c r="D64">
-        <v>5175.976468935469</v>
+        <v>5154.619394562069</v>
       </c>
       <c r="E64">
-        <v>1871.284000000001</v>
+        <v>1935.266000000001</v>
       </c>
       <c r="F64">
-        <v>3966.884</v>
+        <v>4030.866</v>
       </c>
       <c r="G64">
         <v>236.7</v>
@@ -6529,28 +6529,28 @@
         <v>1034.9</v>
       </c>
       <c r="M64">
-        <v>477.5447106705762</v>
+        <v>485.24704471365</v>
       </c>
       <c r="N64">
-        <v>557.3552893294238</v>
+        <v>549.6529552863501</v>
       </c>
       <c r="O64">
-        <v>139.338822332356</v>
+        <v>137.4132388215875</v>
       </c>
       <c r="P64">
-        <v>418.0164669970679</v>
+        <v>412.2397164647626</v>
       </c>
       <c r="Q64">
-        <v>1291.616466997068</v>
+        <v>1285.839716464762</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1682996290383554</v>
+        <v>0.1712382096165984</v>
       </c>
       <c r="T64">
-        <v>1.184665037110784</v>
+        <v>1.213083357207796</v>
       </c>
       <c r="U64">
         <v>0.1203828270931482</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.167126924192661</v>
+        <v>2.132728084126111</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1202390233596539</v>
+        <v>0.1205461730864189</v>
       </c>
       <c r="C65">
-        <v>1360.453394562068</v>
+        <v>1275.289842741527</v>
       </c>
       <c r="D65">
-        <v>5154.619394562069</v>
+        <v>5133.437842741528</v>
       </c>
       <c r="E65">
-        <v>1935.266000000001</v>
+        <v>1999.248000000001</v>
       </c>
       <c r="F65">
-        <v>4030.866</v>
+        <v>4094.848</v>
       </c>
       <c r="G65">
         <v>236.7</v>
@@ -6611,28 +6611,28 @@
         <v>1034.9</v>
       </c>
       <c r="M65">
-        <v>485.24704471365</v>
+        <v>492.9493787567238</v>
       </c>
       <c r="N65">
-        <v>549.6529552863501</v>
+        <v>541.9506212432763</v>
       </c>
       <c r="O65">
-        <v>137.4132388215875</v>
+        <v>135.4876553108191</v>
       </c>
       <c r="P65">
-        <v>412.2397164647626</v>
+        <v>406.4629659324572</v>
       </c>
       <c r="Q65">
-        <v>1285.839716464762</v>
+        <v>1280.062965932457</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1712382096165984</v>
+        <v>0.1743400446714104</v>
       </c>
       <c r="T65">
-        <v>1.213083357207796</v>
+        <v>1.243080472865754</v>
       </c>
       <c r="U65">
         <v>0.1203828270931482</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.132728084126111</v>
+        <v>2.099404207811641</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1205461730864189</v>
+        <v>0.1208533228131838</v>
       </c>
       <c r="C66">
-        <v>1275.289842741527</v>
+        <v>1190.299658537776</v>
       </c>
       <c r="D66">
-        <v>5133.437842741528</v>
+        <v>5112.429658537777</v>
       </c>
       <c r="E66">
-        <v>1999.248000000001</v>
+        <v>2063.230000000001</v>
       </c>
       <c r="F66">
-        <v>4094.848</v>
+        <v>4158.830000000001</v>
       </c>
       <c r="G66">
         <v>236.7</v>
@@ -6693,28 +6693,28 @@
         <v>1034.9</v>
       </c>
       <c r="M66">
-        <v>492.9493787567238</v>
+        <v>500.6517127997977</v>
       </c>
       <c r="N66">
-        <v>541.9506212432763</v>
+        <v>534.2482872002024</v>
       </c>
       <c r="O66">
-        <v>135.4876553108191</v>
+        <v>133.5620718000506</v>
       </c>
       <c r="P66">
-        <v>406.4629659324572</v>
+        <v>400.6862154001518</v>
       </c>
       <c r="Q66">
-        <v>1280.062965932457</v>
+        <v>1274.286215400152</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1743400446714104</v>
+        <v>0.1776191274436402</v>
       </c>
       <c r="T66">
-        <v>1.243080472865754</v>
+        <v>1.274791709418452</v>
       </c>
       <c r="U66">
         <v>0.1203828270931482</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.099404207811641</v>
+        <v>2.067105681537615</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1208533228131838</v>
+        <v>0.1211604725399488</v>
       </c>
       <c r="C67">
-        <v>1190.299658537776</v>
+        <v>1105.480722146586</v>
       </c>
       <c r="D67">
-        <v>5112.429658537777</v>
+        <v>5091.592722146587</v>
       </c>
       <c r="E67">
-        <v>2063.230000000001</v>
+        <v>2127.212000000001</v>
       </c>
       <c r="F67">
-        <v>4158.830000000001</v>
+        <v>4222.812000000001</v>
       </c>
       <c r="G67">
         <v>236.7</v>
@@ -6775,28 +6775,28 @@
         <v>1034.9</v>
       </c>
       <c r="M67">
-        <v>500.6517127997977</v>
+        <v>508.3540468428715</v>
       </c>
       <c r="N67">
-        <v>534.2482872002024</v>
+        <v>526.5459531571287</v>
       </c>
       <c r="O67">
-        <v>133.5620718000506</v>
+        <v>131.6364882892822</v>
       </c>
       <c r="P67">
-        <v>400.6862154001518</v>
+        <v>394.9094648678465</v>
       </c>
       <c r="Q67">
-        <v>1274.286215400152</v>
+        <v>1268.509464867846</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1776191274436402</v>
+        <v>0.1810910974377659</v>
       </c>
       <c r="T67">
-        <v>1.274791709418452</v>
+        <v>1.30836831282719</v>
       </c>
       <c r="U67">
         <v>0.1203828270931482</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.067105681537615</v>
+        <v>2.035785898484015</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1211604725399488</v>
+        <v>0.1214676222667138</v>
       </c>
       <c r="C68">
-        <v>1105.480722146586</v>
+        <v>1020.830948182532</v>
       </c>
       <c r="D68">
-        <v>5091.592722146587</v>
+        <v>5070.924948182533</v>
       </c>
       <c r="E68">
-        <v>2127.212000000001</v>
+        <v>2191.194000000001</v>
       </c>
       <c r="F68">
-        <v>4222.812000000001</v>
+        <v>4286.794000000001</v>
       </c>
       <c r="G68">
         <v>236.7</v>
@@ -6857,28 +6857,28 @@
         <v>1034.9</v>
       </c>
       <c r="M68">
-        <v>508.3540468428715</v>
+        <v>516.0563808859453</v>
       </c>
       <c r="N68">
-        <v>526.5459531571287</v>
+        <v>518.8436191140548</v>
       </c>
       <c r="O68">
-        <v>131.6364882892822</v>
+        <v>129.7109047785137</v>
       </c>
       <c r="P68">
-        <v>394.9094648678465</v>
+        <v>389.1327143355411</v>
       </c>
       <c r="Q68">
-        <v>1268.509464867846</v>
+        <v>1262.732714335541</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1810910974377659</v>
+        <v>0.1847734898557781</v>
       </c>
       <c r="T68">
-        <v>1.30836831282719</v>
+        <v>1.343979861897065</v>
       </c>
       <c r="U68">
         <v>0.1203828270931482</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.035785898484015</v>
+        <v>2.005401034327537</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1214676222667138</v>
+        <v>0.1290167719934787</v>
       </c>
       <c r="C69">
-        <v>1020.830948182532</v>
+        <v>496.8314448597921</v>
       </c>
       <c r="D69">
-        <v>5070.924948182533</v>
+        <v>4610.907444859793</v>
       </c>
       <c r="E69">
-        <v>2191.194000000001</v>
+        <v>2255.176000000001</v>
       </c>
       <c r="F69">
-        <v>4286.794000000001</v>
+        <v>4350.776000000001</v>
       </c>
       <c r="G69">
         <v>236.7</v>
@@ -6939,45 +6939,45 @@
         <v>1034.9</v>
       </c>
       <c r="M69">
-        <v>516.0563808859453</v>
+        <v>585.5397341290191</v>
       </c>
       <c r="N69">
-        <v>518.8436191140548</v>
+        <v>449.360265870981</v>
       </c>
       <c r="O69">
-        <v>129.7109047785137</v>
+        <v>112.3400664677453</v>
       </c>
       <c r="P69">
-        <v>389.1327143355411</v>
+        <v>337.0201994032358</v>
       </c>
       <c r="Q69">
-        <v>1262.732714335541</v>
+        <v>1210.620199403236</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1847734898557781</v>
+        <v>0.188686031799916</v>
       </c>
       <c r="T69">
-        <v>1.343979861897065</v>
+        <v>1.381817132783807</v>
       </c>
       <c r="U69">
-        <v>0.1203828270931482</v>
+        <v>0.1345828270931482</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.09028712031986116</v>
+        <v>0.1009371203198612</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.005401034327537</v>
+        <v>1.767429159251502</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1290167719934787</v>
+        <v>0.1294304217202437</v>
       </c>
       <c r="C70">
-        <v>496.8314448597921</v>
+        <v>410.0431434509001</v>
       </c>
       <c r="D70">
-        <v>4610.907444859793</v>
+        <v>4588.101143450901</v>
       </c>
       <c r="E70">
-        <v>2255.176000000001</v>
+        <v>2319.158000000001</v>
       </c>
       <c r="F70">
-        <v>4350.776000000001</v>
+        <v>4414.758000000001</v>
       </c>
       <c r="G70">
         <v>236.7</v>
@@ -7021,28 +7021,28 @@
         <v>1034.9</v>
       </c>
       <c r="M70">
-        <v>585.5397341290191</v>
+        <v>594.1506125720929</v>
       </c>
       <c r="N70">
-        <v>449.360265870981</v>
+        <v>440.7493874279072</v>
       </c>
       <c r="O70">
-        <v>112.3400664677453</v>
+        <v>110.1873468569768</v>
       </c>
       <c r="P70">
-        <v>337.0201994032358</v>
+        <v>330.5620405709304</v>
       </c>
       <c r="Q70">
-        <v>1210.620199403236</v>
+        <v>1204.16204057093</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.188686031799916</v>
+        <v>0.192850995804966</v>
       </c>
       <c r="T70">
-        <v>1.381817132783807</v>
+        <v>1.422095517921306</v>
       </c>
       <c r="U70">
         <v>0.1345828270931482</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.767429159251502</v>
+        <v>1.741814243900031</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1294304217202437</v>
+        <v>0.1298440714470086</v>
       </c>
       <c r="C71">
-        <v>410.0431434509001</v>
+        <v>323.4793390275499</v>
       </c>
       <c r="D71">
-        <v>4588.101143450901</v>
+        <v>4565.519339027551</v>
       </c>
       <c r="E71">
-        <v>2319.158000000001</v>
+        <v>2383.140000000001</v>
       </c>
       <c r="F71">
-        <v>4414.758000000001</v>
+        <v>4478.740000000001</v>
       </c>
       <c r="G71">
         <v>236.7</v>
@@ -7103,28 +7103,28 @@
         <v>1034.9</v>
       </c>
       <c r="M71">
-        <v>594.1506125720929</v>
+        <v>602.7614910151667</v>
       </c>
       <c r="N71">
-        <v>440.7493874279072</v>
+        <v>432.1385089848334</v>
       </c>
       <c r="O71">
-        <v>110.1873468569768</v>
+        <v>108.0346272462083</v>
       </c>
       <c r="P71">
-        <v>330.5620405709304</v>
+        <v>324.103881738625</v>
       </c>
       <c r="Q71">
-        <v>1204.16204057093</v>
+        <v>1197.703881738625</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.192850995804966</v>
+        <v>0.1972936240770194</v>
       </c>
       <c r="T71">
-        <v>1.422095517921306</v>
+        <v>1.465059128734638</v>
       </c>
       <c r="U71">
         <v>0.1345828270931482</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.741814243900031</v>
+        <v>1.716931183272887</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1298440714470086</v>
+        <v>0.1302577211737736</v>
       </c>
       <c r="C72">
-        <v>323.4793390275499</v>
+        <v>237.1367330239473</v>
       </c>
       <c r="D72">
-        <v>4565.519339027551</v>
+        <v>4543.158733023948</v>
       </c>
       <c r="E72">
-        <v>2383.140000000001</v>
+        <v>2447.122000000001</v>
       </c>
       <c r="F72">
-        <v>4478.740000000001</v>
+        <v>4542.722000000001</v>
       </c>
       <c r="G72">
         <v>236.7</v>
@@ -7185,28 +7185,28 @@
         <v>1034.9</v>
       </c>
       <c r="M72">
-        <v>602.7614910151667</v>
+        <v>611.3723694582404</v>
       </c>
       <c r="N72">
-        <v>432.1385089848334</v>
+        <v>423.5276305417597</v>
       </c>
       <c r="O72">
-        <v>108.0346272462083</v>
+        <v>105.8819076354399</v>
       </c>
       <c r="P72">
-        <v>324.103881738625</v>
+        <v>317.6457229063197</v>
       </c>
       <c r="Q72">
-        <v>1197.703881738625</v>
+        <v>1191.24572290632</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1972936240770194</v>
+        <v>0.2020426405057661</v>
       </c>
       <c r="T72">
-        <v>1.465059128734638</v>
+        <v>1.51098574719027</v>
       </c>
       <c r="U72">
         <v>0.1345828270931482</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.716931183272887</v>
+        <v>1.692749053931016</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1302577211737736</v>
+        <v>0.1306713709005385</v>
       </c>
       <c r="C73">
-        <v>237.1367330239473</v>
+        <v>151.0120911810618</v>
       </c>
       <c r="D73">
-        <v>4543.158733023948</v>
+        <v>4521.016091181063</v>
       </c>
       <c r="E73">
-        <v>2447.122000000001</v>
+        <v>2511.104000000001</v>
       </c>
       <c r="F73">
-        <v>4542.722000000001</v>
+        <v>4606.704000000001</v>
       </c>
       <c r="G73">
         <v>236.7</v>
@@ -7267,28 +7267,28 @@
         <v>1034.9</v>
       </c>
       <c r="M73">
-        <v>611.3723694582404</v>
+        <v>619.9832479013143</v>
       </c>
       <c r="N73">
-        <v>423.5276305417597</v>
+        <v>414.9167520986858</v>
       </c>
       <c r="O73">
-        <v>105.8819076354399</v>
+        <v>103.7291880246715</v>
       </c>
       <c r="P73">
-        <v>317.6457229063197</v>
+        <v>311.1875640740144</v>
       </c>
       <c r="Q73">
-        <v>1191.24572290632</v>
+        <v>1184.787564074014</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.202042640505766</v>
+        <v>0.2071308723937089</v>
       </c>
       <c r="T73">
-        <v>1.510985747190269</v>
+        <v>1.560192838392731</v>
       </c>
       <c r="U73">
         <v>0.1345828270931482</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.692749053931016</v>
+        <v>1.669238650404196</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1306713709005385</v>
+        <v>0.1310850206273035</v>
       </c>
       <c r="C74">
-        <v>151.0120911810618</v>
+        <v>65.10224198712967</v>
       </c>
       <c r="D74">
-        <v>4521.016091181063</v>
+        <v>4499.08824198713</v>
       </c>
       <c r="E74">
-        <v>2511.104000000001</v>
+        <v>2575.086000000001</v>
       </c>
       <c r="F74">
-        <v>4606.704000000001</v>
+        <v>4670.686000000001</v>
       </c>
       <c r="G74">
         <v>236.7</v>
@@ -7349,28 +7349,28 @@
         <v>1034.9</v>
       </c>
       <c r="M74">
-        <v>619.9832479013143</v>
+        <v>628.5941263443881</v>
       </c>
       <c r="N74">
-        <v>414.9167520986858</v>
+        <v>406.305873655612</v>
       </c>
       <c r="O74">
-        <v>103.7291880246715</v>
+        <v>101.576468413903</v>
       </c>
       <c r="P74">
-        <v>311.1875640740144</v>
+        <v>304.729405241709</v>
       </c>
       <c r="Q74">
-        <v>1184.787564074014</v>
+        <v>1178.329405241709</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2071308723937089</v>
+        <v>0.2125960103474253</v>
       </c>
       <c r="T74">
-        <v>1.560192838392731</v>
+        <v>1.613044899313894</v>
       </c>
       <c r="U74">
         <v>0.1345828270931482</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.669238650404196</v>
+        <v>1.646372367521947</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1310850206273035</v>
+        <v>0.1314986703540684</v>
       </c>
       <c r="C75">
-        <v>65.10224198712967</v>
+        <v>-20.59592483669985</v>
       </c>
       <c r="D75">
-        <v>4499.08824198713</v>
+        <v>4477.372075163301</v>
       </c>
       <c r="E75">
-        <v>2575.086000000001</v>
+        <v>2639.068000000001</v>
       </c>
       <c r="F75">
-        <v>4670.686000000001</v>
+        <v>4734.668000000001</v>
       </c>
       <c r="G75">
         <v>236.7</v>
@@ -7431,28 +7431,28 @@
         <v>1034.9</v>
       </c>
       <c r="M75">
-        <v>628.5941263443881</v>
+        <v>637.2050047874619</v>
       </c>
       <c r="N75">
-        <v>406.305873655612</v>
+        <v>397.6949952125382</v>
       </c>
       <c r="O75">
-        <v>101.576468413903</v>
+        <v>99.42374880313454</v>
       </c>
       <c r="P75">
-        <v>304.729405241709</v>
+        <v>298.2712464094036</v>
       </c>
       <c r="Q75">
-        <v>1178.329405241709</v>
+        <v>1171.871246409404</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2125960103474253</v>
+        <v>0.2184815435283507</v>
       </c>
       <c r="T75">
-        <v>1.613044899313894</v>
+        <v>1.669962503382839</v>
       </c>
       <c r="U75">
         <v>0.1345828270931482</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.646372367521947</v>
+        <v>1.624124092285164</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1314986703540684</v>
+        <v>0.1319123200808334</v>
       </c>
       <c r="C76">
-        <v>-20.59592483669985</v>
+        <v>-106.08545980705</v>
       </c>
       <c r="D76">
-        <v>4477.372075163301</v>
+        <v>4455.864540192951</v>
       </c>
       <c r="E76">
-        <v>2639.068000000001</v>
+        <v>2703.050000000001</v>
       </c>
       <c r="F76">
-        <v>4734.668000000001</v>
+        <v>4798.650000000001</v>
       </c>
       <c r="G76">
         <v>236.7</v>
@@ -7513,28 +7513,28 @@
         <v>1034.9</v>
       </c>
       <c r="M76">
-        <v>637.2050047874619</v>
+        <v>645.8158832305356</v>
       </c>
       <c r="N76">
-        <v>397.6949952125382</v>
+        <v>389.0841167694645</v>
       </c>
       <c r="O76">
-        <v>99.42374880313454</v>
+        <v>97.27102919236611</v>
       </c>
       <c r="P76">
-        <v>298.2712464094036</v>
+        <v>291.8130875770984</v>
       </c>
       <c r="Q76">
-        <v>1171.871246409404</v>
+        <v>1165.413087577098</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2184815435283507</v>
+        <v>0.2248379193637501</v>
       </c>
       <c r="T76">
-        <v>1.669962503382839</v>
+        <v>1.7314335157773</v>
       </c>
       <c r="U76">
         <v>0.1345828270931482</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.624124092285164</v>
+        <v>1.602469104388029</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1319123200808334</v>
+        <v>0.1323259698075984</v>
       </c>
       <c r="C77">
-        <v>-106.08545980705</v>
+        <v>-191.3693551068191</v>
       </c>
       <c r="D77">
-        <v>4455.864540192951</v>
+        <v>4434.562644893182</v>
       </c>
       <c r="E77">
-        <v>2703.050000000001</v>
+        <v>2767.032000000001</v>
       </c>
       <c r="F77">
-        <v>4798.650000000001</v>
+        <v>4862.632000000001</v>
       </c>
       <c r="G77">
         <v>236.7</v>
@@ -7595,28 +7595,28 @@
         <v>1034.9</v>
       </c>
       <c r="M77">
-        <v>645.8158832305356</v>
+        <v>654.4267616736095</v>
       </c>
       <c r="N77">
-        <v>389.0841167694645</v>
+        <v>380.4732383263906</v>
       </c>
       <c r="O77">
-        <v>97.27102919236611</v>
+        <v>95.11830958159766</v>
       </c>
       <c r="P77">
-        <v>291.8130875770984</v>
+        <v>285.354928744793</v>
       </c>
       <c r="Q77">
-        <v>1165.413087577098</v>
+        <v>1158.954928744793</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2248379193637501</v>
+        <v>0.2317239931854328</v>
       </c>
       <c r="T77">
-        <v>1.7314335157773</v>
+        <v>1.798027112537965</v>
       </c>
       <c r="U77">
         <v>0.1345828270931482</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.602469104388029</v>
+        <v>1.581383984593449</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1323259698075984</v>
+        <v>0.1327396195343633</v>
       </c>
       <c r="C78">
-        <v>-191.3693551068191</v>
+        <v>-276.4505459729244</v>
       </c>
       <c r="D78">
-        <v>4434.562644893182</v>
+        <v>4413.463454027076</v>
       </c>
       <c r="E78">
-        <v>2767.032000000001</v>
+        <v>2831.014000000001</v>
       </c>
       <c r="F78">
-        <v>4862.632000000001</v>
+        <v>4926.614</v>
       </c>
       <c r="G78">
         <v>236.7</v>
@@ -7677,28 +7677,28 @@
         <v>1034.9</v>
       </c>
       <c r="M78">
-        <v>654.4267616736095</v>
+        <v>663.0376401166833</v>
       </c>
       <c r="N78">
-        <v>380.4732383263906</v>
+        <v>371.8623598833168</v>
       </c>
       <c r="O78">
-        <v>95.11830958159766</v>
+        <v>92.9655899708292</v>
       </c>
       <c r="P78">
-        <v>285.354928744793</v>
+        <v>278.8967699124876</v>
       </c>
       <c r="Q78">
-        <v>1158.954928744793</v>
+        <v>1152.496769912487</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2317239931854328</v>
+        <v>0.2392088560350879</v>
       </c>
       <c r="T78">
-        <v>1.798027112537965</v>
+        <v>1.870411456843036</v>
       </c>
       <c r="U78">
         <v>0.1345828270931482</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.581383984593449</v>
+        <v>1.56084653024808</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1327396195343633</v>
+        <v>0.1331532692611283</v>
       </c>
       <c r="C79">
-        <v>-276.4505459729244</v>
+        <v>-361.331912044594</v>
       </c>
       <c r="D79">
-        <v>4413.463454027076</v>
+        <v>4392.564087955407</v>
       </c>
       <c r="E79">
-        <v>2831.014000000001</v>
+        <v>2894.996000000001</v>
       </c>
       <c r="F79">
-        <v>4926.614</v>
+        <v>4990.596</v>
       </c>
       <c r="G79">
         <v>236.7</v>
@@ -7759,28 +7759,28 @@
         <v>1034.9</v>
       </c>
       <c r="M79">
-        <v>663.0376401166833</v>
+        <v>671.6485185597571</v>
       </c>
       <c r="N79">
-        <v>371.8623598833168</v>
+        <v>363.251481440243</v>
       </c>
       <c r="O79">
-        <v>92.9655899708292</v>
+        <v>90.81287036006074</v>
       </c>
       <c r="P79">
-        <v>278.8967699124876</v>
+        <v>272.4386110801822</v>
       </c>
       <c r="Q79">
-        <v>1152.496769912487</v>
+        <v>1146.038611080182</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2392088560350879</v>
+        <v>0.2473741609619844</v>
       </c>
       <c r="T79">
-        <v>1.870411456843036</v>
+        <v>1.949376196084932</v>
       </c>
       <c r="U79">
         <v>0.1345828270931482</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.56084653024808</v>
+        <v>1.540835677296181</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1331532692611283</v>
+        <v>0.1335669189878932</v>
       </c>
       <c r="C80">
-        <v>-361.331912044594</v>
+        <v>-446.0162786735391</v>
       </c>
       <c r="D80">
-        <v>4392.564087955407</v>
+        <v>4371.861721326462</v>
       </c>
       <c r="E80">
-        <v>2894.996000000001</v>
+        <v>2958.978000000001</v>
       </c>
       <c r="F80">
-        <v>4990.596</v>
+        <v>5054.578</v>
       </c>
       <c r="G80">
         <v>236.7</v>
@@ -7841,28 +7841,28 @@
         <v>1034.9</v>
       </c>
       <c r="M80">
-        <v>671.6485185597571</v>
+        <v>680.259397002831</v>
       </c>
       <c r="N80">
-        <v>363.251481440243</v>
+        <v>354.6406029971691</v>
       </c>
       <c r="O80">
-        <v>90.81287036006074</v>
+        <v>88.66015074929228</v>
       </c>
       <c r="P80">
-        <v>272.4386110801822</v>
+        <v>265.9804522478769</v>
       </c>
       <c r="Q80">
-        <v>1146.038611080182</v>
+        <v>1139.580452247877</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2473741609619844</v>
+        <v>0.2563171139771568</v>
       </c>
       <c r="T80">
-        <v>1.949376196084932</v>
+        <v>2.035861386683199</v>
       </c>
       <c r="U80">
         <v>0.1345828270931482</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.540835677296181</v>
+        <v>1.521331428216483</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1335669189878932</v>
+        <v>0.1339805687146582</v>
       </c>
       <c r="C81">
-        <v>-446.0162786735391</v>
+        <v>-530.5064181972566</v>
       </c>
       <c r="D81">
-        <v>4371.861721326462</v>
+        <v>4351.353581802745</v>
       </c>
       <c r="E81">
-        <v>2958.978000000001</v>
+        <v>3022.960000000001</v>
       </c>
       <c r="F81">
-        <v>5054.578</v>
+        <v>5118.560000000001</v>
       </c>
       <c r="G81">
         <v>236.7</v>
@@ -7923,28 +7923,28 @@
         <v>1034.9</v>
       </c>
       <c r="M81">
-        <v>680.259397002831</v>
+        <v>688.8702754459048</v>
       </c>
       <c r="N81">
-        <v>354.6406029971691</v>
+        <v>346.0297245540953</v>
       </c>
       <c r="O81">
-        <v>88.66015074929228</v>
+        <v>86.50743113852383</v>
       </c>
       <c r="P81">
-        <v>265.9804522478769</v>
+        <v>259.5222934155715</v>
       </c>
       <c r="Q81">
-        <v>1139.580452247877</v>
+        <v>1133.122293415571</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2563171139771568</v>
+        <v>0.2661543622938464</v>
       </c>
       <c r="T81">
-        <v>2.035861386683199</v>
+        <v>2.130995096341292</v>
       </c>
       <c r="U81">
         <v>0.1345828270931482</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.521331428216483</v>
+        <v>1.502314785363777</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1339805687146582</v>
+        <v>0.1689002184414232</v>
       </c>
       <c r="C82">
-        <v>-530.5064181972566</v>
+        <v>-1828.830199533411</v>
       </c>
       <c r="D82">
-        <v>4351.353581802745</v>
+        <v>3117.01180046659</v>
       </c>
       <c r="E82">
-        <v>3022.960000000001</v>
+        <v>3086.942000000001</v>
       </c>
       <c r="F82">
-        <v>5118.560000000001</v>
+        <v>5182.542000000001</v>
       </c>
       <c r="G82">
         <v>236.7</v>
@@ -8005,45 +8005,45 @@
         <v>1034.9</v>
       </c>
       <c r="M82">
-        <v>688.8702754459048</v>
+        <v>991.8495394889787</v>
       </c>
       <c r="N82">
-        <v>346.0297245540953</v>
+        <v>43.05046051102136</v>
       </c>
       <c r="O82">
-        <v>86.50743113852383</v>
+        <v>10.76261512775534</v>
       </c>
       <c r="P82">
-        <v>259.5222934155715</v>
+        <v>32.28784538326602</v>
       </c>
       <c r="Q82">
-        <v>1133.122293415571</v>
+        <v>905.8878453832659</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2661543622938464</v>
+        <v>0.2770271104333454</v>
       </c>
       <c r="T82">
-        <v>2.130995096341292</v>
+        <v>2.236142880700238</v>
       </c>
       <c r="U82">
-        <v>0.1345828270931482</v>
+        <v>0.1913828270931482</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.1009371203198612</v>
+        <v>0.1435371203198612</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.502314785363777</v>
+        <v>1.043404224932344</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1689002184414232</v>
+        <v>0.1697398681681881</v>
       </c>
       <c r="C83">
-        <v>-1828.830199533411</v>
+        <v>-1913.928876073951</v>
       </c>
       <c r="D83">
-        <v>3117.01180046659</v>
+        <v>3095.89512392605</v>
       </c>
       <c r="E83">
-        <v>3086.942000000001</v>
+        <v>3150.924000000001</v>
       </c>
       <c r="F83">
-        <v>5182.542000000001</v>
+        <v>5246.524000000001</v>
       </c>
       <c r="G83">
         <v>236.7</v>
@@ -8087,28 +8087,28 @@
         <v>1034.9</v>
       </c>
       <c r="M83">
-        <v>991.8495394889787</v>
+        <v>1004.094595532053</v>
       </c>
       <c r="N83">
-        <v>43.05046051102136</v>
+        <v>30.80540446794748</v>
       </c>
       <c r="O83">
-        <v>10.76261512775534</v>
+        <v>7.701351116986871</v>
       </c>
       <c r="P83">
-        <v>32.28784538326602</v>
+        <v>23.10405335096061</v>
       </c>
       <c r="Q83">
-        <v>905.8878453832659</v>
+        <v>896.7040533509605</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2770271104333454</v>
+        <v>0.2891079416994553</v>
       </c>
       <c r="T83">
-        <v>2.236142880700238</v>
+        <v>2.352973752210177</v>
       </c>
       <c r="U83">
         <v>0.1913828270931482</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.043404224932344</v>
+        <v>1.030679783164876</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1697398681681881</v>
+        <v>0.1705795178949531</v>
       </c>
       <c r="C84">
-        <v>-1913.928876073951</v>
+        <v>-1998.74336155515</v>
       </c>
       <c r="D84">
-        <v>3095.89512392605</v>
+        <v>3075.062638444851</v>
       </c>
       <c r="E84">
-        <v>3150.924000000001</v>
+        <v>3214.906000000001</v>
       </c>
       <c r="F84">
-        <v>5246.524000000001</v>
+        <v>5310.506000000001</v>
       </c>
       <c r="G84">
         <v>236.7</v>
@@ -8169,28 +8169,28 @@
         <v>1034.9</v>
       </c>
       <c r="M84">
-        <v>1004.094595532053</v>
+        <v>1016.339651575126</v>
       </c>
       <c r="N84">
-        <v>30.80540446794748</v>
+        <v>18.56034842487372</v>
       </c>
       <c r="O84">
-        <v>7.701351116986871</v>
+        <v>4.640087106218431</v>
       </c>
       <c r="P84">
-        <v>23.10405335096061</v>
+        <v>13.92026131865529</v>
       </c>
       <c r="Q84">
-        <v>896.7040533509605</v>
+        <v>887.5202613186552</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2891079416994553</v>
+        <v>0.3026100472321666</v>
       </c>
       <c r="T84">
-        <v>2.352973752210177</v>
+        <v>2.483549432133051</v>
       </c>
       <c r="U84">
         <v>0.1913828270931482</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.030679783164876</v>
+        <v>1.018261954452046</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1705795178949531</v>
+        <v>0.171419167621718</v>
       </c>
       <c r="C85">
-        <v>-1998.74336155515</v>
+        <v>-2083.279354652211</v>
       </c>
       <c r="D85">
-        <v>3075.062638444851</v>
+        <v>3054.508645347791</v>
       </c>
       <c r="E85">
-        <v>3214.906000000001</v>
+        <v>3278.888000000001</v>
       </c>
       <c r="F85">
-        <v>5310.506000000001</v>
+        <v>5374.488000000001</v>
       </c>
       <c r="G85">
         <v>236.7</v>
@@ -8251,28 +8251,28 @@
         <v>1034.9</v>
       </c>
       <c r="M85">
-        <v>1016.339651575126</v>
+        <v>1028.5847076182</v>
       </c>
       <c r="N85">
-        <v>18.56034842487372</v>
+        <v>6.315292381799964</v>
       </c>
       <c r="O85">
-        <v>4.640087106218431</v>
+        <v>1.578823095449991</v>
       </c>
       <c r="P85">
-        <v>13.92026131865529</v>
+        <v>4.736469286349973</v>
       </c>
       <c r="Q85">
-        <v>887.5202613186552</v>
+        <v>878.3364692863499</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3026100472321666</v>
+        <v>0.3177999159564667</v>
       </c>
       <c r="T85">
-        <v>2.483549432133051</v>
+        <v>2.630447072046283</v>
       </c>
       <c r="U85">
         <v>0.1913828270931482</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.018261954452046</v>
+        <v>1.006139788327617</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.171419167621718</v>
+        <v>0.1725572066026605</v>
       </c>
       <c r="C86">
-        <v>-2083.27935465221</v>
+        <v>-2174.685041235397</v>
       </c>
       <c r="D86">
-        <v>3054.508645347791</v>
+        <v>3027.084958764604</v>
       </c>
       <c r="E86">
-        <v>3278.888</v>
+        <v>3342.87</v>
       </c>
       <c r="F86">
-        <v>5374.488</v>
+        <v>5438.47</v>
       </c>
       <c r="G86">
         <v>236.7</v>
@@ -8333,37 +8333,37 @@
         <v>1034.9</v>
       </c>
       <c r="M86">
-        <v>1028.5847076182</v>
+        <v>1040.829763661274</v>
       </c>
       <c r="N86">
-        <v>6.315292381799964</v>
+        <v>-5.929763661273682</v>
       </c>
       <c r="O86">
-        <v>1.578823095449991</v>
+        <v>-1.482440915318421</v>
       </c>
       <c r="P86">
-        <v>4.736469286349973</v>
+        <v>-4.447322745955262</v>
       </c>
       <c r="Q86">
-        <v>878.3364692863499</v>
+        <v>869.1526772540446</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3177999159564665</v>
+        <v>0.3354597184873546</v>
       </c>
       <c r="T86">
-        <v>2.630447072046282</v>
+        <v>2.801230859596146</v>
       </c>
       <c r="U86">
         <v>0.1913828270931482</v>
       </c>
       <c r="V86">
-        <v>0.25</v>
+        <v>0.2485757124103526</v>
       </c>
       <c r="W86">
-        <v>0.1435371203198612</v>
+        <v>0.1438097045053616</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.006139788327617</v>
+        <v>0.9943028496414102</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1725572066026605</v>
+        <v>0.174013034873592</v>
       </c>
       <c r="C87">
-        <v>-2174.685041235397</v>
+        <v>-2273.038865175341</v>
       </c>
       <c r="D87">
-        <v>3027.084958764604</v>
+        <v>2992.713134824659</v>
       </c>
       <c r="E87">
-        <v>3342.87</v>
+        <v>3406.852</v>
       </c>
       <c r="F87">
-        <v>5438.47</v>
+        <v>5502.452</v>
       </c>
       <c r="G87">
         <v>236.7</v>
@@ -8415,37 +8415,37 @@
         <v>1034.9</v>
       </c>
       <c r="M87">
-        <v>1040.829763661274</v>
+        <v>1053.074819704348</v>
       </c>
       <c r="N87">
-        <v>-5.929763661273682</v>
+        <v>-18.17481970434756</v>
       </c>
       <c r="O87">
-        <v>-1.482440915318421</v>
+        <v>-4.543704926086889</v>
       </c>
       <c r="P87">
-        <v>-4.447322745955262</v>
+        <v>-13.63111477826067</v>
       </c>
       <c r="Q87">
-        <v>869.1526772540446</v>
+        <v>859.9688852217392</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3354597184873546</v>
+        <v>0.3561496983793085</v>
       </c>
       <c r="T87">
-        <v>2.801230859596146</v>
+        <v>3.001318778138728</v>
       </c>
       <c r="U87">
         <v>0.1913828270931482</v>
       </c>
       <c r="V87">
-        <v>0.2485757124103526</v>
+        <v>0.2456852971497671</v>
       </c>
       <c r="W87">
-        <v>0.1438097045053616</v>
+        <v>0.1443628803494056</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9943028496414102</v>
+        <v>0.9827411885990682</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.174013034873592</v>
+        <v>0.1754688631445235</v>
       </c>
       <c r="C88">
-        <v>-2273.038865175341</v>
+        <v>-2370.620885124692</v>
       </c>
       <c r="D88">
-        <v>2992.713134824659</v>
+        <v>2959.113114875309</v>
       </c>
       <c r="E88">
-        <v>3406.852</v>
+        <v>3470.834</v>
       </c>
       <c r="F88">
-        <v>5502.452</v>
+        <v>5566.434</v>
       </c>
       <c r="G88">
         <v>236.7</v>
@@ -8497,37 +8497,37 @@
         <v>1034.9</v>
       </c>
       <c r="M88">
-        <v>1053.074819704348</v>
+        <v>1065.319875747422</v>
       </c>
       <c r="N88">
-        <v>-18.17481970434756</v>
+        <v>-30.41987574742143</v>
       </c>
       <c r="O88">
-        <v>-4.543704926086889</v>
+        <v>-7.604968936855357</v>
       </c>
       <c r="P88">
-        <v>-13.63111477826067</v>
+        <v>-22.81490681056607</v>
       </c>
       <c r="Q88">
-        <v>859.9688852217392</v>
+        <v>850.7850931894338</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3561496983793085</v>
+        <v>0.3800227521007938</v>
       </c>
       <c r="T88">
-        <v>3.001318778138728</v>
+        <v>3.232189453380169</v>
       </c>
       <c r="U88">
         <v>0.1913828270931482</v>
       </c>
       <c r="V88">
-        <v>0.2456852971497671</v>
+        <v>0.2428613282170111</v>
       </c>
       <c r="W88">
-        <v>0.1443628803494056</v>
+        <v>0.1449033395073797</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9827411885990682</v>
+        <v>0.9714453128680444</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1754688631445235</v>
+        <v>0.176924691415455</v>
       </c>
       <c r="C89">
-        <v>-2370.620885124692</v>
+        <v>-2467.456808234188</v>
       </c>
       <c r="D89">
-        <v>2959.113114875309</v>
+        <v>2926.259191765813</v>
       </c>
       <c r="E89">
-        <v>3470.834</v>
+        <v>3534.816000000001</v>
       </c>
       <c r="F89">
-        <v>5566.434</v>
+        <v>5630.416000000001</v>
       </c>
       <c r="G89">
         <v>236.7</v>
@@ -8579,37 +8579,37 @@
         <v>1034.9</v>
       </c>
       <c r="M89">
-        <v>1065.319875747422</v>
+        <v>1077.564931790495</v>
       </c>
       <c r="N89">
-        <v>-30.41987574742143</v>
+        <v>-42.6649317904953</v>
       </c>
       <c r="O89">
-        <v>-7.604968936855357</v>
+        <v>-10.66623294762383</v>
       </c>
       <c r="P89">
-        <v>-22.81490681056607</v>
+        <v>-31.99869884287148</v>
       </c>
       <c r="Q89">
-        <v>850.7850931894338</v>
+        <v>841.6013011571284</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3800227521007938</v>
+        <v>0.4078746481091934</v>
       </c>
       <c r="T89">
-        <v>3.232189453380169</v>
+        <v>3.501538574495184</v>
       </c>
       <c r="U89">
         <v>0.1913828270931482</v>
       </c>
       <c r="V89">
-        <v>0.2428613282170111</v>
+        <v>0.2401015403963632</v>
       </c>
       <c r="W89">
-        <v>0.1449033395073797</v>
+        <v>0.1454315155026725</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9714453128680444</v>
+        <v>0.9604061615854529</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.176924691415455</v>
+        <v>0.1783805196863865</v>
       </c>
       <c r="C90">
-        <v>-2467.456808234188</v>
+        <v>-2563.571212523468</v>
       </c>
       <c r="D90">
-        <v>2926.259191765813</v>
+        <v>2894.126787476534</v>
       </c>
       <c r="E90">
-        <v>3534.816000000001</v>
+        <v>3598.798000000001</v>
       </c>
       <c r="F90">
-        <v>5630.416000000001</v>
+        <v>5694.398000000001</v>
       </c>
       <c r="G90">
         <v>236.7</v>
@@ -8661,37 +8661,37 @@
         <v>1034.9</v>
       </c>
       <c r="M90">
-        <v>1077.564931790495</v>
+        <v>1089.809987833569</v>
       </c>
       <c r="N90">
-        <v>-42.6649317904953</v>
+        <v>-54.90998783356918</v>
       </c>
       <c r="O90">
-        <v>-10.66623294762383</v>
+        <v>-13.72749695839229</v>
       </c>
       <c r="P90">
-        <v>-31.99869884287148</v>
+        <v>-41.18249087517688</v>
       </c>
       <c r="Q90">
-        <v>841.6013011571284</v>
+        <v>832.417509124823</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4078746481091934</v>
+        <v>0.4407905252100291</v>
       </c>
       <c r="T90">
-        <v>3.501538574495184</v>
+        <v>3.819860263085655</v>
       </c>
       <c r="U90">
         <v>0.1913828270931482</v>
       </c>
       <c r="V90">
-        <v>0.2401015403963632</v>
+        <v>0.2374037702795501</v>
       </c>
       <c r="W90">
-        <v>0.1454315155026725</v>
+        <v>0.1459478223744756</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9604061615854529</v>
+        <v>0.9496150811182006</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1783805196863865</v>
+        <v>0.179836347957318</v>
       </c>
       <c r="C91">
-        <v>-2563.571212523468</v>
+        <v>-2658.98760820105</v>
       </c>
       <c r="D91">
-        <v>2894.126787476534</v>
+        <v>2862.692391798951</v>
       </c>
       <c r="E91">
-        <v>3598.798000000001</v>
+        <v>3662.780000000001</v>
       </c>
       <c r="F91">
-        <v>5694.398000000001</v>
+        <v>5758.380000000001</v>
       </c>
       <c r="G91">
         <v>236.7</v>
@@ -8743,37 +8743,37 @@
         <v>1034.9</v>
       </c>
       <c r="M91">
-        <v>1089.809987833569</v>
+        <v>1102.055043876643</v>
       </c>
       <c r="N91">
-        <v>-54.90998783356918</v>
+        <v>-67.15504387664282</v>
       </c>
       <c r="O91">
-        <v>-13.72749695839229</v>
+        <v>-16.78876096916071</v>
       </c>
       <c r="P91">
-        <v>-41.18249087517688</v>
+        <v>-50.36628290748212</v>
       </c>
       <c r="Q91">
-        <v>832.417509124823</v>
+        <v>823.2337170925177</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4407905252100291</v>
+        <v>0.480289577731032</v>
       </c>
       <c r="T91">
-        <v>3.819860263085655</v>
+        <v>4.20184628939422</v>
       </c>
       <c r="U91">
         <v>0.1913828270931482</v>
       </c>
       <c r="V91">
-        <v>0.2374037702795501</v>
+        <v>0.2347659506097774</v>
       </c>
       <c r="W91">
-        <v>0.1459478223744756</v>
+        <v>0.1464526557602386</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9496150811182006</v>
+        <v>0.9390638024391096</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.179836347957318</v>
+        <v>0.1812921762282494</v>
       </c>
       <c r="C92">
-        <v>-2658.98760820105</v>
+        <v>-2753.728495031096</v>
       </c>
       <c r="D92">
-        <v>2862.692391798951</v>
+        <v>2831.933504968905</v>
       </c>
       <c r="E92">
-        <v>3662.780000000001</v>
+        <v>3726.762000000001</v>
       </c>
       <c r="F92">
-        <v>5758.380000000001</v>
+        <v>5822.362000000001</v>
       </c>
       <c r="G92">
         <v>236.7</v>
@@ -8825,37 +8825,37 @@
         <v>1034.9</v>
       </c>
       <c r="M92">
-        <v>1102.055043876643</v>
+        <v>1114.300099919717</v>
       </c>
       <c r="N92">
-        <v>-67.15504387664282</v>
+        <v>-79.40009991971669</v>
       </c>
       <c r="O92">
-        <v>-16.78876096916071</v>
+        <v>-19.85002497992917</v>
       </c>
       <c r="P92">
-        <v>-50.36628290748212</v>
+        <v>-59.55007493978752</v>
       </c>
       <c r="Q92">
-        <v>823.2337170925177</v>
+        <v>814.0499250602124</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.480289577731032</v>
+        <v>0.5285661974789245</v>
       </c>
       <c r="T92">
-        <v>4.20184628939422</v>
+        <v>4.668718099326912</v>
       </c>
       <c r="U92">
         <v>0.1913828270931482</v>
       </c>
       <c r="V92">
-        <v>0.2347659506097774</v>
+        <v>0.2321861049986809</v>
       </c>
       <c r="W92">
-        <v>0.1464526557602386</v>
+        <v>0.1469463939067541</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9390638024391096</v>
+        <v>0.9287444199947238</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1812921762282494</v>
+        <v>0.1827480044991809</v>
       </c>
       <c r="C93">
-        <v>-2753.728495031096</v>
+        <v>-2847.815416041146</v>
       </c>
       <c r="D93">
-        <v>2831.933504968905</v>
+        <v>2801.828583958855</v>
       </c>
       <c r="E93">
-        <v>3726.762000000001</v>
+        <v>3790.744000000001</v>
       </c>
       <c r="F93">
-        <v>5822.362000000001</v>
+        <v>5886.344000000001</v>
       </c>
       <c r="G93">
         <v>236.7</v>
@@ -8907,37 +8907,37 @@
         <v>1034.9</v>
       </c>
       <c r="M93">
-        <v>1114.300099919717</v>
+        <v>1126.545155962791</v>
       </c>
       <c r="N93">
-        <v>-79.40009991971669</v>
+        <v>-91.64515596279057</v>
       </c>
       <c r="O93">
-        <v>-19.85002497992917</v>
+        <v>-22.91128899069764</v>
       </c>
       <c r="P93">
-        <v>-59.55007493978752</v>
+        <v>-68.73386697209293</v>
       </c>
       <c r="Q93">
-        <v>814.0499250602124</v>
+        <v>804.8661330279069</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5285661974789245</v>
+        <v>0.5889119721637903</v>
       </c>
       <c r="T93">
-        <v>4.668718099326912</v>
+        <v>5.252307861742779</v>
       </c>
       <c r="U93">
         <v>0.1913828270931482</v>
       </c>
       <c r="V93">
-        <v>0.2321861049986809</v>
+        <v>0.2296623429878257</v>
       </c>
       <c r="W93">
-        <v>0.1469463939067541</v>
+        <v>0.1474293986153019</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9287444199947238</v>
+        <v>0.9186493719513028</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1827480044991809</v>
+        <v>0.1842038327701124</v>
       </c>
       <c r="C94">
-        <v>-2847.815416041146</v>
+        <v>-2941.269007840243</v>
       </c>
       <c r="D94">
-        <v>2801.828583958855</v>
+        <v>2772.356992159758</v>
       </c>
       <c r="E94">
-        <v>3790.744000000001</v>
+        <v>3854.726000000001</v>
       </c>
       <c r="F94">
-        <v>5886.344000000001</v>
+        <v>5950.326000000001</v>
       </c>
       <c r="G94">
         <v>236.7</v>
@@ -8989,37 +8989,37 @@
         <v>1034.9</v>
       </c>
       <c r="M94">
-        <v>1126.545155962791</v>
+        <v>1138.790212005865</v>
       </c>
       <c r="N94">
-        <v>-91.64515596279057</v>
+        <v>-103.8902120058644</v>
       </c>
       <c r="O94">
-        <v>-22.91128899069764</v>
+        <v>-25.97255300146611</v>
       </c>
       <c r="P94">
-        <v>-68.73386697209293</v>
+        <v>-77.91765900439833</v>
       </c>
       <c r="Q94">
-        <v>804.8661330279069</v>
+        <v>795.6823409956016</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5889119721637903</v>
+        <v>0.6664993967586176</v>
       </c>
       <c r="T94">
-        <v>5.252307861742779</v>
+        <v>6.002637556277461</v>
       </c>
       <c r="U94">
         <v>0.1913828270931482</v>
       </c>
       <c r="V94">
-        <v>0.2296623429878257</v>
+        <v>0.2271928554288168</v>
       </c>
       <c r="W94">
-        <v>0.1474293986153019</v>
+        <v>0.1479020161258164</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9186493719513028</v>
+        <v>0.9087714217152673</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1842038327701124</v>
+        <v>0.1856596610410439</v>
       </c>
       <c r="C95">
-        <v>-2941.269007840243</v>
+        <v>-3034.109047794424</v>
       </c>
       <c r="D95">
-        <v>2772.356992159758</v>
+        <v>2743.498952205577</v>
       </c>
       <c r="E95">
-        <v>3854.726000000001</v>
+        <v>3918.708000000001</v>
       </c>
       <c r="F95">
-        <v>5950.326000000001</v>
+        <v>6014.308000000001</v>
       </c>
       <c r="G95">
         <v>236.7</v>
@@ -9071,37 +9071,37 @@
         <v>1034.9</v>
       </c>
       <c r="M95">
-        <v>1138.790212005865</v>
+        <v>1151.035268048938</v>
       </c>
       <c r="N95">
-        <v>-103.8902120058644</v>
+        <v>-116.1352680489381</v>
       </c>
       <c r="O95">
-        <v>-25.97255300146611</v>
+        <v>-29.03381701223452</v>
       </c>
       <c r="P95">
-        <v>-77.91765900439833</v>
+        <v>-87.10145103670357</v>
       </c>
       <c r="Q95">
-        <v>795.6823409956016</v>
+        <v>786.4985489632963</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6664993967586176</v>
+        <v>0.7699492962183871</v>
       </c>
       <c r="T95">
-        <v>6.002637556277461</v>
+        <v>7.003077148990372</v>
       </c>
       <c r="U95">
         <v>0.1913828270931482</v>
       </c>
       <c r="V95">
-        <v>0.2271928554288168</v>
+        <v>0.2247759101582975</v>
       </c>
       <c r="W95">
-        <v>0.1479020161258164</v>
+        <v>0.1483645779446177</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9087714217152673</v>
+        <v>0.89910364063319</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1856596610410439</v>
+        <v>0.1871154893119754</v>
       </c>
       <c r="C96">
-        <v>-3034.109047794424</v>
+        <v>-3126.354498286214</v>
       </c>
       <c r="D96">
-        <v>2743.498952205577</v>
+        <v>2715.235501713787</v>
       </c>
       <c r="E96">
-        <v>3918.708000000001</v>
+        <v>3982.690000000001</v>
       </c>
       <c r="F96">
-        <v>6014.308000000001</v>
+        <v>6078.290000000001</v>
       </c>
       <c r="G96">
         <v>236.7</v>
@@ -9153,37 +9153,37 @@
         <v>1034.9</v>
       </c>
       <c r="M96">
-        <v>1151.035268048938</v>
+        <v>1163.280324092012</v>
       </c>
       <c r="N96">
-        <v>-116.1352680489381</v>
+        <v>-128.380324092012</v>
       </c>
       <c r="O96">
-        <v>-29.03381701223452</v>
+        <v>-32.09508102300299</v>
       </c>
       <c r="P96">
-        <v>-87.10145103670357</v>
+        <v>-96.28524306900897</v>
       </c>
       <c r="Q96">
-        <v>786.4985489632963</v>
+        <v>777.3147569309909</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7699492962183871</v>
+        <v>0.9147791554620653</v>
       </c>
       <c r="T96">
-        <v>7.003077148990372</v>
+        <v>8.403692578788453</v>
       </c>
       <c r="U96">
         <v>0.1913828270931482</v>
       </c>
       <c r="V96">
-        <v>0.2247759101582975</v>
+        <v>0.2224098479461049</v>
       </c>
       <c r="W96">
-        <v>0.1483645779446177</v>
+        <v>0.1488174016198655</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.89910364063319</v>
+        <v>0.8896393917844195</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1871154893119754</v>
+        <v>0.1885713175829069</v>
       </c>
       <c r="C97">
-        <v>-3126.354498286214</v>
+        <v>-3218.023548266237</v>
       </c>
       <c r="D97">
-        <v>2715.235501713787</v>
+        <v>2687.548451733765</v>
       </c>
       <c r="E97">
-        <v>3982.690000000001</v>
+        <v>4046.672000000001</v>
       </c>
       <c r="F97">
-        <v>6078.290000000001</v>
+        <v>6142.272000000001</v>
       </c>
       <c r="G97">
         <v>236.7</v>
@@ -9235,37 +9235,37 @@
         <v>1034.9</v>
       </c>
       <c r="M97">
-        <v>1163.280324092012</v>
+        <v>1175.525380135086</v>
       </c>
       <c r="N97">
-        <v>-128.380324092012</v>
+        <v>-140.6253801350858</v>
       </c>
       <c r="O97">
-        <v>-32.09508102300299</v>
+        <v>-35.15634503377146</v>
       </c>
       <c r="P97">
-        <v>-96.28524306900897</v>
+        <v>-105.4690351013144</v>
       </c>
       <c r="Q97">
-        <v>777.3147569309909</v>
+        <v>768.1309648986855</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9147791554620653</v>
+        <v>1.132023944327582</v>
       </c>
       <c r="T97">
-        <v>8.403692578788453</v>
+        <v>10.50461572348557</v>
       </c>
       <c r="U97">
         <v>0.1913828270931482</v>
       </c>
       <c r="V97">
-        <v>0.2224098479461049</v>
+        <v>0.2200930786966663</v>
       </c>
       <c r="W97">
-        <v>0.1488174016198655</v>
+        <v>0.1492607914685455</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8896393917844195</v>
+        <v>0.8803723147866651</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1885713175829068</v>
+        <v>0.1900271458538383</v>
       </c>
       <c r="C98">
-        <v>-3218.023548266236</v>
+        <v>-3309.133652288327</v>
       </c>
       <c r="D98">
-        <v>2687.548451733765</v>
+        <v>2660.420347711674</v>
       </c>
       <c r="E98">
-        <v>4046.672000000001</v>
+        <v>4110.654</v>
       </c>
       <c r="F98">
-        <v>6142.272000000001</v>
+        <v>6206.254000000001</v>
       </c>
       <c r="G98">
         <v>236.7</v>
@@ -9317,37 +9317,37 @@
         <v>1034.9</v>
       </c>
       <c r="M98">
-        <v>1175.525380135086</v>
+        <v>1187.77043617816</v>
       </c>
       <c r="N98">
-        <v>-140.6253801350858</v>
+        <v>-152.8704361781595</v>
       </c>
       <c r="O98">
-        <v>-35.15634503377146</v>
+        <v>-38.21760904453987</v>
       </c>
       <c r="P98">
-        <v>-105.4690351013144</v>
+        <v>-114.6528271336196</v>
       </c>
       <c r="Q98">
-        <v>768.1309648986855</v>
+        <v>758.9471728663802</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.132023944327579</v>
+        <v>1.494098592436772</v>
       </c>
       <c r="T98">
-        <v>10.50461572348554</v>
+        <v>14.00615429798072</v>
       </c>
       <c r="U98">
         <v>0.1913828270931482</v>
       </c>
       <c r="V98">
-        <v>0.2200930786966663</v>
+        <v>0.2178240778853605</v>
       </c>
       <c r="W98">
-        <v>0.1492607914685455</v>
+        <v>0.1496950392584898</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8803723147866651</v>
+        <v>0.8712963115414419</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1900271458538383</v>
+        <v>0.1914829741247698</v>
       </c>
       <c r="C99">
-        <v>-3309.133652288327</v>
+        <v>-3399.701567204114</v>
       </c>
       <c r="D99">
-        <v>2660.420347711674</v>
+        <v>2633.834432795887</v>
       </c>
       <c r="E99">
-        <v>4110.654</v>
+        <v>4174.636</v>
       </c>
       <c r="F99">
-        <v>6206.254000000001</v>
+        <v>6270.236000000001</v>
       </c>
       <c r="G99">
         <v>236.7</v>
@@ -9399,37 +9399,37 @@
         <v>1034.9</v>
       </c>
       <c r="M99">
-        <v>1187.77043617816</v>
+        <v>1200.015492221233</v>
       </c>
       <c r="N99">
-        <v>-152.8704361781595</v>
+        <v>-165.1154922212334</v>
       </c>
       <c r="O99">
-        <v>-38.21760904453987</v>
+        <v>-41.27887305530834</v>
       </c>
       <c r="P99">
-        <v>-114.6528271336196</v>
+        <v>-123.836619165925</v>
       </c>
       <c r="Q99">
-        <v>758.9471728663802</v>
+        <v>749.763380834075</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.494098592436772</v>
+        <v>2.218247888655158</v>
       </c>
       <c r="T99">
-        <v>14.00615429798072</v>
+        <v>21.00923144697108</v>
       </c>
       <c r="U99">
         <v>0.1913828270931482</v>
       </c>
       <c r="V99">
-        <v>0.2178240778853605</v>
+        <v>0.2156013832130609</v>
       </c>
       <c r="W99">
-        <v>0.1496950392584898</v>
+        <v>0.1501204248486394</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8712963115414419</v>
+        <v>0.8624055328522435</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1914829741247698</v>
+        <v>0.1929388023957013</v>
       </c>
       <c r="C100">
-        <v>-3399.701567204114</v>
+        <v>-3489.743386679232</v>
       </c>
       <c r="D100">
-        <v>2633.834432795887</v>
+        <v>2607.774613320769</v>
       </c>
       <c r="E100">
-        <v>4174.636</v>
+        <v>4238.618</v>
       </c>
       <c r="F100">
-        <v>6270.236000000001</v>
+        <v>6334.218000000001</v>
       </c>
       <c r="G100">
         <v>236.7</v>
@@ -9481,37 +9481,37 @@
         <v>1034.9</v>
       </c>
       <c r="M100">
-        <v>1200.015492221233</v>
+        <v>1212.260548264307</v>
       </c>
       <c r="N100">
-        <v>-165.1154922212334</v>
+        <v>-177.3605482643072</v>
       </c>
       <c r="O100">
-        <v>-41.27887305530834</v>
+        <v>-44.34013706607681</v>
       </c>
       <c r="P100">
-        <v>-123.836619165925</v>
+        <v>-133.0204111982304</v>
       </c>
       <c r="Q100">
-        <v>749.763380834075</v>
+        <v>740.5795888017694</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.218247888655158</v>
+        <v>4.390695777310316</v>
       </c>
       <c r="T100">
-        <v>21.00923144697108</v>
+        <v>42.01846289394216</v>
       </c>
       <c r="U100">
         <v>0.1913828270931482</v>
       </c>
       <c r="V100">
-        <v>0.2156013832130609</v>
+        <v>0.213423591463434</v>
       </c>
       <c r="W100">
-        <v>0.1501204248486394</v>
+        <v>0.1505372167905031</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8624055328522435</v>
+        <v>0.8536943658537359</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1929388023957013</v>
-      </c>
-      <c r="C101">
-        <v>-3489.743386679232</v>
-      </c>
-      <c r="D101">
-        <v>2607.774613320769</v>
-      </c>
-      <c r="E101">
-        <v>4238.618</v>
-      </c>
-      <c r="F101">
-        <v>6334.218000000001</v>
-      </c>
-      <c r="G101">
-        <v>236.7</v>
-      </c>
-      <c r="H101">
-        <v>4302.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1908.5</v>
-      </c>
-      <c r="K101">
-        <v>873.5999999999999</v>
-      </c>
-      <c r="L101">
-        <v>1034.9</v>
-      </c>
-      <c r="M101">
-        <v>1212.260548264307</v>
-      </c>
-      <c r="N101">
-        <v>-177.3605482643072</v>
-      </c>
-      <c r="O101">
-        <v>-44.34013706607681</v>
-      </c>
-      <c r="P101">
-        <v>-133.0204111982304</v>
-      </c>
-      <c r="Q101">
-        <v>740.5795888017694</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.390695777310316</v>
-      </c>
-      <c r="T101">
-        <v>42.01846289394216</v>
-      </c>
-      <c r="U101">
-        <v>0.1913828270931482</v>
-      </c>
-      <c r="V101">
-        <v>0.213423591463434</v>
-      </c>
-      <c r="W101">
-        <v>0.1505372167905031</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8536943658537359</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
